--- a/InputData/trans/BNVFE/BAU New Veh Fuel Economy.xlsx
+++ b/InputData/trans/BNVFE/BAU New Veh Fuel Economy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mary Francis Swint\Vensim\eps-southkorea\InputData\trans\BNVFE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{326CC5F0-0959-406D-94DC-3642BBE429BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC0E3A67-6F24-4A2B-9CC4-E71EB2D4552A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19305" yWindow="-2205" windowWidth="19410" windowHeight="20985" firstSheet="15" activeTab="19" xr2:uid="{D850E225-7E57-43A0-BCF6-AD6641E8498D}"/>
+    <workbookView xWindow="-38505" yWindow="-2205" windowWidth="19410" windowHeight="20985" firstSheet="1" activeTab="2" xr2:uid="{D850E225-7E57-43A0-BCF6-AD6641E8498D}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -10478,25 +10478,25 @@
         <v>16</v>
       </c>
       <c r="B2" s="34">
-        <v>7.4207159768494967E-4</v>
+        <v>8.2452399742772187E-4</v>
       </c>
       <c r="C2" s="34">
-        <v>1.6230924049734821E-4</v>
+        <v>1.8034360055260913E-4</v>
       </c>
       <c r="D2" s="34">
-        <v>2.2348928777281296E-4</v>
+        <v>2.4832143085868106E-4</v>
       </c>
       <c r="E2" s="34">
-        <v>2.0739874957340556E-4</v>
+        <v>2.3044305508156172E-4</v>
       </c>
       <c r="F2" s="34">
-        <v>2.5516646508322039E-4</v>
+        <v>2.8351829453691153E-4</v>
       </c>
       <c r="G2" s="34">
-        <v>2.1840083851069807E-4</v>
+        <v>2.4266759834522006E-4</v>
       </c>
       <c r="H2" s="34">
-        <v>1.1207603070812352E-3</v>
+        <v>1.2452892300902612E-3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -10504,25 +10504,25 @@
         <v>17</v>
       </c>
       <c r="B3" s="34">
-        <v>2.0762257316084497E-3</v>
+        <v>2.3069174795649441E-3</v>
       </c>
       <c r="C3" s="34">
-        <v>1.468986233474341E-3</v>
+        <v>1.632206926082601E-3</v>
       </c>
       <c r="D3" s="34">
-        <v>5.3269391006043217E-4</v>
+        <v>5.9188212228936902E-4</v>
       </c>
       <c r="E3" s="34">
-        <v>6.4609992731560952E-4</v>
+        <v>7.1788880812845496E-4</v>
       </c>
       <c r="F3" s="34">
-        <v>1.4326691196766717E-3</v>
+        <v>1.591854577418524E-3</v>
       </c>
       <c r="G3" s="34">
-        <v>1.1440897583490175E-3</v>
+        <v>1.2712108426100193E-3</v>
       </c>
       <c r="H3" s="34">
-        <v>1.9382997819468279E-3</v>
+        <v>2.1536664243853644E-3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -10530,16 +10530,16 @@
         <v>18</v>
       </c>
       <c r="B4" s="34">
-        <v>5.2005024340248229E-4</v>
+        <v>1.3685532721117956E-3</v>
       </c>
       <c r="C4" s="34">
-        <v>1.6183424535563703E-4</v>
+        <v>4.2587959304115009E-4</v>
       </c>
       <c r="D4" s="34">
-        <v>1.6183424535563703E-4</v>
+        <v>4.2587959304115009E-4</v>
       </c>
       <c r="E4" s="34">
-        <v>1.6183424535563703E-4</v>
+        <v>4.2587959304115009E-4</v>
       </c>
       <c r="F4" s="34">
         <v>0</v>
@@ -10548,7 +10548,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="34">
-        <v>4.855027360669111E-4</v>
+        <v>1.2776387791234502E-3</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -10582,16 +10582,16 @@
         <v>20</v>
       </c>
       <c r="B6" s="34">
-        <v>2.8337186195252846E-3</v>
+        <v>4.1217725374913233E-3</v>
       </c>
       <c r="C6" s="34">
         <v>0</v>
       </c>
       <c r="D6" s="34">
-        <v>8.8182399449386899E-4</v>
+        <v>1.2826530829001732E-3</v>
       </c>
       <c r="E6" s="34">
-        <v>8.8182386251894039E-4</v>
+        <v>1.2826528909366407E-3</v>
       </c>
       <c r="F6" s="34">
         <v>0</v>
@@ -10600,7 +10600,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="34">
-        <v>2.6454715875568204E-3</v>
+        <v>3.8479586728099209E-3</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -10755,127 +10755,127 @@
       </c>
       <c r="B2" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$2:$H$2,,MATCH($A2,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>7.4775158711811547E-4</v>
+        <v>8.308350967979061E-4</v>
       </c>
       <c r="C2" s="14">
         <f>IFERROR(B2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>7.5347505251783424E-4</v>
+        <v>8.3719450279759369E-4</v>
       </c>
       <c r="D2" s="14">
         <f>IFERROR(C2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>7.5924232665931454E-4</v>
+        <v>8.4360258517701626E-4</v>
       </c>
       <c r="E2" s="14">
         <f>IFERROR(D2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>7.6505374486490394E-4</v>
+        <v>8.5005971651656007E-4</v>
       </c>
       <c r="F2" s="14">
         <f>IFERROR(E2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>7.7090964502358583E-4</v>
+        <v>8.5656627224842878E-4</v>
       </c>
       <c r="G2" s="14">
         <f>IFERROR(F2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>7.7681036761062462E-4</v>
+        <v>8.6312263067847192E-4</v>
       </c>
       <c r="H2" s="14">
         <f>IFERROR(G2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>7.827562557073622E-4</v>
+        <v>8.6972917300818034E-4</v>
       </c>
       <c r="I2" s="14">
         <f>IFERROR(H2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>7.8874765502116514E-4</v>
+        <v>8.7638628335685029E-4</v>
       </c>
       <c r="J2" s="14">
         <f>IFERROR(I2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>7.9478491390552492E-4</v>
+        <v>8.8309434878391675E-4</v>
       </c>
       <c r="K2" s="14">
         <f>IFERROR(J2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>8.0086838338031213E-4</v>
+        <v>8.8985375931145813E-4</v>
       </c>
       <c r="L2" s="14">
         <f>IFERROR(K2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>8.0699841715218548E-4</v>
+        <v>8.9666490794687299E-4</v>
       </c>
       <c r="M2" s="14">
         <f>IFERROR(L2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>8.1317537163515708E-4</v>
+        <v>9.035281907057303E-4</v>
       </c>
       <c r="N2" s="14">
         <f>IFERROR(M2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>8.1939960597131518E-4</v>
+        <v>9.1044400663479487E-4</v>
       </c>
       <c r="O2" s="14">
         <f>IFERROR(N2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>8.2567148205170556E-4</v>
+        <v>9.1741275783522864E-4</v>
       </c>
       <c r="P2" s="14">
         <f>IFERROR(O2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>8.3199136453737253E-4</v>
+        <v>9.2443484948596976E-4</v>
       </c>
       <c r="Q2" s="14">
         <f>IFERROR(P2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>8.3835962088056137E-4</v>
+        <v>9.3151068986729077E-4</v>
       </c>
       <c r="R2" s="14">
         <f>IFERROR(Q2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>8.4477662134608276E-4</v>
+        <v>9.3864069038453667E-4</v>
       </c>
       <c r="S2" s="14">
         <f>IFERROR(R2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>8.5124273903284056E-4</v>
+        <v>9.4582526559204539E-4</v>
       </c>
       <c r="T2" s="14">
         <f>IFERROR(S2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>8.5775834989552501E-4</v>
+        <v>9.530648332172504E-4</v>
       </c>
       <c r="U2" s="14">
         <f>IFERROR(T2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>8.6432383276647141E-4</v>
+        <v>9.6035981418496862E-4</v>
       </c>
       <c r="V2" s="14">
         <f>IFERROR(U2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>8.7093956937768621E-4</v>
+        <v>9.6771063264187388E-4</v>
       </c>
       <c r="W2" s="14">
         <f>IFERROR(V2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>8.7760594438304187E-4</v>
+        <v>9.7511771598115789E-4</v>
       </c>
       <c r="X2" s="14">
         <f>IFERROR(W2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>8.8432334538064141E-4</v>
+        <v>9.8258149486737966E-4</v>
       </c>
       <c r="Y2" s="14">
         <f>IFERROR(X2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>8.9109216293535457E-4</v>
+        <v>9.9010240326150543E-4</v>
       </c>
       <c r="Z2" s="14">
         <f>IFERROR(Y2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>8.979127906015256E-4</v>
+        <v>9.9768087844613997E-4</v>
       </c>
       <c r="AA2" s="14">
         <f>IFERROR(Z2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>9.0478562494585577E-4</v>
+        <v>1.0053173610509512E-3</v>
       </c>
       <c r="AB2" s="14">
         <f>IFERROR(AA2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>9.1171106557046068E-4</v>
+        <v>1.0130122950782899E-3</v>
       </c>
       <c r="AC2" s="14">
         <f>IFERROR(AB2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>9.1868951513610368E-4</v>
+        <v>1.0207661279290044E-3</v>
       </c>
       <c r="AD2" s="14">
         <f>IFERROR(AC2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>9.257213793856079E-4</v>
+        <v>1.0285793104284535E-3</v>
       </c>
       <c r="AE2" s="14">
         <f>IFERROR(AD2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>9.3280706716744686E-4</v>
+        <v>1.036452296852719E-3</v>
       </c>
       <c r="AF2" s="14">
         <f>IFERROR(AE2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>9.3994699045951572E-4</v>
+        <v>1.0443855449550178E-3</v>
       </c>
       <c r="AG2" s="14"/>
     </row>
@@ -10885,127 +10885,127 @@
       </c>
       <c r="B3" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$2:$H$2,,MATCH($A3,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.6230924049734821E-4</v>
+        <v>1.8034360055260913E-4</v>
       </c>
       <c r="C3" s="14">
         <f>IFERROR(B3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.6230924049734821E-4</v>
+        <v>1.8034360055260913E-4</v>
       </c>
       <c r="D3" s="14">
         <f>IFERROR(C3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.6230924049734821E-4</v>
+        <v>1.8034360055260913E-4</v>
       </c>
       <c r="E3" s="14">
         <f>IFERROR(D3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.6230924049734821E-4</v>
+        <v>1.8034360055260913E-4</v>
       </c>
       <c r="F3" s="14">
         <f>IFERROR(E3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.6230924049734821E-4</v>
+        <v>1.8034360055260913E-4</v>
       </c>
       <c r="G3" s="14">
         <f>IFERROR(F3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.6230924049734821E-4</v>
+        <v>1.8034360055260913E-4</v>
       </c>
       <c r="H3" s="14">
         <f>IFERROR(G3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.6230924049734821E-4</v>
+        <v>1.8034360055260913E-4</v>
       </c>
       <c r="I3" s="14">
         <f>IFERROR(H3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.6230924049734821E-4</v>
+        <v>1.8034360055260913E-4</v>
       </c>
       <c r="J3" s="14">
         <f>IFERROR(I3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.6230924049734821E-4</v>
+        <v>1.8034360055260913E-4</v>
       </c>
       <c r="K3" s="14">
         <f>IFERROR(J3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.6230924049734821E-4</v>
+        <v>1.8034360055260913E-4</v>
       </c>
       <c r="L3" s="14">
         <f>IFERROR(K3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.6230924049734821E-4</v>
+        <v>1.8034360055260913E-4</v>
       </c>
       <c r="M3" s="14">
         <f>IFERROR(L3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.6230924049734821E-4</v>
+        <v>1.8034360055260913E-4</v>
       </c>
       <c r="N3" s="14">
         <f>IFERROR(M3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.6230924049734821E-4</v>
+        <v>1.8034360055260913E-4</v>
       </c>
       <c r="O3" s="14">
         <f>IFERROR(N3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.6230924049734821E-4</v>
+        <v>1.8034360055260913E-4</v>
       </c>
       <c r="P3" s="14">
         <f>IFERROR(O3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.6230924049734821E-4</v>
+        <v>1.8034360055260913E-4</v>
       </c>
       <c r="Q3" s="14">
         <f>IFERROR(P3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.6230924049734821E-4</v>
+        <v>1.8034360055260913E-4</v>
       </c>
       <c r="R3" s="14">
         <f>IFERROR(Q3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.6230924049734821E-4</v>
+        <v>1.8034360055260913E-4</v>
       </c>
       <c r="S3" s="14">
         <f>IFERROR(R3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.6230924049734821E-4</v>
+        <v>1.8034360055260913E-4</v>
       </c>
       <c r="T3" s="14">
         <f>IFERROR(S3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.6230924049734821E-4</v>
+        <v>1.8034360055260913E-4</v>
       </c>
       <c r="U3" s="14">
         <f>IFERROR(T3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.6230924049734821E-4</v>
+        <v>1.8034360055260913E-4</v>
       </c>
       <c r="V3" s="14">
         <f>IFERROR(U3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.6230924049734821E-4</v>
+        <v>1.8034360055260913E-4</v>
       </c>
       <c r="W3" s="14">
         <f>IFERROR(V3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.6230924049734821E-4</v>
+        <v>1.8034360055260913E-4</v>
       </c>
       <c r="X3" s="14">
         <f>IFERROR(W3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.6230924049734821E-4</v>
+        <v>1.8034360055260913E-4</v>
       </c>
       <c r="Y3" s="14">
         <f>IFERROR(X3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.6230924049734821E-4</v>
+        <v>1.8034360055260913E-4</v>
       </c>
       <c r="Z3" s="14">
         <f>IFERROR(Y3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.6230924049734821E-4</v>
+        <v>1.8034360055260913E-4</v>
       </c>
       <c r="AA3" s="14">
         <f>IFERROR(Z3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.6230924049734821E-4</v>
+        <v>1.8034360055260913E-4</v>
       </c>
       <c r="AB3" s="14">
         <f>IFERROR(AA3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.6230924049734821E-4</v>
+        <v>1.8034360055260913E-4</v>
       </c>
       <c r="AC3" s="14">
         <f>IFERROR(AB3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.6230924049734821E-4</v>
+        <v>1.8034360055260913E-4</v>
       </c>
       <c r="AD3" s="14">
         <f>IFERROR(AC3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.6230924049734821E-4</v>
+        <v>1.8034360055260913E-4</v>
       </c>
       <c r="AE3" s="14">
         <f>IFERROR(AD3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.6230924049734821E-4</v>
+        <v>1.8034360055260913E-4</v>
       </c>
       <c r="AF3" s="14">
         <f>IFERROR(AE3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.6230924049734821E-4</v>
+        <v>1.8034360055260913E-4</v>
       </c>
       <c r="AG3" s="14"/>
     </row>
@@ -11015,127 +11015,127 @@
       </c>
       <c r="B4" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$2:$H$2,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.2408983655186905E-4</v>
+        <v>2.4898870727985448E-4</v>
       </c>
       <c r="C4" s="14">
         <f>IFERROR(B4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.2469199909433911E-4</v>
+        <v>2.4965777677148792E-4</v>
       </c>
       <c r="D4" s="14">
         <f>IFERROR(C4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.2529577973664421E-4</v>
+        <v>2.503286441518269E-4</v>
       </c>
       <c r="E4" s="14">
         <f>IFERROR(D4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.2590118282685796E-4</v>
+        <v>2.5100131425206441E-4</v>
       </c>
       <c r="F4" s="14">
         <f>IFERROR(E4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.2650821272473791E-4</v>
+        <v>2.516757919163755E-4</v>
       </c>
       <c r="G4" s="14">
         <f>IFERROR(F4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.2711687380175694E-4</v>
+        <v>2.5235208200195222E-4</v>
       </c>
       <c r="H4" s="14">
         <f>IFERROR(G4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.2772717044113473E-4</v>
+        <v>2.5303018937903866E-4</v>
       </c>
       <c r="I4" s="14">
         <f>IFERROR(H4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.2833910703786927E-4</v>
+        <v>2.5371011893096591E-4</v>
       </c>
       <c r="J4" s="14">
         <f>IFERROR(I4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.2895268799876859E-4</v>
+        <v>2.5439187555418739E-4</v>
       </c>
       <c r="K4" s="14">
         <f>IFERROR(J4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.2956791774248248E-4</v>
+        <v>2.5507546415831395E-4</v>
       </c>
       <c r="L4" s="14">
         <f>IFERROR(K4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.3018480069953429E-4</v>
+        <v>2.5576088966614929E-4</v>
       </c>
       <c r="M4" s="14">
         <f>IFERROR(L4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.3080334131235283E-4</v>
+        <v>2.5644815701372542E-4</v>
       </c>
       <c r="N4" s="14">
         <f>IFERROR(M4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.3142354403530438E-4</v>
+        <v>2.5713727115033824E-4</v>
       </c>
       <c r="O4" s="14">
         <f>IFERROR(N4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.3204541333472474E-4</v>
+        <v>2.5782823703858308E-4</v>
       </c>
       <c r="P4" s="14">
         <f>IFERROR(O4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.3266895368895143E-4</v>
+        <v>2.5852105965439053E-4</v>
       </c>
       <c r="Q4" s="14">
         <f>IFERROR(P4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.3329416958835596E-4</v>
+        <v>2.5921574398706226E-4</v>
       </c>
       <c r="R4" s="14">
         <f>IFERROR(Q4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.3392106553537609E-4</v>
+        <v>2.5991229503930684E-4</v>
       </c>
       <c r="S4" s="14">
         <f>IFERROR(R4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.3454964604454828E-4</v>
+        <v>2.6061071782727596E-4</v>
       </c>
       <c r="T4" s="14">
         <f>IFERROR(S4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.351799156425403E-4</v>
+        <v>2.613110173806004E-4</v>
       </c>
       <c r="U4" s="14">
         <f>IFERROR(T4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.3581187886818363E-4</v>
+        <v>2.6201319874242634E-4</v>
       </c>
       <c r="V4" s="14">
         <f>IFERROR(U4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.3644554027250637E-4</v>
+        <v>2.6271726696945158E-4</v>
       </c>
       <c r="W4" s="14">
         <f>IFERROR(V4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.3708090441876584E-4</v>
+        <v>2.634232271319621E-4</v>
       </c>
       <c r="X4" s="14">
         <f>IFERROR(W4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.3771797588248154E-4</v>
+        <v>2.6413108431386841E-4</v>
       </c>
       <c r="Y4" s="14">
         <f>IFERROR(X4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.3835675925146802E-4</v>
+        <v>2.6484084361274229E-4</v>
       </c>
       <c r="Z4" s="14">
         <f>IFERROR(Y4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.3899725912586802E-4</v>
+        <v>2.6555251013985344E-4</v>
       </c>
       <c r="AA4" s="14">
         <f>IFERROR(Z4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.3963948011818554E-4</v>
+        <v>2.6626608902020622E-4</v>
       </c>
       <c r="AB4" s="14">
         <f>IFERROR(AA4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.4028342685331904E-4</v>
+        <v>2.6698158539257676E-4</v>
       </c>
       <c r="AC4" s="14">
         <f>IFERROR(AB4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.4092910396859474E-4</v>
+        <v>2.6769900440954975E-4</v>
       </c>
       <c r="AD4" s="14">
         <f>IFERROR(AC4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.415765161138001E-4</v>
+        <v>2.6841835123755573E-4</v>
       </c>
       <c r="AE4" s="14">
         <f>IFERROR(AD4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.4222566795121722E-4</v>
+        <v>2.6913963105690806E-4</v>
       </c>
       <c r="AF4" s="14">
         <f>IFERROR(AE4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.4287656415565643E-4</v>
+        <v>2.6986284906184053E-4</v>
       </c>
       <c r="AG4" s="14"/>
     </row>
@@ -11145,127 +11145,127 @@
       </c>
       <c r="B5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$2:$H$2,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.0650137373996445E-4</v>
+        <v>2.294459708221827E-4</v>
       </c>
       <c r="C5" s="14">
         <f>IFERROR(B5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.0560788068493016E-4</v>
+        <v>2.2845320076103349E-4</v>
       </c>
       <c r="D5" s="14">
         <f>IFERROR(C5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.0471825360824232E-4</v>
+        <v>2.2746472623138035E-4</v>
       </c>
       <c r="E5" s="14">
         <f>IFERROR(D5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.0383247578253133E-4</v>
+        <v>2.2648052864725703E-4</v>
       </c>
       <c r="F5" s="14">
         <f>IFERROR(E5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.0295053055280381E-4</v>
+        <v>2.2550058950311536E-4</v>
       </c>
       <c r="G5" s="14">
         <f>IFERROR(F5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.0207240133612945E-4</v>
+        <v>2.2452489037347716E-4</v>
       </c>
       <c r="H5" s="14">
         <f>IFERROR(G5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.0119807162132913E-4</v>
+        <v>2.2355341291258792E-4</v>
       </c>
       <c r="I5" s="14">
         <f>IFERROR(H5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.003275249686646E-4</v>
+        <v>2.2258613885407178E-4</v>
       </c>
       <c r="J5" s="14">
         <f>IFERROR(I5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.9946074500952929E-4</v>
+        <v>2.2162305001058809E-4</v>
       </c>
       <c r="K5" s="14">
         <f>IFERROR(J5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.9859771544614052E-4</v>
+        <v>2.2066412827348946E-4</v>
       </c>
       <c r="L5" s="14">
         <f>IFERROR(K5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.9773842005123312E-4</v>
+        <v>2.1970935561248123E-4</v>
       </c>
       <c r="M5" s="14">
         <f>IFERROR(L5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.9688284266775424E-4</v>
+        <v>2.1875871407528249E-4</v>
       </c>
       <c r="N5" s="14">
         <f>IFERROR(M5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.9603096720855964E-4</v>
+        <v>2.1781218578728847E-4</v>
       </c>
       <c r="O5" s="14">
         <f>IFERROR(N5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.9518277765611113E-4</v>
+        <v>2.1686975295123455E-4</v>
       </c>
       <c r="P5" s="14">
         <f>IFERROR(O5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.9433825806217542E-4</v>
+        <v>2.1593139784686154E-4</v>
       </c>
       <c r="Q5" s="14">
         <f>IFERROR(P5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.9349739254752432E-4</v>
+        <v>2.1499710283058251E-4</v>
       </c>
       <c r="R5" s="14">
         <f>IFERROR(Q5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.9266016530163603E-4</v>
+        <v>2.1406685033515107E-4</v>
       </c>
       <c r="S5" s="14">
         <f>IFERROR(R5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.91826560582398E-4</v>
+        <v>2.1314062286933102E-4</v>
       </c>
       <c r="T5" s="14">
         <f>IFERROR(S5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.9099656271581082E-4</v>
+        <v>2.122184030175675E-4</v>
       </c>
       <c r="U5" s="14">
         <f>IFERROR(T5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.9017015609569364E-4</v>
+        <v>2.1130017343965951E-4</v>
       </c>
       <c r="V5" s="14">
         <f>IFERROR(U5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.8934732518339058E-4</v>
+        <v>2.1038591687043388E-4</v>
       </c>
       <c r="W5" s="14">
         <f>IFERROR(V5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.8852805450747864E-4</v>
+        <v>2.0947561611942063E-4</v>
       </c>
       <c r="X5" s="14">
         <f>IFERROR(W5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.8771232866347687E-4</v>
+        <v>2.0856925407052975E-4</v>
       </c>
       <c r="Y5" s="14">
         <f>IFERROR(X5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.8690013231355653E-4</v>
+        <v>2.0766681368172938E-4</v>
       </c>
       <c r="Z5" s="14">
         <f>IFERROR(Y5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.860914501862529E-4</v>
+        <v>2.0676827798472535E-4</v>
       </c>
       <c r="AA5" s="14">
         <f>IFERROR(Z5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.8528626707617804E-4</v>
+        <v>2.0587363008464215E-4</v>
       </c>
       <c r="AB5" s="14">
         <f>IFERROR(AA5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.8448456784373485E-4</v>
+        <v>2.0498285315970525E-4</v>
       </c>
       <c r="AC5" s="14">
         <f>IFERROR(AB5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.8368633741483247E-4</v>
+        <v>2.0409593046092484E-4</v>
       </c>
       <c r="AD5" s="14">
         <f>IFERROR(AC5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.8289156078060286E-4</v>
+        <v>2.0321284531178084E-4</v>
       </c>
       <c r="AE5" s="14">
         <f>IFERROR(AD5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.8210022299711853E-4</v>
+        <v>2.0233358110790937E-4</v>
       </c>
       <c r="AF5" s="14">
         <f>IFERROR(AE5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.8131230918511161E-4</v>
+        <v>2.0145812131679055E-4</v>
       </c>
       <c r="AG5" s="14"/>
     </row>
@@ -11275,127 +11275,127 @@
       </c>
       <c r="B6" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$2:$H$2,,MATCH($A6,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5562553524211392E-4</v>
+        <v>2.8402837249123764E-4</v>
       </c>
       <c r="C6" s="14">
         <f>IFERROR(B6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5608543131443894E-4</v>
+        <v>2.8453936812715435E-4</v>
       </c>
       <c r="D6" s="14">
         <f>IFERROR(C6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5654615478609688E-4</v>
+        <v>2.8505128309566321E-4</v>
       </c>
       <c r="E6" s="14">
         <f>IFERROR(D6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5700770714566246E-4</v>
+        <v>2.855641190507361E-4</v>
       </c>
       <c r="F6" s="14">
         <f>IFERROR(E6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5747008988438849E-4</v>
+        <v>2.8607787764932055E-4</v>
       </c>
       <c r="G6" s="14">
         <f>IFERROR(F6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5793330449621065E-4</v>
+        <v>2.8659256055134515E-4</v>
       </c>
       <c r="H6" s="14">
         <f>IFERROR(G6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5839735247775233E-4</v>
+        <v>2.8710816941972483E-4</v>
       </c>
       <c r="I6" s="14">
         <f>IFERROR(H6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5886223532832963E-4</v>
+        <v>2.8762470592036627E-4</v>
       </c>
       <c r="J6" s="14">
         <f>IFERROR(I6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5932795454995596E-4</v>
+        <v>2.8814217172217334E-4</v>
       </c>
       <c r="K6" s="14">
         <f>IFERROR(J6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5979451164734704E-4</v>
+        <v>2.8866056849705232E-4</v>
       </c>
       <c r="L6" s="14">
         <f>IFERROR(K6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.6026190812792574E-4</v>
+        <v>2.8917989791991754E-4</v>
       </c>
       <c r="M6" s="14">
         <f>IFERROR(L6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.6073014550182693E-4</v>
+        <v>2.897001616686966E-4</v>
       </c>
       <c r="N6" s="14">
         <f>IFERROR(M6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.6119922528190234E-4</v>
+        <v>2.9022136142433589E-4</v>
       </c>
       <c r="O6" s="14">
         <f>IFERROR(N6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.6166914898372544E-4</v>
+        <v>2.9074349887080598E-4</v>
       </c>
       <c r="P6" s="14">
         <f>IFERROR(O6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.6213991812559643E-4</v>
+        <v>2.9126657569510708E-4</v>
       </c>
       <c r="Q6" s="14">
         <f>IFERROR(P6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.6261153422854708E-4</v>
+        <v>2.9179059358727449E-4</v>
       </c>
       <c r="R6" s="14">
         <f>IFERROR(Q6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.6308399881634566E-4</v>
+        <v>2.9231555424038402E-4</v>
       </c>
       <c r="S6" s="14">
         <f>IFERROR(R6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.6355731341550181E-4</v>
+        <v>2.9284145935055755E-4</v>
       </c>
       <c r="T6" s="14">
         <f>IFERROR(S6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.6403147955527154E-4</v>
+        <v>2.9336831061696836E-4</v>
       </c>
       <c r="U6" s="14">
         <f>IFERROR(T6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.6450649876766212E-4</v>
+        <v>2.9389610974184683E-4</v>
       </c>
       <c r="V6" s="14">
         <f>IFERROR(U6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.6498237258743712E-4</v>
+        <v>2.9442485843048571E-4</v>
       </c>
       <c r="W6" s="14">
         <f>IFERROR(V6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.6545910255212121E-4</v>
+        <v>2.9495455839124583E-4</v>
       </c>
       <c r="X6" s="14">
         <f>IFERROR(W6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.6593669020200529E-4</v>
+        <v>2.9548521133556153E-4</v>
       </c>
       <c r="Y6" s="14">
         <f>IFERROR(X6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.6641513708015142E-4</v>
+        <v>2.9601681897794608E-4</v>
       </c>
       <c r="Z6" s="14">
         <f>IFERROR(Y6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.6689444473239771E-4</v>
+        <v>2.9654938303599752E-4</v>
       </c>
       <c r="AA6" s="14">
         <f>IFERROR(Z6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.6737461470736343E-4</v>
+        <v>2.9708290523040382E-4</v>
       </c>
       <c r="AB6" s="14">
         <f>IFERROR(AA6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.6785564855645393E-4</v>
+        <v>2.9761738728494881E-4</v>
       </c>
       <c r="AC6" s="14">
         <f>IFERROR(AB6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.6833754783386573E-4</v>
+        <v>2.9815283092651752E-4</v>
       </c>
       <c r="AD6" s="14">
         <f>IFERROR(AC6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.6882031409659153E-4</v>
+        <v>2.9868923788510179E-4</v>
       </c>
       <c r="AE6" s="14">
         <f>IFERROR(AD6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.6930394890442523E-4</v>
+        <v>2.9922660989380591E-4</v>
       </c>
       <c r="AF6" s="14">
         <f>IFERROR(AE6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.6978845381996688E-4</v>
+        <v>2.9976494868885214E-4</v>
       </c>
       <c r="AG6" s="14"/>
     </row>
@@ -11405,127 +11405,127 @@
       </c>
       <c r="B7" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$2:$H$2,,MATCH($A7,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.1840083851069807E-4</v>
+        <v>2.4266759834522006E-4</v>
       </c>
       <c r="C7" s="14">
         <f>IFERROR(B7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.1840083851069807E-4</v>
+        <v>2.4266759834522006E-4</v>
       </c>
       <c r="D7" s="14">
         <f>IFERROR(C7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.1840083851069807E-4</v>
+        <v>2.4266759834522006E-4</v>
       </c>
       <c r="E7" s="14">
         <f>IFERROR(D7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.1840083851069807E-4</v>
+        <v>2.4266759834522006E-4</v>
       </c>
       <c r="F7" s="14">
         <f>IFERROR(E7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.1840083851069807E-4</v>
+        <v>2.4266759834522006E-4</v>
       </c>
       <c r="G7" s="14">
         <f>IFERROR(F7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.1840083851069807E-4</v>
+        <v>2.4266759834522006E-4</v>
       </c>
       <c r="H7" s="14">
         <f>IFERROR(G7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.1840083851069807E-4</v>
+        <v>2.4266759834522006E-4</v>
       </c>
       <c r="I7" s="14">
         <f>IFERROR(H7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.1840083851069807E-4</v>
+        <v>2.4266759834522006E-4</v>
       </c>
       <c r="J7" s="14">
         <f>IFERROR(I7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.1840083851069807E-4</v>
+        <v>2.4266759834522006E-4</v>
       </c>
       <c r="K7" s="14">
         <f>IFERROR(J7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.1840083851069807E-4</v>
+        <v>2.4266759834522006E-4</v>
       </c>
       <c r="L7" s="14">
         <f>IFERROR(K7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.1840083851069807E-4</v>
+        <v>2.4266759834522006E-4</v>
       </c>
       <c r="M7" s="14">
         <f>IFERROR(L7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.1840083851069807E-4</v>
+        <v>2.4266759834522006E-4</v>
       </c>
       <c r="N7" s="14">
         <f>IFERROR(M7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.1840083851069807E-4</v>
+        <v>2.4266759834522006E-4</v>
       </c>
       <c r="O7" s="14">
         <f>IFERROR(N7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.1840083851069807E-4</v>
+        <v>2.4266759834522006E-4</v>
       </c>
       <c r="P7" s="14">
         <f>IFERROR(O7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.1840083851069807E-4</v>
+        <v>2.4266759834522006E-4</v>
       </c>
       <c r="Q7" s="14">
         <f>IFERROR(P7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.1840083851069807E-4</v>
+        <v>2.4266759834522006E-4</v>
       </c>
       <c r="R7" s="14">
         <f>IFERROR(Q7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.1840083851069807E-4</v>
+        <v>2.4266759834522006E-4</v>
       </c>
       <c r="S7" s="14">
         <f>IFERROR(R7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.1840083851069807E-4</v>
+        <v>2.4266759834522006E-4</v>
       </c>
       <c r="T7" s="14">
         <f>IFERROR(S7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.1840083851069807E-4</v>
+        <v>2.4266759834522006E-4</v>
       </c>
       <c r="U7" s="14">
         <f>IFERROR(T7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.1840083851069807E-4</v>
+        <v>2.4266759834522006E-4</v>
       </c>
       <c r="V7" s="14">
         <f>IFERROR(U7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.1840083851069807E-4</v>
+        <v>2.4266759834522006E-4</v>
       </c>
       <c r="W7" s="14">
         <f>IFERROR(V7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.1840083851069807E-4</v>
+        <v>2.4266759834522006E-4</v>
       </c>
       <c r="X7" s="14">
         <f>IFERROR(W7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.1840083851069807E-4</v>
+        <v>2.4266759834522006E-4</v>
       </c>
       <c r="Y7" s="14">
         <f>IFERROR(X7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.1840083851069807E-4</v>
+        <v>2.4266759834522006E-4</v>
       </c>
       <c r="Z7" s="14">
         <f>IFERROR(Y7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.1840083851069807E-4</v>
+        <v>2.4266759834522006E-4</v>
       </c>
       <c r="AA7" s="14">
         <f>IFERROR(Z7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.1840083851069807E-4</v>
+        <v>2.4266759834522006E-4</v>
       </c>
       <c r="AB7" s="14">
         <f>IFERROR(AA7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.1840083851069807E-4</v>
+        <v>2.4266759834522006E-4</v>
       </c>
       <c r="AC7" s="14">
         <f>IFERROR(AB7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.1840083851069807E-4</v>
+        <v>2.4266759834522006E-4</v>
       </c>
       <c r="AD7" s="14">
         <f>IFERROR(AC7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.1840083851069807E-4</v>
+        <v>2.4266759834522006E-4</v>
       </c>
       <c r="AE7" s="14">
         <f>IFERROR(AD7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.1840083851069807E-4</v>
+        <v>2.4266759834522006E-4</v>
       </c>
       <c r="AF7" s="14">
         <f>IFERROR(AE7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.1840083851069807E-4</v>
+        <v>2.4266759834522006E-4</v>
       </c>
       <c r="AG7" s="14"/>
     </row>
@@ -11535,127 +11535,127 @@
       </c>
       <c r="B8" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$2:$H$2,,MATCH($A8,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.1485676289530171E-3</v>
+        <v>1.2761862543922413E-3</v>
       </c>
       <c r="C8" s="14">
         <f>IFERROR(B8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.177064881709035E-3</v>
+        <v>1.3078498685655945E-3</v>
       </c>
       <c r="D8" s="14">
         <f>IFERROR(C8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.206269183309343E-3</v>
+        <v>1.3402990925659368E-3</v>
       </c>
       <c r="E8" s="14">
         <f>IFERROR(D8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.2361980764298086E-3</v>
+        <v>1.3735534182553431E-3</v>
       </c>
       <c r="F8" s="14">
         <f>IFERROR(E8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.2668695389997887E-3</v>
+        <v>1.4076328211108766E-3</v>
       </c>
       <c r="G8" s="14">
         <f>IFERROR(F8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.2983019950012571E-3</v>
+        <v>1.4425577722236194E-3</v>
       </c>
       <c r="H8" s="14">
         <f>IFERROR(G8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.3305143255358716E-3</v>
+        <v>1.4783492505954132E-3</v>
       </c>
       <c r="I8" s="14">
         <f>IFERROR(H8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.3635258801666258E-3</v>
+        <v>1.5150287557406956E-3</v>
       </c>
       <c r="J8" s="14">
         <f>IFERROR(I8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.3973564885409015E-3</v>
+        <v>1.5526183206010021E-3</v>
       </c>
       <c r="K8" s="14">
         <f>IFERROR(J8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.4320264723019017E-3</v>
+        <v>1.5911405247798912E-3</v>
       </c>
       <c r="L8" s="14">
         <f>IFERROR(K8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.4675566572956188E-3</v>
+        <v>1.6306185081062436E-3</v>
       </c>
       <c r="M8" s="14">
         <f>IFERROR(L8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.5039683860806729E-3</v>
+        <v>1.6710759845340814E-3</v>
       </c>
       <c r="N8" s="14">
         <f>IFERROR(M8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.5412835307485316E-3</v>
+        <v>1.7125372563872576E-3</v>
       </c>
       <c r="O8" s="14">
         <f>IFERROR(N8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.5795245060618148E-3</v>
+        <v>1.7550272289575722E-3</v>
       </c>
       <c r="P8" s="14">
         <f>IFERROR(O8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.6187142829185758E-3</v>
+        <v>1.7985714254650845E-3</v>
       </c>
       <c r="Q8" s="14">
         <f>IFERROR(P8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.6588764021506456E-3</v>
+        <v>1.8431960023896066E-3</v>
       </c>
       <c r="R8" s="14">
         <f>IFERROR(Q8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.7000349886643303E-3</v>
+        <v>1.8889277651825895E-3</v>
       </c>
       <c r="S8" s="14">
         <f>IFERROR(R8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.7422147659319543E-3</v>
+        <v>1.9357941843688384E-3</v>
       </c>
       <c r="T8" s="14">
         <f>IFERROR(S8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.7854410708429559E-3</v>
+        <v>1.9838234120477293E-3</v>
       </c>
       <c r="U8" s="14">
         <f>IFERROR(T8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.8297398689234546E-3</v>
+        <v>2.0330442988038388E-3</v>
       </c>
       <c r="V8" s="14">
         <f>IFERROR(U8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.875137769933433E-3</v>
+        <v>2.0834864110371482E-3</v>
       </c>
       <c r="W8" s="14">
         <f>IFERROR(V8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.9216620438509025E-3</v>
+        <v>2.1351800487232255E-3</v>
       </c>
       <c r="X8" s="14">
         <f>IFERROR(W8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.9693406372526543E-3</v>
+        <v>2.1881562636140608E-3</v>
       </c>
       <c r="Y8" s="14">
         <f>IFERROR(X8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.0182021901014344E-3</v>
+        <v>2.2424468778904833E-3</v>
       </c>
       <c r="Z8" s="14">
         <f>IFERROR(Y8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.068276052949629E-3</v>
+        <v>2.2980845032773661E-3</v>
       </c>
       <c r="AA8" s="14">
         <f>IFERROR(Z8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.11959230456979E-3</v>
+        <v>2.3551025606331003E-3</v>
       </c>
       <c r="AB8" s="14">
         <f>IFERROR(AA8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.1721817700225956E-3</v>
+        <v>2.4135353000251064E-3</v>
       </c>
       <c r="AC8" s="14">
         <f>IFERROR(AB8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.2260760391730979E-3</v>
+        <v>2.4734178213034422E-3</v>
       </c>
       <c r="AD8" s="14">
         <f>IFERROR(AC8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.2813074856663767E-3</v>
+        <v>2.5347860951848633E-3</v>
       </c>
       <c r="AE8" s="14">
         <f>IFERROR(AD8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.3379092863740035E-3</v>
+        <v>2.5976769848600045E-3</v>
       </c>
       <c r="AF8" s="14">
         <f>IFERROR(AE8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.3959154413229922E-3</v>
+        <v>2.6621282681366584E-3</v>
       </c>
       <c r="AG8" s="14"/>
     </row>
@@ -11782,127 +11782,127 @@
       </c>
       <c r="B2" s="14">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$2:$H$2,,MATCH($A2,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.5456701824154734E-4</v>
+        <v>1.7174113137949704E-4</v>
       </c>
       <c r="C2" s="14">
         <f>IFERROR(B2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.5680870539743974E-4</v>
+        <v>1.7423189488604415E-4</v>
       </c>
       <c r="D2" s="14">
         <f>IFERROR(C2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.5908290376666898E-4</v>
+        <v>1.7675878196296555E-4</v>
       </c>
       <c r="E2" s="14">
         <f>IFERROR(D2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.6139008485971767E-4</v>
+        <v>1.793223165107974E-4</v>
       </c>
       <c r="F2" s="14">
         <f>IFERROR(E2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.6373072702539001E-4</v>
+        <v>1.8192303002821113E-4</v>
       </c>
       <c r="G2" s="14">
         <f>IFERROR(F2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.6610531554998823E-4</v>
+        <v>1.8456146172220916E-4</v>
       </c>
       <c r="H2" s="14">
         <f>IFERROR(G2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.6851434275792706E-4</v>
+        <v>1.8723815861991896E-4</v>
       </c>
       <c r="I2" s="14">
         <f>IFERROR(H2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.7095830811380758E-4</v>
+        <v>1.8995367568200842E-4</v>
       </c>
       <c r="J2" s="14">
         <f>IFERROR(I2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.7343771832597149E-4</v>
+        <v>1.927085759177461E-4</v>
       </c>
       <c r="K2" s="14">
         <f>IFERROR(J2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.7595308745155708E-4</v>
+        <v>1.955034305017301E-4</v>
       </c>
       <c r="L2" s="14">
         <f>IFERROR(K2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.7850493700307895E-4</v>
+        <v>1.9833881889230997E-4</v>
       </c>
       <c r="M2" s="14">
         <f>IFERROR(L2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.8109379605655342E-4</v>
+        <v>2.0121532895172605E-4</v>
       </c>
       <c r="N2" s="14">
         <f>IFERROR(M2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.8372020136119203E-4</v>
+        <v>2.0413355706799119E-4</v>
       </c>
       <c r="O2" s="14">
         <f>IFERROR(N2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.8638469745068601E-4</v>
+        <v>2.0709410827854006E-4</v>
       </c>
       <c r="P2" s="14">
         <f>IFERROR(O2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.890878367561047E-4</v>
+        <v>2.1009759639567193E-4</v>
       </c>
       <c r="Q2" s="14">
         <f>IFERROR(P2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.9183017972043123E-4</v>
+        <v>2.1314464413381252E-4</v>
       </c>
       <c r="R2" s="14">
         <f>IFERROR(Q2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.9461229491475948E-4</v>
+        <v>2.162358832386217E-4</v>
       </c>
       <c r="S2" s="14">
         <f>IFERROR(R2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.9743475915617612E-4</v>
+        <v>2.1937195461797353E-4</v>
       </c>
       <c r="T2" s="14">
         <f>IFERROR(S2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>2.0029815762735232E-4</v>
+        <v>2.2255350847483598E-4</v>
       </c>
       <c r="U2" s="14">
         <f>IFERROR(T2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>2.0320308399786994E-4</v>
+        <v>2.2578120444207775E-4</v>
       </c>
       <c r="V2" s="14">
         <f>IFERROR(U2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>2.0615014054730727E-4</v>
+        <v>2.2905571171923033E-4</v>
       </c>
       <c r="W2" s="14">
         <f>IFERROR(V2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>2.0913993829010989E-4</v>
+        <v>2.3237770921123325E-4</v>
       </c>
       <c r="X2" s="14">
         <f>IFERROR(W2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>2.1217309710227264E-4</v>
+        <v>2.3574788566919187E-4</v>
       </c>
       <c r="Y2" s="14">
         <f>IFERROR(X2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>2.1525024584985862E-4</v>
+        <v>2.3916693983317628E-4</v>
       </c>
       <c r="Z2" s="14">
         <f>IFERROR(Y2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>2.1837202251938234E-4</v>
+        <v>2.4263558057709153E-4</v>
       </c>
       <c r="AA2" s="14">
         <f>IFERROR(Z2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>2.2153907435008371E-4</v>
+        <v>2.4615452705564858E-4</v>
       </c>
       <c r="AB2" s="14">
         <f>IFERROR(AA2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>2.2475205796812042E-4</v>
+        <v>2.4972450885346717E-4</v>
       </c>
       <c r="AC2" s="14">
         <f>IFERROR(AB2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>2.2801163952270652E-4</v>
+        <v>2.5334626613634061E-4</v>
       </c>
       <c r="AD2" s="14">
         <f>IFERROR(AC2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>2.3131849482422535E-4</v>
+        <v>2.5702054980469488E-4</v>
       </c>
       <c r="AE2" s="14">
         <f>IFERROR(AD2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>2.3467330948434567E-4</v>
+        <v>2.60748121649273E-4</v>
       </c>
       <c r="AF2" s="14">
         <f>IFERROR(AE2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>2.3807677905816977E-4</v>
+        <v>2.6452975450907756E-4</v>
       </c>
       <c r="AG2" s="14"/>
     </row>
@@ -11912,127 +11912,127 @@
       </c>
       <c r="B3" s="21">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$2:$H$2,,MATCH($A3,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>3.5551015298695876E-5</v>
+        <v>3.9501128109662086E-5</v>
       </c>
       <c r="C3" s="21">
         <f>IFERROR(B3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>3.5628962119972754E-5</v>
+        <v>3.9587735688858621E-5</v>
       </c>
       <c r="D3" s="21">
         <f>IFERROR(C3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>3.5707079842330686E-5</v>
+        <v>3.9674533158145217E-5</v>
       </c>
       <c r="E3" s="21">
         <f>IFERROR(D3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>3.5785368840476164E-5</v>
+        <v>3.9761520933862413E-5</v>
       </c>
       <c r="F3" s="21">
         <f>IFERROR(E3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>3.5863829489937226E-5</v>
+        <v>3.9848699433263594E-5</v>
       </c>
       <c r="G3" s="21">
         <f>IFERROR(F3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>3.5942462167065275E-5</v>
+        <v>3.9936069074516979E-5</v>
       </c>
       <c r="H3" s="21">
         <f>IFERROR(G3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>3.6021267249036872E-5</v>
+        <v>4.0023630276707642E-5</v>
       </c>
       <c r="I3" s="21">
         <f>IFERROR(H3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>3.6100245113855553E-5</v>
+        <v>4.0111383459839513E-5</v>
       </c>
       <c r="J3" s="21">
         <f>IFERROR(I3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>3.6179396140353648E-5</v>
+        <v>4.0199329044837397E-5</v>
       </c>
       <c r="K3" s="21">
         <f>IFERROR(J3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>3.6258720708194076E-5</v>
+        <v>4.0287467453548982E-5</v>
       </c>
       <c r="L3" s="21">
         <f>IFERROR(K3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>3.6338219197872191E-5</v>
+        <v>4.0375799108746885E-5</v>
       </c>
       <c r="M3" s="21">
         <f>IFERROR(L3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>3.641789199071759E-5</v>
+        <v>4.0464324434130661E-5</v>
       </c>
       <c r="N3" s="21">
         <f>IFERROR(M3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>3.6497739468895947E-5</v>
+        <v>4.0553043854328836E-5</v>
       </c>
       <c r="O3" s="21">
         <f>IFERROR(N3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>3.6577762015410853E-5</v>
+        <v>4.0641957794900953E-5</v>
       </c>
       <c r="P3" s="21">
         <f>IFERROR(O3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>3.6657960014105644E-5</v>
+        <v>4.0731066682339616E-5</v>
       </c>
       <c r="Q3" s="21">
         <f>IFERROR(P3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>3.6738333849665252E-5</v>
+        <v>4.0820370944072509E-5</v>
       </c>
       <c r="R3" s="21">
         <f>IFERROR(Q3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>3.681888390761803E-5</v>
+        <v>4.0909871008464488E-5</v>
       </c>
       <c r="S3" s="21">
         <f>IFERROR(R3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>3.6899610574337631E-5</v>
+        <v>4.0999567304819601E-5</v>
       </c>
       <c r="T3" s="21">
         <f>IFERROR(S3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>3.6980514237044834E-5</v>
+        <v>4.1089460263383158E-5</v>
       </c>
       <c r="U3" s="21">
         <f>IFERROR(T3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>3.7061595283809418E-5</v>
+        <v>4.1179550315343805E-5</v>
       </c>
       <c r="V3" s="21">
         <f>IFERROR(U3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>3.7142854103552015E-5</v>
+        <v>4.126983789283558E-5</v>
       </c>
       <c r="W3" s="21">
         <f>IFERROR(V3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>3.7224291086045982E-5</v>
+        <v>4.1360323428939992E-5</v>
       </c>
       <c r="X3" s="21">
         <f>IFERROR(W3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>3.7305906621919272E-5</v>
+        <v>4.1451007357688088E-5</v>
       </c>
       <c r="Y3" s="21">
         <f>IFERROR(X3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>3.7387701102656291E-5</v>
+        <v>4.154189011406255E-5</v>
       </c>
       <c r="Z3" s="21">
         <f>IFERROR(Y3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>3.7469674920599799E-5</v>
+        <v>4.1632972133999782E-5</v>
       </c>
       <c r="AA3" s="21">
         <f>IFERROR(Z3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>3.7551828468952769E-5</v>
+        <v>4.1724253854391977E-5</v>
       </c>
       <c r="AB3" s="21">
         <f>IFERROR(AA3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>3.7634162141780301E-5</v>
+        <v>4.1815735713089238E-5</v>
       </c>
       <c r="AC3" s="21">
         <f>IFERROR(AB3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>3.7716676334011483E-5</v>
+        <v>4.1907418148901664E-5</v>
       </c>
       <c r="AD3" s="21">
         <f>IFERROR(AC3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>3.7799371441441307E-5</v>
+        <v>4.199930160160147E-5</v>
       </c>
       <c r="AE3" s="21">
         <f>IFERROR(AD3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>3.7882247860732556E-5</v>
+        <v>4.209138651192508E-5</v>
       </c>
       <c r="AF3" s="21">
         <f>IFERROR(AE3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>3.7965305989417709E-5</v>
+        <v>4.2183673321575252E-5</v>
       </c>
       <c r="AG3" s="14"/>
     </row>
@@ -12042,127 +12042,127 @@
       </c>
       <c r="B4" s="14">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$2:$H$2,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>4.7251632385280506E-5</v>
+        <v>5.250181376142278E-5</v>
       </c>
       <c r="C4" s="14">
         <f>IFERROR(B4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>4.7355233211125592E-5</v>
+        <v>5.2616925790139543E-5</v>
       </c>
       <c r="D4" s="14">
         <f>IFERROR(C4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>4.7459061185337281E-5</v>
+        <v>5.2732290205930314E-5</v>
       </c>
       <c r="E4" s="14">
         <f>IFERROR(D4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>4.7563116805946173E-5</v>
+        <v>5.284790756216241E-5</v>
       </c>
       <c r="F4" s="14">
         <f>IFERROR(E4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>4.7667400572074801E-5</v>
+        <v>5.2963778413416435E-5</v>
       </c>
       <c r="G4" s="14">
         <f>IFERROR(F4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>4.7771912983940043E-5</v>
+        <v>5.3079903315488929E-5</v>
       </c>
       <c r="H4" s="14">
         <f>IFERROR(G4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>4.7876654542855531E-5</v>
+        <v>5.3196282825395025E-5</v>
       </c>
       <c r="I4" s="14">
         <f>IFERROR(H4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>4.7981625751234032E-5</v>
+        <v>5.3312917501371143E-5</v>
       </c>
       <c r="J4" s="14">
         <f>IFERROR(I4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>4.8086827112589885E-5</v>
+        <v>5.3429807902877647E-5</v>
       </c>
       <c r="K4" s="14">
         <f>IFERROR(J4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>4.8192259131541388E-5</v>
+        <v>5.3546954590601537E-5</v>
       </c>
       <c r="L4" s="14">
         <f>IFERROR(K4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>4.8297922313813236E-5</v>
+        <v>5.3664358126459145E-5</v>
       </c>
       <c r="M4" s="14">
         <f>IFERROR(L4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>4.8403817166238943E-5</v>
+        <v>5.3782019073598814E-5</v>
       </c>
       <c r="N4" s="14">
         <f>IFERROR(M4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>4.8509944196763268E-5</v>
+        <v>5.3899937996403619E-5</v>
       </c>
       <c r="O4" s="14">
         <f>IFERROR(N4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>4.8616303914444666E-5</v>
+        <v>5.4018115460494061E-5</v>
       </c>
       <c r="P4" s="14">
         <f>IFERROR(O4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>4.8722896829457721E-5</v>
+        <v>5.4136552032730784E-5</v>
       </c>
       <c r="Q4" s="14">
         <f>IFERROR(P4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>4.8829723453095576E-5</v>
+        <v>5.425524828121729E-5</v>
       </c>
       <c r="R4" s="14">
         <f>IFERROR(Q4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>4.8936784297772418E-5</v>
+        <v>5.437420477530267E-5</v>
       </c>
       <c r="S4" s="14">
         <f>IFERROR(R4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>4.9044079877025919E-5</v>
+        <v>5.4493422085584334E-5</v>
       </c>
       <c r="T4" s="14">
         <f>IFERROR(S4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>4.9151610705519688E-5</v>
+        <v>5.4612900783910744E-5</v>
       </c>
       <c r="U4" s="14">
         <f>IFERROR(T4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>4.9259377299045763E-5</v>
+        <v>5.4732641443384164E-5</v>
       </c>
       <c r="V4" s="14">
         <f>IFERROR(U4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>4.9367380174527069E-5</v>
+        <v>5.485264463836339E-5</v>
       </c>
       <c r="W4" s="14">
         <f>IFERROR(V4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>4.94756198500199E-5</v>
+        <v>5.4972910944466535E-5</v>
       </c>
       <c r="X4" s="14">
         <f>IFERROR(W4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>4.9584096844716415E-5</v>
+        <v>5.5093440938573769E-5</v>
       </c>
       <c r="Y4" s="14">
         <f>IFERROR(X4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>4.9692811678947109E-5</v>
+        <v>5.5214235198830095E-5</v>
       </c>
       <c r="Z4" s="14">
         <f>IFERROR(Y4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>4.9801764874183324E-5</v>
+        <v>5.5335294304648107E-5</v>
       </c>
       <c r="AA4" s="14">
         <f>IFERROR(Z4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>4.9910956953039747E-5</v>
+        <v>5.5456618836710797E-5</v>
       </c>
       <c r="AB4" s="14">
         <f>IFERROR(AA4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>5.0020388439276911E-5</v>
+        <v>5.5578209376974318E-5</v>
       </c>
       <c r="AC4" s="14">
         <f>IFERROR(AB4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>5.0130059857803721E-5</v>
+        <v>5.5700066508670775E-5</v>
       </c>
       <c r="AD4" s="14">
         <f>IFERROR(AC4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>5.0239971734679957E-5</v>
+        <v>5.5822190816311037E-5</v>
       </c>
       <c r="AE4" s="14">
         <f>IFERROR(AD4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>5.03501245971188E-5</v>
+        <v>5.594458288568753E-5</v>
       </c>
       <c r="AF4" s="14">
         <f>IFERROR(AE4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>5.0460518973489374E-5</v>
+        <v>5.6067243303877056E-5</v>
       </c>
       <c r="AG4" s="14"/>
     </row>
@@ -12172,127 +12172,127 @@
       </c>
       <c r="B5" s="14">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$2:$H$2,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>4.569856582360258E-5</v>
+        <v>5.0776184248447306E-5</v>
       </c>
       <c r="C5" s="14">
         <f>IFERROR(B5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>4.6138560144644872E-5</v>
+        <v>5.1265066827383191E-5</v>
       </c>
       <c r="D5" s="14">
         <f>IFERROR(C5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>4.6582790813131785E-5</v>
+        <v>5.1758656459035312E-5</v>
       </c>
       <c r="E5" s="14">
         <f>IFERROR(D5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>4.7031298617407193E-5</v>
+        <v>5.2256998463785761E-5</v>
       </c>
       <c r="F5" s="14">
         <f>IFERROR(E5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>4.7484124738532764E-5</v>
+        <v>5.2760138598369723E-5</v>
       </c>
       <c r="G5" s="14">
         <f>IFERROR(F5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>4.7941310754069111E-5</v>
+        <v>5.3268123060076776E-5</v>
       </c>
       <c r="H5" s="14">
         <f>IFERROR(G5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>4.8402898641893363E-5</v>
+        <v>5.3780998490992609E-5</v>
       </c>
       <c r="I5" s="14">
         <f>IFERROR(H5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>4.8868930784053484E-5</v>
+        <v>5.4298811982281631E-5</v>
       </c>
       <c r="J5" s="14">
         <f>IFERROR(I5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>4.9339449970659708E-5</v>
+        <v>5.4821611078510766E-5</v>
       </c>
       <c r="K5" s="14">
         <f>IFERROR(J5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>4.9814499403813436E-5</v>
+        <v>5.5349443782014908E-5</v>
       </c>
       <c r="L5" s="14">
         <f>IFERROR(K5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>5.0294122701573962E-5</v>
+        <v>5.5882358557304376E-5</v>
       </c>
       <c r="M5" s="14">
         <f>IFERROR(L5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>5.0778363901963393E-5</v>
+        <v>5.6420404335514857E-5</v>
       </c>
       <c r="N5" s="14">
         <f>IFERROR(M5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>5.1267267467010144E-5</v>
+        <v>5.6963630518900135E-5</v>
       </c>
       <c r="O5" s="14">
         <f>IFERROR(N5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>5.176087828683133E-5</v>
+        <v>5.7512086985368115E-5</v>
       </c>
       <c r="P5" s="14">
         <f>IFERROR(O5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>5.2259241683754487E-5</v>
+        <v>5.8065824093060516E-5</v>
       </c>
       <c r="Q5" s="14">
         <f>IFERROR(P5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>5.2762403416478988E-5</v>
+        <v>5.8624892684976632E-5</v>
       </c>
       <c r="R5" s="14">
         <f>IFERROR(Q5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>5.3270409684277507E-5</v>
+        <v>5.9189344093641654E-5</v>
       </c>
       <c r="S5" s="14">
         <f>IFERROR(R5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>5.3783307131237926E-5</v>
+        <v>5.9759230145819897E-5</v>
       </c>
       <c r="T5" s="14">
         <f>IFERROR(S5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>5.4301142850546124E-5</v>
+        <v>6.0334603167273447E-5</v>
       </c>
       <c r="U5" s="14">
         <f>IFERROR(T5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>5.4823964388809953E-5</v>
+        <v>6.0915515987566587E-5</v>
       </c>
       <c r="V5" s="14">
         <f>IFERROR(U5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>5.5351819750424882E-5</v>
+        <v>6.1502021944916501E-5</v>
       </c>
       <c r="W5" s="14">
         <f>IFERROR(V5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>5.5884757401981664E-5</v>
+        <v>6.2094174891090697E-5</v>
       </c>
       <c r="X5" s="14">
         <f>IFERROR(W5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>5.6422826276716423E-5</v>
+        <v>6.2692029196351542E-5</v>
       </c>
       <c r="Y5" s="14">
         <f>IFERROR(X5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>5.6966075779003626E-5</v>
+        <v>6.3295639754448429E-5</v>
       </c>
       <c r="Z5" s="14">
         <f>IFERROR(Y5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>5.7514555788892277E-5</v>
+        <v>6.3905061987658041E-5</v>
       </c>
       <c r="AA5" s="14">
         <f>IFERROR(Z5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>5.8068316666685787E-5</v>
+        <v>6.4520351851873048E-5</v>
       </c>
       <c r="AB5" s="14">
         <f>IFERROR(AA5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>5.8627409257565987E-5</v>
+        <v>6.5141565841739937E-5</v>
       </c>
       <c r="AC5" s="14">
         <f>IFERROR(AB5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>5.9191884896261595E-5</v>
+        <v>6.576876099584617E-5</v>
       </c>
       <c r="AD5" s="14">
         <f>IFERROR(AC5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>5.976179541176169E-5</v>
+        <v>6.6401994901957385E-5</v>
       </c>
       <c r="AE5" s="14">
         <f>IFERROR(AD5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>6.0337193132074517E-5</v>
+        <v>6.7041325702304967E-5</v>
       </c>
       <c r="AF5" s="14">
         <f>IFERROR(AE5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>6.0918130889032159E-5</v>
+        <v>6.7686812098924568E-5</v>
       </c>
       <c r="AG5" s="14"/>
     </row>
@@ -12302,127 +12302,127 @@
       </c>
       <c r="B6" s="15">
         <f>B5*Calibration!$C$21</f>
-        <v>7.826150109436674E-5</v>
+        <v>8.6957223438185259E-5</v>
       </c>
       <c r="C6" s="15">
         <f>B6*(1+CAGR!$C$13)</f>
-        <v>7.8433092121723064E-5</v>
+        <v>8.7147880135247829E-5</v>
       </c>
       <c r="D6" s="15">
         <f>C6*(1+CAGR!$C$13)</f>
-        <v>7.8605059368296463E-5</v>
+        <v>8.7338954853662714E-5</v>
       </c>
       <c r="E6" s="15">
         <f>D6*(1+CAGR!$C$13)</f>
-        <v>7.8777403658960486E-5</v>
+        <v>8.7530448509956073E-5</v>
       </c>
       <c r="F6" s="15">
         <f>E6*(1+CAGR!$C$13)</f>
-        <v>7.8950125820397241E-5</v>
+        <v>8.7722362022663581E-5</v>
       </c>
       <c r="G6" s="15">
         <f>F6*(1+CAGR!$C$13)</f>
-        <v>7.9123226681101374E-5</v>
+        <v>8.7914696312334844E-5</v>
       </c>
       <c r="H6" s="15">
         <f>G6*(1+CAGR!$C$13)</f>
-        <v>7.9296707071384022E-5</v>
+        <v>8.8107452301537792E-5</v>
       </c>
       <c r="I6" s="15">
         <f>H6*(1+CAGR!$C$13)</f>
-        <v>7.9470567823376815E-5</v>
+        <v>8.8300630914863124E-5</v>
       </c>
       <c r="J6" s="15">
         <f>I6*(1+CAGR!$C$13)</f>
-        <v>7.9644809771035869E-5</v>
+        <v>8.8494233078928726E-5</v>
       </c>
       <c r="K6" s="15">
         <f>J6*(1+CAGR!$C$13)</f>
-        <v>7.9819433750145748E-5</v>
+        <v>8.8688259722384145E-5</v>
       </c>
       <c r="L6" s="15">
         <f>K6*(1+CAGR!$C$13)</f>
-        <v>7.9994440598323525E-5</v>
+        <v>8.8882711775915016E-5</v>
       </c>
       <c r="M6" s="15">
         <f>L6*(1+CAGR!$C$13)</f>
-        <v>8.0169831155022775E-5</v>
+        <v>8.9077590172247526E-5</v>
       </c>
       <c r="N6" s="15">
         <f>M6*(1+CAGR!$C$13)</f>
-        <v>8.0345606261537613E-5</v>
+        <v>8.9272895846152897E-5</v>
       </c>
       <c r="O6" s="15">
         <f>N6*(1+CAGR!$C$13)</f>
-        <v>8.0521766761006695E-5</v>
+        <v>8.9468629734451872E-5</v>
       </c>
       <c r="P6" s="15">
         <f>O6*(1+CAGR!$C$13)</f>
-        <v>8.0698313498417295E-5</v>
+        <v>8.9664792776019217E-5</v>
       </c>
       <c r="Q6" s="15">
         <f>P6*(1+CAGR!$C$13)</f>
-        <v>8.0875247320609373E-5</v>
+        <v>8.9861385911788188E-5</v>
       </c>
       <c r="R6" s="15">
         <f>Q6*(1+CAGR!$C$13)</f>
-        <v>8.1052569076279585E-5</v>
+        <v>9.0058410084755091E-5</v>
       </c>
       <c r="S6" s="15">
         <f>R6*(1+CAGR!$C$13)</f>
-        <v>8.1230279615985402E-5</v>
+        <v>9.0255866239983778E-5</v>
       </c>
       <c r="T6" s="15">
         <f>S6*(1+CAGR!$C$13)</f>
-        <v>8.1408379792149177E-5</v>
+        <v>9.0453755324610186E-5</v>
       </c>
       <c r="U6" s="15">
         <f>T6*(1+CAGR!$C$13)</f>
-        <v>8.1586870459062199E-5</v>
+        <v>9.065207828784688E-5</v>
       </c>
       <c r="V6" s="15">
         <f>U6*(1+CAGR!$C$13)</f>
-        <v>8.176575247288885E-5</v>
+        <v>9.0850836080987605E-5</v>
       </c>
       <c r="W6" s="15">
         <f>V6*(1+CAGR!$C$13)</f>
-        <v>8.1945026691670672E-5</v>
+        <v>9.1050029657411852E-5</v>
       </c>
       <c r="X6" s="15">
         <f>W6*(1+CAGR!$C$13)</f>
-        <v>8.2124693975330491E-5</v>
+        <v>9.124965997258943E-5</v>
       </c>
       <c r="Y6" s="15">
         <f>X6*(1+CAGR!$C$13)</f>
-        <v>8.2304755185676543E-5</v>
+        <v>9.144972798408504E-5</v>
       </c>
       <c r="Z6" s="15">
         <f>Y6*(1+CAGR!$C$13)</f>
-        <v>8.2485211186406599E-5</v>
+        <v>9.1650234651562888E-5</v>
       </c>
       <c r="AA6" s="15">
         <f>Z6*(1+CAGR!$C$13)</f>
-        <v>8.2666062843112141E-5</v>
+        <v>9.1851180936791265E-5</v>
       </c>
       <c r="AB6" s="15">
         <f>AA6*(1+CAGR!$C$13)</f>
-        <v>8.2847311023282461E-5</v>
+        <v>9.2052567803647178E-5</v>
       </c>
       <c r="AC6" s="15">
         <f>AB6*(1+CAGR!$C$13)</f>
-        <v>8.3028956596308871E-5</v>
+        <v>9.2254396218120963E-5</v>
       </c>
       <c r="AD6" s="15">
         <f>AC6*(1+CAGR!$C$13)</f>
-        <v>8.3211000433488857E-5</v>
+        <v>9.2456667148320946E-5</v>
       </c>
       <c r="AE6" s="15">
         <f>AD6*(1+CAGR!$C$13)</f>
-        <v>8.3393443408030229E-5</v>
+        <v>9.2659381564478034E-5</v>
       </c>
       <c r="AF6" s="15">
         <f>AE6*(1+CAGR!$C$13)</f>
-        <v>8.3576286395055363E-5</v>
+        <v>9.2862540438950407E-5</v>
       </c>
       <c r="AG6" s="14"/>
     </row>
@@ -12432,127 +12432,127 @@
       </c>
       <c r="B7" s="14">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$2:$H$2,,MATCH($A7,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>5.847739095406833E-5</v>
+        <v>6.4974878837853692E-5</v>
       </c>
       <c r="C7" s="14">
         <f>IFERROR(B7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>5.8605604640882574E-5</v>
+        <v>6.5117338489869523E-5</v>
       </c>
       <c r="D7" s="14">
         <f>IFERROR(C7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>5.87340994406059E-5</v>
+        <v>6.5260110489562102E-5</v>
       </c>
       <c r="E7" s="14">
         <f>IFERROR(D7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>5.8862875969588003E-5</v>
+        <v>6.5403195521764439E-5</v>
       </c>
       <c r="F7" s="14">
         <f>IFERROR(E7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>5.8991934845529958E-5</v>
+        <v>6.5546594272811054E-5</v>
       </c>
       <c r="G7" s="14">
         <f>IFERROR(F7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>5.9121276687487163E-5</v>
+        <v>6.5690307430541287E-5</v>
       </c>
       <c r="H7" s="14">
         <f>IFERROR(G7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>5.9250902115872323E-5</v>
+        <v>6.5834335684302573E-5</v>
       </c>
       <c r="I7" s="14">
         <f>IFERROR(H7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>5.9380811752458414E-5</v>
+        <v>6.5978679724953783E-5</v>
       </c>
       <c r="J7" s="14">
         <f>IFERROR(I7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>5.9511006220381672E-5</v>
+        <v>6.6123340244868511E-5</v>
       </c>
       <c r="K7" s="14">
         <f>IFERROR(J7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>5.964148614414458E-5</v>
+        <v>6.6268317937938411E-5</v>
       </c>
       <c r="L7" s="14">
         <f>IFERROR(K7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>5.9772252149618862E-5</v>
+        <v>6.6413613499576501E-5</v>
       </c>
       <c r="M7" s="14">
         <f>IFERROR(L7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>5.9903304864048488E-5</v>
+        <v>6.655922762672053E-5</v>
       </c>
       <c r="N7" s="14">
         <f>IFERROR(M7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>6.0034644916052685E-5</v>
+        <v>6.6705161017836304E-5</v>
       </c>
       <c r="O7" s="14">
         <f>IFERROR(N7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>6.0166272935628952E-5</v>
+        <v>6.6851414372921041E-5</v>
       </c>
       <c r="P7" s="14">
         <f>IFERROR(O7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>6.0298189554156067E-5</v>
+        <v>6.6997988393506725E-5</v>
       </c>
       <c r="Q7" s="14">
         <f>IFERROR(P7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>6.0430395404397141E-5</v>
+        <v>6.7144883782663473E-5</v>
       </c>
       <c r="R7" s="14">
         <f>IFERROR(Q7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>6.0562891120502632E-5</v>
+        <v>6.7292101245002906E-5</v>
       </c>
       <c r="S7" s="14">
         <f>IFERROR(R7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>6.0695677338013403E-5</v>
+        <v>6.7439641486681539E-5</v>
       </c>
       <c r="T7" s="14">
         <f>IFERROR(S7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>6.0828754693863753E-5</v>
+        <v>6.7587505215404141E-5</v>
       </c>
       <c r="U7" s="14">
         <f>IFERROR(T7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>6.0962123826384479E-5</v>
+        <v>6.7735693140427163E-5</v>
       </c>
       <c r="V7" s="14">
         <f>IFERROR(U7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>6.1095785375305951E-5</v>
+        <v>6.7884205972562129E-5</v>
       </c>
       <c r="W7" s="14">
         <f>IFERROR(V7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>6.1229739981761162E-5</v>
+        <v>6.8033044424179034E-5</v>
       </c>
       <c r="X7" s="14">
         <f>IFERROR(W7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>6.1363988288288813E-5</v>
+        <v>6.8182209209209762E-5</v>
       </c>
       <c r="Y7" s="14">
         <f>IFERROR(X7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>6.1498530938836394E-5</v>
+        <v>6.8331701043151515E-5</v>
       </c>
       <c r="Z7" s="14">
         <f>IFERROR(Y7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>6.1633368578763279E-5</v>
+        <v>6.8481520643070266E-5</v>
       </c>
       <c r="AA7" s="14">
         <f>IFERROR(Z7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>6.1768501854843797E-5</v>
+        <v>6.8631668727604176E-5</v>
       </c>
       <c r="AB7" s="14">
         <f>IFERROR(AA7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>6.1903931415270357E-5</v>
+        <v>6.8782146016967025E-5</v>
       </c>
       <c r="AC7" s="14">
         <f>IFERROR(AB7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>6.203965790965657E-5</v>
+        <v>6.8932953232951703E-5</v>
       </c>
       <c r="AD7" s="14">
         <f>IFERROR(AC7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>6.2175681989040335E-5</v>
+        <v>6.9084091098933658E-5</v>
       </c>
       <c r="AE7" s="14">
         <f>IFERROR(AD7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>6.2312004305886969E-5</v>
+        <v>6.9235560339874364E-5</v>
       </c>
       <c r="AF7" s="14">
         <f>IFERROR(AE7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>6.2448625514092341E-5</v>
+        <v>6.9387361682324774E-5</v>
       </c>
       <c r="AG7" s="14"/>
     </row>
@@ -12562,127 +12562,127 @@
       </c>
       <c r="B8" s="13">
         <f>B5*Calibration!$D$21</f>
-        <v>4.2744493958450162E-5</v>
+        <v>4.7493882176055731E-5</v>
       </c>
       <c r="C8" s="13">
         <f>B8*(1+CAGR!$C$15)</f>
-        <v>4.2838212728593759E-5</v>
+        <v>4.7598014142881948E-5</v>
       </c>
       <c r="D8" s="13">
         <f>C8*(1+CAGR!$C$15)</f>
-        <v>4.2932136980357648E-5</v>
+        <v>4.7702374422619603E-5</v>
       </c>
       <c r="E8" s="13">
         <f>D8*(1+CAGR!$C$15)</f>
-        <v>4.3026267164267337E-5</v>
+        <v>4.7806963515852589E-5</v>
       </c>
       <c r="F8" s="13">
         <f>E8*(1+CAGR!$C$15)</f>
-        <v>4.3120603731836124E-5</v>
+        <v>4.7911781924262347E-5</v>
       </c>
       <c r="G8" s="13">
         <f>F8*(1+CAGR!$C$15)</f>
-        <v>4.3215147135567265E-5</v>
+        <v>4.8016830150630281E-5</v>
       </c>
       <c r="H8" s="13">
         <f>G8*(1+CAGR!$C$15)</f>
-        <v>4.3309897828956141E-5</v>
+        <v>4.8122108698840142E-5</v>
       </c>
       <c r="I8" s="13">
         <f>H8*(1+CAGR!$C$15)</f>
-        <v>4.340485626649245E-5</v>
+        <v>4.8227618073880485E-5</v>
       </c>
       <c r="J8" s="13">
         <f>I8*(1+CAGR!$C$15)</f>
-        <v>4.3500022903662359E-5</v>
+        <v>4.8333358781847052E-5</v>
       </c>
       <c r="K8" s="13">
         <f>J8*(1+CAGR!$C$15)</f>
-        <v>4.3595398196950712E-5</v>
+        <v>4.8439331329945225E-5</v>
       </c>
       <c r="L8" s="13">
         <f>K8*(1+CAGR!$C$15)</f>
-        <v>4.3690982603843211E-5</v>
+        <v>4.8545536226492446E-5</v>
       </c>
       <c r="M8" s="13">
         <f>L8*(1+CAGR!$C$15)</f>
-        <v>4.3786776582828612E-5</v>
+        <v>4.8651973980920667E-5</v>
       </c>
       <c r="N8" s="13">
         <f>M8*(1+CAGR!$C$15)</f>
-        <v>4.3882780593400923E-5</v>
+        <v>4.8758645103778789E-5</v>
       </c>
       <c r="O8" s="13">
         <f>N8*(1+CAGR!$C$15)</f>
-        <v>4.3978995096061607E-5</v>
+        <v>4.8865550106735101E-5</v>
       </c>
       <c r="P8" s="13">
         <f>O8*(1+CAGR!$C$15)</f>
-        <v>4.4075420552321789E-5</v>
+        <v>4.8972689502579745E-5</v>
       </c>
       <c r="Q8" s="13">
         <f>P8*(1+CAGR!$C$15)</f>
-        <v>4.4172057424704474E-5</v>
+        <v>4.9080063805227179E-5</v>
       </c>
       <c r="R8" s="13">
         <f>Q8*(1+CAGR!$C$15)</f>
-        <v>4.4268906176746776E-5</v>
+        <v>4.9187673529718626E-5</v>
       </c>
       <c r="S8" s="13">
         <f>R8*(1+CAGR!$C$15)</f>
-        <v>4.4365967273002112E-5</v>
+        <v>4.9295519192224561E-5</v>
       </c>
       <c r="T8" s="13">
         <f>S8*(1+CAGR!$C$15)</f>
-        <v>4.4463241179042467E-5</v>
+        <v>4.9403601310047173E-5</v>
       </c>
       <c r="U8" s="13">
         <f>T8*(1+CAGR!$C$15)</f>
-        <v>4.4560728361460595E-5</v>
+        <v>4.9511920401622865E-5</v>
       </c>
       <c r="V8" s="13">
         <f>U8*(1+CAGR!$C$15)</f>
-        <v>4.465842928787227E-5</v>
+        <v>4.962047698652473E-5</v>
       </c>
       <c r="W8" s="13">
         <f>V8*(1+CAGR!$C$15)</f>
-        <v>4.4756344426918542E-5</v>
+        <v>4.9729271585465032E-5</v>
       </c>
       <c r="X8" s="13">
         <f>W8*(1+CAGR!$C$15)</f>
-        <v>4.4854474248267957E-5</v>
+        <v>4.9838304720297714E-5</v>
       </c>
       <c r="Y8" s="13">
         <f>X8*(1+CAGR!$C$15)</f>
-        <v>4.4952819222618839E-5</v>
+        <v>4.9947576914020918E-5</v>
       </c>
       <c r="Z8" s="13">
         <f>Y8*(1+CAGR!$C$15)</f>
-        <v>4.5051379821701529E-5</v>
+        <v>5.0057088690779457E-5</v>
       </c>
       <c r="AA8" s="13">
         <f>Z8*(1+CAGR!$C$15)</f>
-        <v>4.5150156518280649E-5</v>
+        <v>5.0166840575867369E-5</v>
       </c>
       <c r="AB8" s="13">
         <f>AA8*(1+CAGR!$C$15)</f>
-        <v>4.5249149786157381E-5</v>
+        <v>5.02768330957304E-5</v>
       </c>
       <c r="AC8" s="13">
         <f>AB8*(1+CAGR!$C$15)</f>
-        <v>4.5348360100171721E-5</v>
+        <v>5.0387066777968555E-5</v>
       </c>
       <c r="AD8" s="13">
         <f>AC8*(1+CAGR!$C$15)</f>
-        <v>4.5447787936204781E-5</v>
+        <v>5.0497542151338622E-5</v>
       </c>
       <c r="AE8" s="13">
         <f>AD8*(1+CAGR!$C$15)</f>
-        <v>4.5547433771181053E-5</v>
+        <v>5.0608259745756703E-5</v>
       </c>
       <c r="AF8" s="13">
         <f>AE8*(1+CAGR!$C$15)</f>
-        <v>4.5647298083070703E-5</v>
+        <v>5.0719220092300762E-5</v>
       </c>
       <c r="AG8" s="14"/>
     </row>
@@ -12809,127 +12809,127 @@
       </c>
       <c r="B2" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$3:$H$3,,MATCH($A2,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.0832731482389663E-3</v>
+        <v>2.3147479424877404E-3</v>
       </c>
       <c r="C2" s="14">
         <f>IFERROR(B2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.0903444861996197E-3</v>
+        <v>2.3226049846662442E-3</v>
       </c>
       <c r="D2" s="14">
         <f>IFERROR(C2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.0974398266875439E-3</v>
+        <v>2.3304886963194933E-3</v>
       </c>
       <c r="E2" s="14">
         <f>IFERROR(D2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.1045592511754847E-3</v>
+        <v>2.3383991679727608E-3</v>
       </c>
       <c r="F2" s="14">
         <f>IFERROR(E2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.1117028414127329E-3</v>
+        <v>2.3463364904585922E-3</v>
       </c>
       <c r="G2" s="14">
         <f>IFERROR(F2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.118870679426065E-3</v>
+        <v>2.3543007549178502E-3</v>
       </c>
       <c r="H2" s="14">
         <f>IFERROR(G2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.126062847520684E-3</v>
+        <v>2.3622920528007601E-3</v>
       </c>
       <c r="I2" s="14">
         <f>IFERROR(H2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.133279428281165E-3</v>
+        <v>2.370310475867961E-3</v>
       </c>
       <c r="J2" s="14">
         <f>IFERROR(I2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.1405205045724024E-3</v>
+        <v>2.3783561161915584E-3</v>
       </c>
       <c r="K2" s="14">
         <f>IFERROR(J2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.1477861595405635E-3</v>
+        <v>2.3864290661561819E-3</v>
       </c>
       <c r="L2" s="14">
         <f>IFERROR(K2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.1550764766140413E-3</v>
+        <v>2.3945294184600464E-3</v>
       </c>
       <c r="M2" s="14">
         <f>IFERROR(L2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.1623915395044134E-3</v>
+        <v>2.4026572661160154E-3</v>
       </c>
       <c r="N2" s="14">
         <f>IFERROR(M2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.1697314322074029E-3</v>
+        <v>2.4108127024526703E-3</v>
       </c>
       <c r="O2" s="14">
         <f>IFERROR(N2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.1770962390038427E-3</v>
+        <v>2.4189958211153812E-3</v>
       </c>
       <c r="P2" s="14">
         <f>IFERROR(O2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.1844860444606437E-3</v>
+        <v>2.4272067160673824E-3</v>
       </c>
       <c r="Q2" s="14">
         <f>IFERROR(P2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.1919009334317656E-3</v>
+        <v>2.4354454815908515E-3</v>
       </c>
       <c r="R2" s="14">
         <f>IFERROR(Q2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.1993409910591915E-3</v>
+        <v>2.4437122122879917E-3</v>
       </c>
       <c r="S2" s="14">
         <f>IFERROR(R2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.2068063027739053E-3</v>
+        <v>2.4520070030821183E-3</v>
       </c>
       <c r="T2" s="14">
         <f>IFERROR(S2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.214296954296873E-3</v>
+        <v>2.460329949218749E-3</v>
       </c>
       <c r="U2" s="14">
         <f>IFERROR(T2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.2218130316400261E-3</v>
+        <v>2.468681146266697E-3</v>
       </c>
       <c r="V2" s="14">
         <f>IFERROR(U2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.2293546211072505E-3</v>
+        <v>2.4770606901191685E-3</v>
       </c>
       <c r="W2" s="14">
         <f>IFERROR(V2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.2369218092953762E-3</v>
+        <v>2.4854686769948636E-3</v>
       </c>
       <c r="X2" s="14">
         <f>IFERROR(W2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.2445146830951728E-3</v>
+        <v>2.4939052034390822E-3</v>
       </c>
       <c r="Y2" s="14">
         <f>IFERROR(X2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.2521333296923467E-3</v>
+        <v>2.502370366324831E-3</v>
       </c>
       <c r="Z2" s="14">
         <f>IFERROR(Y2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.259777836568542E-3</v>
+        <v>2.5108642628539368E-3</v>
       </c>
       <c r="AA2" s="14">
         <f>IFERROR(Z2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.2674482915023457E-3</v>
+        <v>2.519386990558163E-3</v>
       </c>
       <c r="AB2" s="14">
         <f>IFERROR(AA2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.2751447825702944E-3</v>
+        <v>2.5279386473003283E-3</v>
       </c>
       <c r="AC2" s="14">
         <f>IFERROR(AB2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.2828673981478875E-3</v>
+        <v>2.5365193312754317E-3</v>
       </c>
       <c r="AD2" s="14">
         <f>IFERROR(AC2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.2906162269106002E-3</v>
+        <v>2.5451291410117788E-3</v>
       </c>
       <c r="AE2" s="14">
         <f>IFERROR(AD2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.2983913578349022E-3</v>
+        <v>2.5537681753721145E-3</v>
       </c>
       <c r="AF2" s="14">
         <f>IFERROR(AE2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.3061928801992805E-3</v>
+        <v>2.5624365335547572E-3</v>
       </c>
       <c r="AG2" s="14"/>
     </row>
@@ -12939,127 +12939,127 @@
       </c>
       <c r="B3" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$3:$H$3,,MATCH($A3,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.480435075829397E-3</v>
+        <v>1.6449278620326634E-3</v>
       </c>
       <c r="C3" s="14">
         <f>IFERROR(B3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.4919731470609968E-3</v>
+        <v>1.6577479411788853E-3</v>
       </c>
       <c r="D3" s="14">
         <f>IFERROR(C3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.5036011425924992E-3</v>
+        <v>1.6706679362138879E-3</v>
       </c>
       <c r="E3" s="14">
         <f>IFERROR(D3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.5153197632671869E-3</v>
+        <v>1.6836886258524296E-3</v>
       </c>
       <c r="F3" s="14">
         <f>IFERROR(E3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.5271297153905061E-3</v>
+        <v>1.6968107948783398E-3</v>
       </c>
       <c r="G3" s="14">
         <f>IFERROR(F3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.5390317107726384E-3</v>
+        <v>1.7100352341918202E-3</v>
       </c>
       <c r="H3" s="14">
         <f>IFERROR(G3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.5510264667714024E-3</v>
+        <v>1.7233627408571137E-3</v>
       </c>
       <c r="I3" s="14">
         <f>IFERROR(H3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.5631147063354905E-3</v>
+        <v>1.736794118150545E-3</v>
       </c>
       <c r="J3" s="14">
         <f>IFERROR(I3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.5752971580480426E-3</v>
+        <v>1.7503301756089361E-3</v>
       </c>
       <c r="K3" s="14">
         <f>IFERROR(J3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.5875745561705586E-3</v>
+        <v>1.7639717290783984E-3</v>
       </c>
       <c r="L3" s="14">
         <f>IFERROR(K3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.5999476406871552E-3</v>
+        <v>1.7777196007635057E-3</v>
       </c>
       <c r="M3" s="14">
         <f>IFERROR(L3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.6124171573491651E-3</v>
+        <v>1.7915746192768498E-3</v>
       </c>
       <c r="N3" s="14">
         <f>IFERROR(M3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.624983857720085E-3</v>
+        <v>1.8055376196889831E-3</v>
       </c>
       <c r="O3" s="14">
         <f>IFERROR(N3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.6376484992208749E-3</v>
+        <v>1.8196094435787497E-3</v>
       </c>
       <c r="P3" s="14">
         <f>IFERROR(O3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.6504118451756084E-3</v>
+        <v>1.8337909390840092E-3</v>
       </c>
       <c r="Q3" s="14">
         <f>IFERROR(P3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.6632746648574804E-3</v>
+        <v>1.848082960952756E-3</v>
       </c>
       <c r="R3" s="14">
         <f>IFERROR(Q3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.6762377335351724E-3</v>
+        <v>1.8624863705946359E-3</v>
       </c>
       <c r="S3" s="14">
         <f>IFERROR(R3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.6893018325195798E-3</v>
+        <v>1.8770020361328665E-3</v>
       </c>
       <c r="T3" s="14">
         <f>IFERROR(S3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.7024677492109032E-3</v>
+        <v>1.891630832456559E-3</v>
       </c>
       <c r="U3" s="14">
         <f>IFERROR(T3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.7157362771461062E-3</v>
+        <v>1.9063736412734511E-3</v>
       </c>
       <c r="V3" s="14">
         <f>IFERROR(U3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.7291082160467439E-3</v>
+        <v>1.9212313511630483E-3</v>
       </c>
       <c r="W3" s="14">
         <f>IFERROR(V3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.7425843718671635E-3</v>
+        <v>1.9362048576301812E-3</v>
       </c>
       <c r="X3" s="14">
         <f>IFERROR(W3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.7561655568430813E-3</v>
+        <v>1.9512950631589787E-3</v>
       </c>
       <c r="Y3" s="14">
         <f>IFERROR(X3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.769852589540537E-3</v>
+        <v>1.9665028772672629E-3</v>
       </c>
       <c r="Z3" s="14">
         <f>IFERROR(Y3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.7836462949052316E-3</v>
+        <v>1.9818292165613679E-3</v>
       </c>
       <c r="AA3" s="14">
         <f>IFERROR(Z3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.7975475043122472E-3</v>
+        <v>1.9972750047913853E-3</v>
       </c>
       <c r="AB3" s="14">
         <f>IFERROR(AA3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.8115570556161565E-3</v>
+        <v>2.0128411729068403E-3</v>
       </c>
       <c r="AC3" s="14">
         <f>IFERROR(AB3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.8256757932015222E-3</v>
+        <v>2.028528659112802E-3</v>
       </c>
       <c r="AD3" s="14">
         <f>IFERROR(AC3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.8399045680337891E-3</v>
+        <v>2.0443384089264319E-3</v>
       </c>
       <c r="AE3" s="14">
         <f>IFERROR(AD3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.854244237710574E-3</v>
+        <v>2.0602713752339709E-3</v>
       </c>
       <c r="AF3" s="14">
         <f>IFERROR(AE3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.8686956665133548E-3</v>
+        <v>2.0763285183481718E-3</v>
       </c>
       <c r="AG3" s="14"/>
     </row>
@@ -13069,127 +13069,127 @@
       </c>
       <c r="B4" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$3:$H$3,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>5.3802510963146669E-4</v>
+        <v>5.978056773682963E-4</v>
       </c>
       <c r="C4" s="14">
         <f>IFERROR(B4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>5.4340966383699093E-4</v>
+        <v>6.0378851537443439E-4</v>
       </c>
       <c r="D4" s="14">
         <f>IFERROR(C4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>5.4884810665007874E-4</v>
+        <v>6.0983122961119857E-4</v>
       </c>
       <c r="E4" s="14">
         <f>IFERROR(D4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>5.5434097738780519E-4</v>
+        <v>6.1593441931978349E-4</v>
       </c>
       <c r="F4" s="14">
         <f>IFERROR(E4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>5.5988882076472954E-4</v>
+        <v>6.2209868973858837E-4</v>
       </c>
       <c r="G4" s="14">
         <f>IFERROR(F4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>5.6549218694691347E-4</v>
+        <v>6.2832465216323713E-4</v>
       </c>
       <c r="H4" s="14">
         <f>IFERROR(G4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>5.7115163160647935E-4</v>
+        <v>6.3461292400719921E-4</v>
       </c>
       <c r="I4" s="14">
         <f>IFERROR(H4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>5.7686771597671499E-4</v>
+        <v>6.4096412886301656E-4</v>
       </c>
       <c r="J4" s="14">
         <f>IFERROR(I4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>5.8264100690772977E-4</v>
+        <v>6.473788965641441E-4</v>
       </c>
       <c r="K4" s="14">
         <f>IFERROR(J4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>5.8847207692266804E-4</v>
+        <v>6.5385786324740887E-4</v>
       </c>
       <c r="L4" s="14">
         <f>IFERROR(K4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>5.9436150427448443E-4</v>
+        <v>6.6040167141609375E-4</v>
       </c>
       <c r="M4" s="14">
         <f>IFERROR(L4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>6.0030987300328797E-4</v>
+        <v>6.6701097000365325E-4</v>
       </c>
       <c r="N4" s="14">
         <f>IFERROR(M4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>6.0631777299425995E-4</v>
+        <v>6.736864144380666E-4</v>
       </c>
       <c r="O4" s="14">
         <f>IFERROR(N4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>6.1238580003615138E-4</v>
+        <v>6.8042866670683488E-4</v>
       </c>
       <c r="P4" s="14">
         <f>IFERROR(O4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>6.1851455588036596E-4</v>
+        <v>6.8723839542262884E-4</v>
       </c>
       <c r="Q4" s="14">
         <f>IFERROR(P4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>6.24704648300634E-4</v>
+        <v>6.9411627588959334E-4</v>
       </c>
       <c r="R4" s="14">
         <f>IFERROR(Q4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>6.3095669115328424E-4</v>
+        <v>7.0106299017031577E-4</v>
       </c>
       <c r="S4" s="14">
         <f>IFERROR(R4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>6.3727130443811818E-4</v>
+        <v>7.0807922715346457E-4</v>
       </c>
       <c r="T4" s="14">
         <f>IFERROR(S4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>6.4364911435989421E-4</v>
+        <v>7.1516568262210459E-4</v>
       </c>
       <c r="U4" s="14">
         <f>IFERROR(T4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>6.5009075339042663E-4</v>
+        <v>7.2232305932269614E-4</v>
       </c>
       <c r="V4" s="14">
         <f>IFERROR(U4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>6.5659686033130637E-4</v>
+        <v>7.295520670347848E-4</v>
       </c>
       <c r="W4" s="14">
         <f>IFERROR(V4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>6.6316808037724935E-4</v>
+        <v>7.3685342264138813E-4</v>
       </c>
       <c r="X4" s="14">
         <f>IFERROR(W4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>6.6980506518007899E-4</v>
+        <v>7.4422785020008772E-4</v>
       </c>
       <c r="Y4" s="14">
         <f>IFERROR(X4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>6.7650847291334871E-4</v>
+        <v>7.5167608101483184E-4</v>
       </c>
       <c r="Z4" s="14">
         <f>IFERROR(Y4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>6.8327896833761154E-4</v>
+        <v>7.5919885370845722E-4</v>
       </c>
       <c r="AA4" s="14">
         <f>IFERROR(Z4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>6.9011722286634297E-4</v>
+        <v>7.6679691429593652E-4</v>
       </c>
       <c r="AB4" s="14">
         <f>IFERROR(AA4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>6.9702391463252289E-4</v>
+        <v>7.7447101625835869E-4</v>
       </c>
       <c r="AC4" s="14">
         <f>IFERROR(AB4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>7.0399972855588486E-4</v>
+        <v>7.8222192061764976E-4</v>
       </c>
       <c r="AD4" s="14">
         <f>IFERROR(AC4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>7.1104535641083779E-4</v>
+        <v>7.9005039601204188E-4</v>
       </c>
       <c r="AE4" s="14">
         <f>IFERROR(AD4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>7.1816149689506723E-4</v>
+        <v>7.979572187722969E-4</v>
       </c>
       <c r="AF4" s="14">
         <f>IFERROR(AE4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>7.2534885569882409E-4</v>
+        <v>8.0594317299869332E-4</v>
       </c>
       <c r="AG4" s="14"/>
     </row>
@@ -13199,127 +13199,127 @@
       </c>
       <c r="B5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$3:$H$3,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>6.5134982867137345E-4</v>
+        <v>7.2372203185708153E-4</v>
       </c>
       <c r="C5" s="14">
         <f>IFERROR(B5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>6.566423882338327E-4</v>
+        <v>7.2960265359314736E-4</v>
       </c>
       <c r="D5" s="14">
         <f>IFERROR(C5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>6.6197795262332832E-4</v>
+        <v>7.3553105847036471E-4</v>
       </c>
       <c r="E5" s="14">
         <f>IFERROR(D5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>6.6735687127667377E-4</v>
+        <v>7.4150763475185966E-4</v>
       </c>
       <c r="F5" s="14">
         <f>IFERROR(E5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>6.7277949647004008E-4</v>
+        <v>7.4753277385560001E-4</v>
       </c>
       <c r="G5" s="14">
         <f>IFERROR(F5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>6.782461833420274E-4</v>
+        <v>7.536068703800304E-4</v>
       </c>
       <c r="H5" s="14">
         <f>IFERROR(G5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>6.8375728991692359E-4</v>
+        <v>7.597303221299151E-4</v>
       </c>
       <c r="I5" s="14">
         <f>IFERROR(H5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>6.8931317712815187E-4</v>
+        <v>7.6590353014239099E-4</v>
       </c>
       <c r="J5" s="14">
         <f>IFERROR(I5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>6.9491420884190919E-4</v>
+        <v>7.7212689871323245E-4</v>
       </c>
       <c r="K5" s="14">
         <f>IFERROR(J5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>7.0056075188099651E-4</v>
+        <v>7.7840083542332942E-4</v>
       </c>
       <c r="L5" s="14">
         <f>IFERROR(K5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>7.0625317604884272E-4</v>
+        <v>7.8472575116538077E-4</v>
       </c>
       <c r="M5" s="14">
         <f>IFERROR(L5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>7.1199185415372391E-4</v>
+        <v>7.9110206017080434E-4</v>
       </c>
       <c r="N5" s="14">
         <f>IFERROR(M5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>7.1777716203317926E-4</v>
+        <v>7.975301800368658E-4</v>
       </c>
       <c r="O5" s="14">
         <f>IFERROR(N5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>7.2360947857862535E-4</v>
+        <v>8.0401053175402815E-4</v>
       </c>
       <c r="P5" s="14">
         <f>IFERROR(O5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>7.2948918576017075E-4</v>
+        <v>8.1054353973352301E-4</v>
       </c>
       <c r="Q5" s="14">
         <f>IFERROR(P5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>7.354166686516317E-4</v>
+        <v>8.1712963183514626E-4</v>
       </c>
       <c r="R5" s="14">
         <f>IFERROR(Q5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>7.4139231545575159E-4</v>
+        <v>8.2376923939527944E-4</v>
       </c>
       <c r="S5" s="14">
         <f>IFERROR(R5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>7.4741651752962494E-4</v>
+        <v>8.3046279725513877E-4</v>
       </c>
       <c r="T5" s="14">
         <f>IFERROR(S5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>7.5348966941032837E-4</v>
+        <v>8.3721074378925373E-4</v>
       </c>
       <c r="U5" s="14">
         <f>IFERROR(T5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>7.5961216884075952E-4</v>
+        <v>8.4401352093417721E-4</v>
       </c>
       <c r="V5" s="14">
         <f>IFERROR(U5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>7.65784416795686E-4</v>
+        <v>8.5087157421742882E-4</v>
       </c>
       <c r="W5" s="14">
         <f>IFERROR(V5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>7.7200681750800605E-4</v>
+        <v>8.5778535278667326E-4</v>
       </c>
       <c r="X5" s="14">
         <f>IFERROR(W5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>7.782797784952226E-4</v>
+        <v>8.6475530943913614E-4</v>
       </c>
       <c r="Y5" s="14">
         <f>IFERROR(X5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>7.8460371058613251E-4</v>
+        <v>8.7178190065125818E-4</v>
       </c>
       <c r="Z5" s="14">
         <f>IFERROR(Y5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>7.9097902794773227E-4</v>
+        <v>8.7886558660859129E-4</v>
       </c>
       <c r="AA5" s="14">
         <f>IFERROR(Z5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>7.9740614811234288E-4</v>
+        <v>8.8600683123593647E-4</v>
       </c>
       <c r="AB5" s="14">
         <f>IFERROR(AA5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>8.0388549200495496E-4</v>
+        <v>8.932061022277276E-4</v>
       </c>
       <c r="AC5" s="14">
         <f>IFERROR(AB5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>8.1041748397079553E-4</v>
+        <v>9.0046387107866157E-4</v>
       </c>
       <c r="AD5" s="14">
         <f>IFERROR(AC5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>8.1700255180311985E-4</v>
+        <v>9.077806131145774E-4</v>
       </c>
       <c r="AE5" s="14">
         <f>IFERROR(AD5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>8.236411267712278E-4</v>
+        <v>9.1515680752358628E-4</v>
       </c>
       <c r="AF5" s="14">
         <f>IFERROR(AE5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>8.3033364364870914E-4</v>
+        <v>9.2259293738745452E-4</v>
       </c>
       <c r="AG5" s="14"/>
     </row>
@@ -13329,127 +13329,127 @@
       </c>
       <c r="B6" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$3:$H$3,,MATCH($A6,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.4326691196766717E-3</v>
+        <v>1.591854577418524E-3</v>
       </c>
       <c r="C6" s="14">
         <f>IFERROR(B6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.4326691196766717E-3</v>
+        <v>1.591854577418524E-3</v>
       </c>
       <c r="D6" s="14">
         <f>IFERROR(C6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.4326691196766717E-3</v>
+        <v>1.591854577418524E-3</v>
       </c>
       <c r="E6" s="14">
         <f>IFERROR(D6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.4326691196766717E-3</v>
+        <v>1.591854577418524E-3</v>
       </c>
       <c r="F6" s="14">
         <f>IFERROR(E6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.4326691196766717E-3</v>
+        <v>1.591854577418524E-3</v>
       </c>
       <c r="G6" s="14">
         <f>IFERROR(F6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.4326691196766717E-3</v>
+        <v>1.591854577418524E-3</v>
       </c>
       <c r="H6" s="14">
         <f>IFERROR(G6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.4326691196766717E-3</v>
+        <v>1.591854577418524E-3</v>
       </c>
       <c r="I6" s="14">
         <f>IFERROR(H6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.4326691196766717E-3</v>
+        <v>1.591854577418524E-3</v>
       </c>
       <c r="J6" s="14">
         <f>IFERROR(I6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.4326691196766717E-3</v>
+        <v>1.591854577418524E-3</v>
       </c>
       <c r="K6" s="14">
         <f>IFERROR(J6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.4326691196766717E-3</v>
+        <v>1.591854577418524E-3</v>
       </c>
       <c r="L6" s="14">
         <f>IFERROR(K6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.4326691196766717E-3</v>
+        <v>1.591854577418524E-3</v>
       </c>
       <c r="M6" s="14">
         <f>IFERROR(L6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.4326691196766717E-3</v>
+        <v>1.591854577418524E-3</v>
       </c>
       <c r="N6" s="14">
         <f>IFERROR(M6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.4326691196766717E-3</v>
+        <v>1.591854577418524E-3</v>
       </c>
       <c r="O6" s="14">
         <f>IFERROR(N6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.4326691196766717E-3</v>
+        <v>1.591854577418524E-3</v>
       </c>
       <c r="P6" s="14">
         <f>IFERROR(O6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.4326691196766717E-3</v>
+        <v>1.591854577418524E-3</v>
       </c>
       <c r="Q6" s="14">
         <f>IFERROR(P6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.4326691196766717E-3</v>
+        <v>1.591854577418524E-3</v>
       </c>
       <c r="R6" s="14">
         <f>IFERROR(Q6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.4326691196766717E-3</v>
+        <v>1.591854577418524E-3</v>
       </c>
       <c r="S6" s="14">
         <f>IFERROR(R6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.4326691196766717E-3</v>
+        <v>1.591854577418524E-3</v>
       </c>
       <c r="T6" s="14">
         <f>IFERROR(S6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.4326691196766717E-3</v>
+        <v>1.591854577418524E-3</v>
       </c>
       <c r="U6" s="14">
         <f>IFERROR(T6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.4326691196766717E-3</v>
+        <v>1.591854577418524E-3</v>
       </c>
       <c r="V6" s="14">
         <f>IFERROR(U6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.4326691196766717E-3</v>
+        <v>1.591854577418524E-3</v>
       </c>
       <c r="W6" s="14">
         <f>IFERROR(V6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.4326691196766717E-3</v>
+        <v>1.591854577418524E-3</v>
       </c>
       <c r="X6" s="14">
         <f>IFERROR(W6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.4326691196766717E-3</v>
+        <v>1.591854577418524E-3</v>
       </c>
       <c r="Y6" s="14">
         <f>IFERROR(X6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.4326691196766717E-3</v>
+        <v>1.591854577418524E-3</v>
       </c>
       <c r="Z6" s="14">
         <f>IFERROR(Y6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.4326691196766717E-3</v>
+        <v>1.591854577418524E-3</v>
       </c>
       <c r="AA6" s="14">
         <f>IFERROR(Z6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.4326691196766717E-3</v>
+        <v>1.591854577418524E-3</v>
       </c>
       <c r="AB6" s="14">
         <f>IFERROR(AA6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.4326691196766717E-3</v>
+        <v>1.591854577418524E-3</v>
       </c>
       <c r="AC6" s="14">
         <f>IFERROR(AB6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.4326691196766717E-3</v>
+        <v>1.591854577418524E-3</v>
       </c>
       <c r="AD6" s="14">
         <f>IFERROR(AC6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.4326691196766717E-3</v>
+        <v>1.591854577418524E-3</v>
       </c>
       <c r="AE6" s="14">
         <f>IFERROR(AD6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.4326691196766717E-3</v>
+        <v>1.591854577418524E-3</v>
       </c>
       <c r="AF6" s="14">
         <f>IFERROR(AE6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.4326691196766717E-3</v>
+        <v>1.591854577418524E-3</v>
       </c>
       <c r="AG6" s="14"/>
     </row>
@@ -13459,127 +13459,127 @@
       </c>
       <c r="B7" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$3:$H$3,,MATCH($A7,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.154665397086832E-3</v>
+        <v>1.2829615523187021E-3</v>
       </c>
       <c r="C7" s="14">
         <f>IFERROR(B7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.1653387940065518E-3</v>
+        <v>1.2948208822295018E-3</v>
       </c>
       <c r="D7" s="14">
         <f>IFERROR(C7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.1761108527568705E-3</v>
+        <v>1.3067898363965226E-3</v>
       </c>
       <c r="E7" s="14">
         <f>IFERROR(D7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.186982485339552E-3</v>
+        <v>1.3188694281550577E-3</v>
       </c>
       <c r="F7" s="14">
         <f>IFERROR(E7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.197954612186644E-3</v>
+        <v>1.331060680207382E-3</v>
       </c>
       <c r="G7" s="14">
         <f>IFERROR(F7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.2090281622384046E-3</v>
+        <v>1.3433646247093382E-3</v>
       </c>
       <c r="H7" s="14">
         <f>IFERROR(G7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.2202040730219504E-3</v>
+        <v>1.3557823033577222E-3</v>
       </c>
       <c r="I7" s="14">
         <f>IFERROR(H7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.2314832907306306E-3</v>
+        <v>1.3683147674784779E-3</v>
       </c>
       <c r="J7" s="14">
         <f>IFERROR(I7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.2428667703041352E-3</v>
+        <v>1.3809630781157053E-3</v>
       </c>
       <c r="K7" s="14">
         <f>IFERROR(J7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.2543554755093441E-3</v>
+        <v>1.3937283061214931E-3</v>
       </c>
       <c r="L7" s="14">
         <f>IFERROR(K7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.2659503790219226E-3</v>
+        <v>1.4066115322465805E-3</v>
       </c>
       <c r="M7" s="14">
         <f>IFERROR(L7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.277652462508672E-3</v>
+        <v>1.4196138472318575E-3</v>
       </c>
       <c r="N7" s="14">
         <f>IFERROR(M7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.2894627167106406E-3</v>
+        <v>1.4327363519007115E-3</v>
       </c>
       <c r="O7" s="14">
         <f>IFERROR(N7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.3013821415270039E-3</v>
+        <v>1.4459801572522264E-3</v>
       </c>
       <c r="P7" s="14">
         <f>IFERROR(O7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.3134117460997198E-3</v>
+        <v>1.459346384555244E-3</v>
       </c>
       <c r="Q7" s="14">
         <f>IFERROR(P7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.325552548898966E-3</v>
+        <v>1.4728361654432953E-3</v>
       </c>
       <c r="R7" s="14">
         <f>IFERROR(Q7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.3378055778093673E-3</v>
+        <v>1.4864506420104078E-3</v>
       </c>
       <c r="S7" s="14">
         <f>IFERROR(R7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.3501718702170202E-3</v>
+        <v>1.5001909669077999E-3</v>
       </c>
       <c r="T7" s="14">
         <f>IFERROR(S7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.362652473097322E-3</v>
+        <v>1.5140583034414683E-3</v>
       </c>
       <c r="U7" s="14">
         <f>IFERROR(T7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.3752484431036108E-3</v>
+        <v>1.5280538256706782E-3</v>
       </c>
       <c r="V7" s="14">
         <f>IFERROR(U7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.3879608466566269E-3</v>
+        <v>1.5421787185073629E-3</v>
       </c>
       <c r="W7" s="14">
         <f>IFERROR(V7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.4007907600347988E-3</v>
+        <v>1.5564341778164428E-3</v>
       </c>
       <c r="X7" s="14">
         <f>IFERROR(W7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.413739269465365E-3</v>
+        <v>1.570821410517072E-3</v>
       </c>
       <c r="Y7" s="14">
         <f>IFERROR(X7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.4268074712163383E-3</v>
+        <v>1.5853416346848202E-3</v>
       </c>
       <c r="Z7" s="14">
         <f>IFERROR(Y7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.4399964716893198E-3</v>
+        <v>1.5999960796547997E-3</v>
       </c>
       <c r="AA7" s="14">
         <f>IFERROR(Z7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.4533073875131707E-3</v>
+        <v>1.614785986125745E-3</v>
       </c>
       <c r="AB7" s="14">
         <f>IFERROR(AA7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.46674134563855E-3</v>
+        <v>1.6297126062650553E-3</v>
       </c>
       <c r="AC7" s="14">
         <f>IFERROR(AB7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.480299483433327E-3</v>
+        <v>1.6447772038148073E-3</v>
       </c>
       <c r="AD7" s="14">
         <f>IFERROR(AC7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.4939829487788741E-3</v>
+        <v>1.6599810541987484E-3</v>
       </c>
       <c r="AE7" s="14">
         <f>IFERROR(AD7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.5077929001672511E-3</v>
+        <v>1.6753254446302784E-3</v>
       </c>
       <c r="AF7" s="14">
         <f>IFERROR(AE7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.5217305067992874E-3</v>
+        <v>1.69081167422143E-3</v>
       </c>
       <c r="AG7" s="14"/>
     </row>
@@ -13589,127 +13589,127 @@
       </c>
       <c r="B8" s="18">
         <f>'SYFAFE psgr'!H3</f>
-        <v>1.9382997819468279E-3</v>
+        <v>2.1536664243853644E-3</v>
       </c>
       <c r="C8" s="18">
         <f>B8*(1+CAGR!$D$22)</f>
-        <v>1.9588297709946028E-3</v>
+        <v>2.1764775233273363E-3</v>
       </c>
       <c r="D8" s="18">
         <f>C8*(1+CAGR!$D$22)</f>
-        <v>1.9795772085785777E-3</v>
+        <v>2.1995302317539753E-3</v>
       </c>
       <c r="E8" s="18">
         <f>D8*(1+CAGR!$D$22)</f>
-        <v>2.0005443978595482E-3</v>
+        <v>2.222827108732831E-3</v>
       </c>
       <c r="F8" s="18">
         <f>E8*(1+CAGR!$D$22)</f>
-        <v>2.021733666392815E-3</v>
+        <v>2.2463707404364605E-3</v>
       </c>
       <c r="G8" s="18">
         <f>F8*(1+CAGR!$D$22)</f>
-        <v>2.043147366386566E-3</v>
+        <v>2.2701637404295171E-3</v>
       </c>
       <c r="H8" s="18">
         <f>G8*(1+CAGR!$D$22)</f>
-        <v>2.0647878749629925E-3</v>
+        <v>2.29420874995888E-3</v>
       </c>
       <c r="I8" s="18">
         <f>H8*(1+CAGR!$D$22)</f>
-        <v>2.0866575944221734E-3</v>
+        <v>2.3185084382468584E-3</v>
       </c>
       <c r="J8" s="18">
         <f>I8*(1+CAGR!$D$22)</f>
-        <v>2.1087589525087516E-3</v>
+        <v>2.3430655027875009E-3</v>
       </c>
       <c r="K8" s="18">
         <f>J8*(1+CAGR!$D$22)</f>
-        <v>2.1310944026814377E-3</v>
+        <v>2.3678826696460408E-3</v>
       </c>
       <c r="L8" s="18">
         <f>K8*(1+CAGR!$D$22)</f>
-        <v>2.1536664243853665E-3</v>
+        <v>2.3929626937615172E-3</v>
       </c>
       <c r="M8" s="18">
         <f>L8*(1+CAGR!$D$22)</f>
-        <v>2.1764775233273385E-3</v>
+        <v>2.4183083592525969E-3</v>
       </c>
       <c r="N8" s="18">
         <f>M8*(1+CAGR!$D$22)</f>
-        <v>2.1995302317539774E-3</v>
+        <v>2.4439224797266402E-3</v>
       </c>
       <c r="O8" s="18">
         <f>N8*(1+CAGR!$D$22)</f>
-        <v>2.2228271087328332E-3</v>
+        <v>2.4698078985920355E-3</v>
       </c>
       <c r="P8" s="18">
         <f>O8*(1+CAGR!$D$22)</f>
-        <v>2.2463707404364627E-3</v>
+        <v>2.4959674893738461E-3</v>
       </c>
       <c r="Q8" s="18">
         <f>P8*(1+CAGR!$D$22)</f>
-        <v>2.2701637404295193E-3</v>
+        <v>2.5224041560327976E-3</v>
       </c>
       <c r="R8" s="18">
         <f>Q8*(1+CAGR!$D$22)</f>
-        <v>2.2942087499588822E-3</v>
+        <v>2.5491208332876453E-3</v>
       </c>
       <c r="S8" s="18">
         <f>R8*(1+CAGR!$D$22)</f>
-        <v>2.3185084382468606E-3</v>
+        <v>2.5761204869409549E-3</v>
       </c>
       <c r="T8" s="18">
         <f>S8*(1+CAGR!$D$22)</f>
-        <v>2.3430655027875031E-3</v>
+        <v>2.6034061142083354E-3</v>
       </c>
       <c r="U8" s="18">
         <f>T8*(1+CAGR!$D$22)</f>
-        <v>2.367882669646043E-3</v>
+        <v>2.6309807440511577E-3</v>
       </c>
       <c r="V8" s="18">
         <f>U8*(1+CAGR!$D$22)</f>
-        <v>2.3929626937615194E-3</v>
+        <v>2.6588474375127979E-3</v>
       </c>
       <c r="W8" s="18">
         <f>V8*(1+CAGR!$D$22)</f>
-        <v>2.4183083592525991E-3</v>
+        <v>2.6870092880584423E-3</v>
       </c>
       <c r="X8" s="18">
         <f>W8*(1+CAGR!$D$22)</f>
-        <v>2.4439224797266424E-3</v>
+        <v>2.7154694219184905E-3</v>
       </c>
       <c r="Y8" s="18">
         <f>X8*(1+CAGR!$D$22)</f>
-        <v>2.4698078985920377E-3</v>
+        <v>2.7442309984355966E-3</v>
       </c>
       <c r="Z8" s="18">
         <f>Y8*(1+CAGR!$D$22)</f>
-        <v>2.4959674893738483E-3</v>
+        <v>2.7732972104153862E-3</v>
       </c>
       <c r="AA8" s="18">
         <f>Z8*(1+CAGR!$D$22)</f>
-        <v>2.5224041560327998E-3</v>
+        <v>2.8026712844808877E-3</v>
       </c>
       <c r="AB8" s="18">
         <f>AA8*(1+CAGR!$D$22)</f>
-        <v>2.5491208332876474E-3</v>
+        <v>2.8323564814307185E-3</v>
       </c>
       <c r="AC8" s="18">
         <f>AB8*(1+CAGR!$D$22)</f>
-        <v>2.5761204869409571E-3</v>
+        <v>2.8623560966010626E-3</v>
       </c>
       <c r="AD8" s="18">
         <f>AC8*(1+CAGR!$D$22)</f>
-        <v>2.6034061142083376E-3</v>
+        <v>2.8926734602314854E-3</v>
       </c>
       <c r="AE8" s="18">
         <f>AD8*(1+CAGR!$D$22)</f>
-        <v>2.6309807440511599E-3</v>
+        <v>2.9233119378346212E-3</v>
       </c>
       <c r="AF8" s="18">
         <f>AE8*(1+CAGR!$D$22)</f>
-        <v>2.6588474375128001E-3</v>
+        <v>2.9542749305697773E-3</v>
       </c>
       <c r="AG8" s="14"/>
     </row>
@@ -13836,127 +13836,127 @@
       </c>
       <c r="B2" s="21">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$3:$H$3,,MATCH($A2,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>6.1502304216890663E-4</v>
+        <v>6.8335893574322944E-4</v>
       </c>
       <c r="C2" s="21">
         <f>IFERROR(B2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>6.1711063965387482E-4</v>
+        <v>6.8567848850430515E-4</v>
       </c>
       <c r="D2" s="21">
         <f>IFERROR(C2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>6.1920532315507405E-4</v>
+        <v>6.8800591461674865E-4</v>
       </c>
       <c r="E2" s="21">
         <f>IFERROR(D2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>6.2130711672485459E-4</v>
+        <v>6.9034124080539366E-4</v>
       </c>
       <c r="F2" s="21">
         <f>IFERROR(E2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>6.2341604449720855E-4</v>
+        <v>6.9268449388578692E-4</v>
       </c>
       <c r="G2" s="21">
         <f>IFERROR(F2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>6.2553213068804723E-4</v>
+        <v>6.9503570076449655E-4</v>
       </c>
       <c r="H2" s="21">
         <f>IFERROR(G2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>6.2765539959547874E-4</v>
+        <v>6.9739488843942039E-4</v>
       </c>
       <c r="I2" s="21">
         <f>IFERROR(H2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>6.2978587560008734E-4</v>
+        <v>6.9976208400009663E-4</v>
       </c>
       <c r="J2" s="21">
         <f>IFERROR(I2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>6.3192358316521322E-4</v>
+        <v>7.0213731462801432E-4</v>
       </c>
       <c r="K2" s="21">
         <f>IFERROR(J2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>6.3406854683723359E-4</v>
+        <v>7.0452060759692593E-4</v>
       </c>
       <c r="L2" s="21">
         <f>IFERROR(K2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>6.362207912458444E-4</v>
+        <v>7.0691199027316019E-4</v>
       </c>
       <c r="M2" s="21">
         <f>IFERROR(L2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>6.3838034110434304E-4</v>
+        <v>7.0931149011593656E-4</v>
       </c>
       <c r="N2" s="21">
         <f>IFERROR(M2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>6.4054722120991247E-4</v>
+        <v>7.1171913467768034E-4</v>
       </c>
       <c r="O2" s="21">
         <f>IFERROR(N2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>6.4272145644390542E-4</v>
+        <v>7.1413495160433922E-4</v>
       </c>
       <c r="P2" s="21">
         <f>IFERROR(O2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>6.4490307177213061E-4</v>
+        <v>7.1655896863570057E-4</v>
       </c>
       <c r="Q2" s="21">
         <f>IFERROR(P2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>6.470920922451392E-4</v>
+        <v>7.1899121360571015E-4</v>
       </c>
       <c r="R2" s="21">
         <f>IFERROR(Q2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>6.492885429985124E-4</v>
+        <v>7.2143171444279141E-4</v>
       </c>
       <c r="S2" s="21">
         <f>IFERROR(R2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>6.5149244925315013E-4</v>
+        <v>7.2388049917016667E-4</v>
       </c>
       <c r="T2" s="21">
         <f>IFERROR(S2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>6.5370383631556059E-4</v>
+        <v>7.2633759590617832E-4</v>
       </c>
       <c r="U2" s="21">
         <f>IFERROR(T2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>6.559227295781509E-4</v>
+        <v>7.2880303286461205E-4</v>
       </c>
       <c r="V2" s="21">
         <f>IFERROR(U2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>6.5814915451951883E-4</v>
+        <v>7.3127683835502082E-4</v>
       </c>
       <c r="W2" s="21">
         <f>IFERROR(V2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>6.6038313670474492E-4</v>
+        <v>7.3375904078304974E-4</v>
       </c>
       <c r="X2" s="21">
         <f>IFERROR(W2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>6.6262470178568642E-4</v>
+        <v>7.3624966865076249E-4</v>
       </c>
       <c r="Y2" s="21">
         <f>IFERROR(X2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>6.648738755012717E-4</v>
+        <v>7.3874875055696836E-4</v>
       </c>
       <c r="Z2" s="21">
         <f>IFERROR(Y2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>6.6713068367779574E-4</v>
+        <v>7.4125631519755071E-4</v>
       </c>
       <c r="AA2" s="21">
         <f>IFERROR(Z2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>6.693951522292169E-4</v>
+        <v>7.4377239136579651E-4</v>
       </c>
       <c r="AB2" s="21">
         <f>IFERROR(AA2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>6.7166730715745423E-4</v>
+        <v>7.4629700795272684E-4</v>
       </c>
       <c r="AC2" s="21">
         <f>IFERROR(AB2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>6.7394717455268615E-4</v>
+        <v>7.48830193947429E-4</v>
       </c>
       <c r="AD2" s="21">
         <f>IFERROR(AC2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>6.7623478059365011E-4</v>
+        <v>7.5137197843738886E-4</v>
       </c>
       <c r="AE2" s="21">
         <f>IFERROR(AD2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>6.7853015154794292E-4</v>
+        <v>7.5392239060882531E-4</v>
       </c>
       <c r="AF2" s="21">
         <f>IFERROR(AE2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>6.8083331377232273E-4</v>
+        <v>7.564814597470251E-4</v>
       </c>
       <c r="AG2" s="14"/>
     </row>
@@ -13966,127 +13966,127 @@
       </c>
       <c r="B3" s="13">
         <f>B5*Calibration!$C$27</f>
-        <v>2.9319976788482139E-4</v>
+        <v>3.2577751987202382E-4</v>
       </c>
       <c r="C3" s="13">
         <f>B3*(1+CAGR!$C$24)</f>
-        <v>2.954848797834626E-4</v>
+        <v>3.2831653309273629E-4</v>
       </c>
       <c r="D3" s="13">
         <f>C3*(1+CAGR!$C$24)</f>
-        <v>2.9778780116547065E-4</v>
+        <v>3.3087533462830082E-4</v>
       </c>
       <c r="E3" s="13">
         <f>D3*(1+CAGR!$C$24)</f>
-        <v>3.0010867083266881E-4</v>
+        <v>3.3345407870296543E-4</v>
       </c>
       <c r="F3" s="13">
         <f>E3*(1+CAGR!$C$24)</f>
-        <v>3.0244762866866044E-4</v>
+        <v>3.3605292074295615E-4</v>
       </c>
       <c r="G3" s="13">
         <f>F3*(1+CAGR!$C$24)</f>
-        <v>3.0480481564726023E-4</v>
+        <v>3.3867201738584476E-4</v>
       </c>
       <c r="H3" s="13">
         <f>G3*(1+CAGR!$C$24)</f>
-        <v>3.0718037384099082E-4</v>
+        <v>3.4131152648998986E-4</v>
       </c>
       <c r="I3" s="13">
         <f>H3*(1+CAGR!$C$24)</f>
-        <v>3.0957444642964598E-4</v>
+        <v>3.4397160714405112E-4</v>
       </c>
       <c r="J3" s="13">
         <f>I3*(1+CAGR!$C$24)</f>
-        <v>3.1198717770892023E-4</v>
+        <v>3.4665241967657802E-4</v>
       </c>
       <c r="K3" s="13">
         <f>J3*(1+CAGR!$C$24)</f>
-        <v>3.1441871309910582E-4</v>
+        <v>3.4935412566567314E-4</v>
       </c>
       <c r="L3" s="13">
         <f>K3*(1+CAGR!$C$24)</f>
-        <v>3.1686919915385764E-4</v>
+        <v>3.5207688794873071E-4</v>
       </c>
       <c r="M3" s="13">
         <f>L3*(1+CAGR!$C$24)</f>
-        <v>3.1933878356902619E-4</v>
+        <v>3.5482087063225135E-4</v>
       </c>
       <c r="N3" s="13">
         <f>M3*(1+CAGR!$C$24)</f>
-        <v>3.2182761519155959E-4</v>
+        <v>3.5758623910173289E-4</v>
       </c>
       <c r="O3" s="13">
         <f>N3*(1+CAGR!$C$24)</f>
-        <v>3.243358440284748E-4</v>
+        <v>3.603731600316387E-4</v>
       </c>
       <c r="P3" s="13">
         <f>O3*(1+CAGR!$C$24)</f>
-        <v>3.2686362125589898E-4</v>
+        <v>3.6318180139544335E-4</v>
       </c>
       <c r="Q3" s="13">
         <f>P3*(1+CAGR!$C$24)</f>
-        <v>3.2941109922818111E-4</v>
+        <v>3.6601233247575681E-4</v>
       </c>
       <c r="R3" s="13">
         <f>Q3*(1+CAGR!$C$24)</f>
-        <v>3.3197843148707467E-4</v>
+        <v>3.6886492387452739E-4</v>
       </c>
       <c r="S3" s="13">
         <f>R3*(1+CAGR!$C$24)</f>
-        <v>3.3456577277099194E-4</v>
+        <v>3.7173974752332438E-4</v>
       </c>
       <c r="T3" s="13">
         <f>S3*(1+CAGR!$C$24)</f>
-        <v>3.3717327902433052E-4</v>
+        <v>3.7463697669370055E-4</v>
       </c>
       <c r="U3" s="13">
         <f>T3*(1+CAGR!$C$24)</f>
-        <v>3.3980110740687222E-4</v>
+        <v>3.775567860076358E-4</v>
       </c>
       <c r="V3" s="13">
         <f>U3*(1+CAGR!$C$24)</f>
-        <v>3.4244941630325558E-4</v>
+        <v>3.8049935144806175E-4</v>
       </c>
       <c r="W3" s="13">
         <f>V3*(1+CAGR!$C$24)</f>
-        <v>3.4511836533252194E-4</v>
+        <v>3.8346485036946877E-4</v>
       </c>
       <c r="X3" s="13">
         <f>W3*(1+CAGR!$C$24)</f>
-        <v>3.4780811535773597E-4</v>
+        <v>3.8645346150859548E-4</v>
       </c>
       <c r="Y3" s="13">
         <f>X3*(1+CAGR!$C$24)</f>
-        <v>3.5051882849568142E-4</v>
+        <v>3.8946536499520152E-4</v>
       </c>
       <c r="Z3" s="13">
         <f>Y3*(1+CAGR!$C$24)</f>
-        <v>3.5325066812663198E-4</v>
+        <v>3.9250074236292439E-4</v>
       </c>
       <c r="AA3" s="13">
         <f>Z3*(1+CAGR!$C$24)</f>
-        <v>3.5600379890419874E-4</v>
+        <v>3.9555977656022078E-4</v>
       </c>
       <c r="AB3" s="13">
         <f>AA3*(1+CAGR!$C$24)</f>
-        <v>3.5877838676525402E-4</v>
+        <v>3.9864265196139334E-4</v>
       </c>
       <c r="AC3" s="13">
         <f>AB3*(1+CAGR!$C$24)</f>
-        <v>3.61574598939933E-4</v>
+        <v>4.0174955437770332E-4</v>
       </c>
       <c r="AD3" s="13">
         <f>AC3*(1+CAGR!$C$24)</f>
-        <v>3.6439260396171268E-4</v>
+        <v>4.0488067106856962E-4</v>
       </c>
       <c r="AE3" s="13">
         <f>AD3*(1+CAGR!$C$24)</f>
-        <v>3.6723257167757003E-4</v>
+        <v>4.0803619075285559E-4</v>
       </c>
       <c r="AF3" s="13">
         <f>AE3*(1+CAGR!$C$24)</f>
-        <v>3.7009467325821888E-4</v>
+        <v>4.1121630362024321E-4</v>
       </c>
       <c r="AG3" s="14"/>
     </row>
@@ -14096,127 +14096,127 @@
       </c>
       <c r="B4" s="14">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$3:$H$3,,MATCH($A4,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>2.5551255846750889E-4</v>
+        <v>2.8390284274167651E-4</v>
       </c>
       <c r="C4" s="14">
         <f>IFERROR(B4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>2.5806972763420987E-4</v>
+        <v>2.8674414181578868E-4</v>
       </c>
       <c r="D4" s="14">
         <f>IFERROR(C4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>2.606524889447426E-4</v>
+        <v>2.8961387660526953E-4</v>
       </c>
       <c r="E4" s="14">
         <f>IFERROR(D4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>2.6326109852523066E-4</v>
+        <v>2.9251233169470071E-4</v>
       </c>
       <c r="F4" s="14">
         <f>IFERROR(E4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>2.658958150651073E-4</v>
+        <v>2.954397945167859E-4</v>
       </c>
       <c r="G4" s="14">
         <f>IFERROR(F4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>2.6855689984276913E-4</v>
+        <v>2.9839655538085462E-4</v>
       </c>
       <c r="H4" s="14">
         <f>IFERROR(G4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>2.7124461675148638E-4</v>
+        <v>3.0138290750165157E-4</v>
       </c>
       <c r="I4" s="14">
         <f>IFERROR(H4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>2.7395923232557262E-4</v>
+        <v>3.0439914702841409E-4</v>
       </c>
       <c r="J4" s="14">
         <f>IFERROR(I4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>2.7670101576681631E-4</v>
+        <v>3.074455730742404E-4</v>
       </c>
       <c r="K4" s="14">
         <f>IFERROR(J4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>2.7947023897117681E-4</v>
+        <v>3.1052248774575208E-4</v>
       </c>
       <c r="L4" s="14">
         <f>IFERROR(K4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>2.8226717655574772E-4</v>
+        <v>3.1363019617305308E-4</v>
       </c>
       <c r="M4" s="14">
         <f>IFERROR(L4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>2.8509210588598995E-4</v>
+        <v>3.1676900653998888E-4</v>
       </c>
       <c r="N4" s="14">
         <f>IFERROR(M4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>2.8794530710323738E-4</v>
+        <v>3.1993923011470825E-4</v>
       </c>
       <c r="O4" s="14">
         <f>IFERROR(N4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>2.9082706315247778E-4</v>
+        <v>3.2314118128053094E-4</v>
       </c>
       <c r="P4" s="14">
         <f>IFERROR(O4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>2.9373765981041184E-4</v>
+        <v>3.2637517756712431E-4</v>
       </c>
       <c r="Q4" s="14">
         <f>IFERROR(P4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>2.9667738571379285E-4</v>
+        <v>3.2964153968199206E-4</v>
       </c>
       <c r="R4" s="14">
         <f>IFERROR(Q4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>2.9964653238805008E-4</v>
+        <v>3.3294059154227788E-4</v>
       </c>
       <c r="S4" s="14">
         <f>IFERROR(R4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.0264539427619881E-4</v>
+        <v>3.362726603068876E-4</v>
       </c>
       <c r="T4" s="14">
         <f>IFERROR(S4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.0567426876803937E-4</v>
+        <v>3.3963807640893264E-4</v>
       </c>
       <c r="U4" s="14">
         <f>IFERROR(T4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.0873345622964857E-4</v>
+        <v>3.4303717358849842E-4</v>
       </c>
       <c r="V4" s="14">
         <f>IFERROR(U4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.1182326003316641E-4</v>
+        <v>3.4647028892574046E-4</v>
       </c>
       <c r="W4" s="14">
         <f>IFERROR(V4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.1494398658688053E-4</v>
+        <v>3.4993776287431172E-4</v>
       </c>
       <c r="X4" s="14">
         <f>IFERROR(W4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.1809594536561219E-4</v>
+        <v>3.5343993929512469E-4</v>
       </c>
       <c r="Y4" s="14">
         <f>IFERROR(X4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.2127944894140602E-4</v>
+        <v>3.5697716549045112E-4</v>
       </c>
       <c r="Z4" s="14">
         <f>IFERROR(Y4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.2449481301452694E-4</v>
+        <v>3.6054979223836328E-4</v>
       </c>
       <c r="AA4" s="14">
         <f>IFERROR(Z4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.2774235644476759E-4</v>
+        <v>3.641581738275196E-4</v>
       </c>
       <c r="AB4" s="14">
         <f>IFERROR(AA4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.3102240128306877E-4</v>
+        <v>3.6780266809229869E-4</v>
       </c>
       <c r="AC4" s="14">
         <f>IFERROR(AB4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.3433527280345637E-4</v>
+        <v>3.714836364482849E-4</v>
       </c>
       <c r="AD4" s="14">
         <f>IFERROR(AC4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.3768129953529809E-4</v>
+        <v>3.7520144392810904E-4</v>
       </c>
       <c r="AE4" s="14">
         <f>IFERROR(AD4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.4106081329588291E-4</v>
+        <v>3.7895645921764769E-4</v>
       </c>
       <c r="AF4" s="14">
         <f>IFERROR(AE4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.4447414922332656E-4</v>
+        <v>3.8274905469258503E-4</v>
       </c>
       <c r="AG4" s="14"/>
     </row>
@@ -14226,127 +14226,127 @@
       </c>
       <c r="B5" s="14">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$3:$H$3,,MATCH($A5,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>2.8483542757721825E-4</v>
+        <v>3.1648380841913144E-4</v>
       </c>
       <c r="C5" s="14">
         <f>IFERROR(B5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>2.871498650723904E-4</v>
+        <v>3.1905540563598937E-4</v>
       </c>
       <c r="D5" s="14">
         <f>IFERROR(C5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>2.8948310858816406E-4</v>
+        <v>3.2164789843129344E-4</v>
       </c>
       <c r="E5" s="14">
         <f>IFERROR(D5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>2.9183531093333686E-4</v>
+        <v>3.2426145659259658E-4</v>
       </c>
       <c r="F5" s="14">
         <f>IFERROR(E5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>2.9420662615835822E-4</v>
+        <v>3.268962512870648E-4</v>
       </c>
       <c r="G5" s="14">
         <f>IFERROR(F5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>2.9659720956541841E-4</v>
+        <v>3.2955245507268726E-4</v>
       </c>
       <c r="H5" s="14">
         <f>IFERROR(G5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>2.9900721771861956E-4</v>
+        <v>3.3223024190957742E-4</v>
       </c>
       <c r="I5" s="14">
         <f>IFERROR(H5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.0143680845422938E-4</v>
+        <v>3.349297871713661E-4</v>
       </c>
       <c r="J5" s="14">
         <f>IFERROR(I5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.0388614089101816E-4</v>
+        <v>3.3765126765668697E-4</v>
       </c>
       <c r="K5" s="14">
         <f>IFERROR(J5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.0635537544067986E-4</v>
+        <v>3.4039486160075553E-4</v>
       </c>
       <c r="L5" s="14">
         <f>IFERROR(K5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.0884467381833773E-4</v>
+        <v>3.4316074868704201E-4</v>
       </c>
       <c r="M5" s="14">
         <f>IFERROR(L5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.1135419905313526E-4</v>
+        <v>3.4594911005903927E-4</v>
       </c>
       <c r="N5" s="14">
         <f>IFERROR(M5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.1388411549891344E-4</v>
+        <v>3.4876012833212611E-4</v>
       </c>
       <c r="O5" s="14">
         <f>IFERROR(N5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.1643458884497461E-4</v>
+        <v>3.5159398760552739E-4</v>
       </c>
       <c r="P5" s="14">
         <f>IFERROR(O5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.1900578612693365E-4</v>
+        <v>3.5445087347437076E-4</v>
       </c>
       <c r="Q5" s="14">
         <f>IFERROR(P5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.2159787573765765E-4</v>
+        <v>3.5733097304184187E-4</v>
       </c>
       <c r="R5" s="14">
         <f>IFERROR(Q5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.2421102743829418E-4</v>
+        <v>3.60234474931438E-4</v>
       </c>
       <c r="S5" s="14">
         <f>IFERROR(R5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.2684541236938932E-4</v>
+        <v>3.6316156929932153E-4</v>
       </c>
       <c r="T5" s="14">
         <f>IFERROR(S5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.2950120306209606E-4</v>
+        <v>3.6611244784677343E-4</v>
       </c>
       <c r="U5" s="14">
         <f>IFERROR(T5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.3217857344947354E-4</v>
+        <v>3.6908730383274839E-4</v>
       </c>
       <c r="V5" s="14">
         <f>IFERROR(U5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.3487769887787845E-4</v>
+        <v>3.720863320865316E-4</v>
       </c>
       <c r="W5" s="14">
         <f>IFERROR(V5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.3759875611844877E-4</v>
+        <v>3.7510972902049858E-4</v>
       </c>
       <c r="X5" s="14">
         <f>IFERROR(W5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.4034192337868078E-4</v>
+        <v>3.7815769264297857E-4</v>
       </c>
       <c r="Y5" s="14">
         <f>IFERROR(X5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.4310738031410036E-4</v>
+        <v>3.8123042257122257E-4</v>
       </c>
       <c r="Z5" s="14">
         <f>IFERROR(Y5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.458953080400289E-4</v>
+        <v>3.843281200444765E-4</v>
       </c>
       <c r="AA5" s="14">
         <f>IFERROR(Z5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.4870588914344495E-4</v>
+        <v>3.8745098793716102E-4</v>
       </c>
       <c r="AB5" s="14">
         <f>IFERROR(AA5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.5153930769494217E-4</v>
+        <v>3.9059923077215789E-4</v>
       </c>
       <c r="AC5" s="14">
         <f>IFERROR(AB5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.5439574926078446E-4</v>
+        <v>3.9377305473420489E-4</v>
       </c>
       <c r="AD5" s="14">
         <f>IFERROR(AC5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.5727540091505918E-4</v>
+        <v>3.9697266768339901E-4</v>
       </c>
       <c r="AE5" s="14">
         <f>IFERROR(AD5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.601784512519289E-4</v>
+        <v>4.0019827916880981E-4</v>
       </c>
       <c r="AF5" s="14">
         <f>IFERROR(AE5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.6310509039798284E-4</v>
+        <v>4.0345010044220302E-4</v>
       </c>
       <c r="AG5" s="14"/>
     </row>
@@ -14356,127 +14356,127 @@
       </c>
       <c r="B6" s="13">
         <f>B5*Calibration!$E$26</f>
-        <v>6.3159722517728049E-4</v>
+        <v>7.0177469464142289E-4</v>
       </c>
       <c r="C6" s="13">
         <f>B6*(1+CAGR!$C$27)</f>
-        <v>6.3159722517728049E-4</v>
+        <v>7.0177469464142289E-4</v>
       </c>
       <c r="D6" s="13">
         <f>C6*(1+CAGR!$C$27)</f>
-        <v>6.3159722517728049E-4</v>
+        <v>7.0177469464142289E-4</v>
       </c>
       <c r="E6" s="13">
         <f>D6*(1+CAGR!$C$27)</f>
-        <v>6.3159722517728049E-4</v>
+        <v>7.0177469464142289E-4</v>
       </c>
       <c r="F6" s="13">
         <f>E6*(1+CAGR!$C$27)</f>
-        <v>6.3159722517728049E-4</v>
+        <v>7.0177469464142289E-4</v>
       </c>
       <c r="G6" s="13">
         <f>F6*(1+CAGR!$C$27)</f>
-        <v>6.3159722517728049E-4</v>
+        <v>7.0177469464142289E-4</v>
       </c>
       <c r="H6" s="13">
         <f>G6*(1+CAGR!$C$27)</f>
-        <v>6.3159722517728049E-4</v>
+        <v>7.0177469464142289E-4</v>
       </c>
       <c r="I6" s="13">
         <f>H6*(1+CAGR!$C$27)</f>
-        <v>6.3159722517728049E-4</v>
+        <v>7.0177469464142289E-4</v>
       </c>
       <c r="J6" s="13">
         <f>I6*(1+CAGR!$C$27)</f>
-        <v>6.3159722517728049E-4</v>
+        <v>7.0177469464142289E-4</v>
       </c>
       <c r="K6" s="13">
         <f>J6*(1+CAGR!$C$27)</f>
-        <v>6.3159722517728049E-4</v>
+        <v>7.0177469464142289E-4</v>
       </c>
       <c r="L6" s="13">
         <f>K6*(1+CAGR!$C$27)</f>
-        <v>6.3159722517728049E-4</v>
+        <v>7.0177469464142289E-4</v>
       </c>
       <c r="M6" s="13">
         <f>L6*(1+CAGR!$C$27)</f>
-        <v>6.3159722517728049E-4</v>
+        <v>7.0177469464142289E-4</v>
       </c>
       <c r="N6" s="13">
         <f>M6*(1+CAGR!$C$27)</f>
-        <v>6.3159722517728049E-4</v>
+        <v>7.0177469464142289E-4</v>
       </c>
       <c r="O6" s="13">
         <f>N6*(1+CAGR!$C$27)</f>
-        <v>6.3159722517728049E-4</v>
+        <v>7.0177469464142289E-4</v>
       </c>
       <c r="P6" s="13">
         <f>O6*(1+CAGR!$C$27)</f>
-        <v>6.3159722517728049E-4</v>
+        <v>7.0177469464142289E-4</v>
       </c>
       <c r="Q6" s="13">
         <f>P6*(1+CAGR!$C$27)</f>
-        <v>6.3159722517728049E-4</v>
+        <v>7.0177469464142289E-4</v>
       </c>
       <c r="R6" s="13">
         <f>Q6*(1+CAGR!$C$27)</f>
-        <v>6.3159722517728049E-4</v>
+        <v>7.0177469464142289E-4</v>
       </c>
       <c r="S6" s="13">
         <f>R6*(1+CAGR!$C$27)</f>
-        <v>6.3159722517728049E-4</v>
+        <v>7.0177469464142289E-4</v>
       </c>
       <c r="T6" s="13">
         <f>S6*(1+CAGR!$C$27)</f>
-        <v>6.3159722517728049E-4</v>
+        <v>7.0177469464142289E-4</v>
       </c>
       <c r="U6" s="13">
         <f>T6*(1+CAGR!$C$27)</f>
-        <v>6.3159722517728049E-4</v>
+        <v>7.0177469464142289E-4</v>
       </c>
       <c r="V6" s="13">
         <f>U6*(1+CAGR!$C$27)</f>
-        <v>6.3159722517728049E-4</v>
+        <v>7.0177469464142289E-4</v>
       </c>
       <c r="W6" s="13">
         <f>V6*(1+CAGR!$C$27)</f>
-        <v>6.3159722517728049E-4</v>
+        <v>7.0177469464142289E-4</v>
       </c>
       <c r="X6" s="13">
         <f>W6*(1+CAGR!$C$27)</f>
-        <v>6.3159722517728049E-4</v>
+        <v>7.0177469464142289E-4</v>
       </c>
       <c r="Y6" s="13">
         <f>X6*(1+CAGR!$C$27)</f>
-        <v>6.3159722517728049E-4</v>
+        <v>7.0177469464142289E-4</v>
       </c>
       <c r="Z6" s="13">
         <f>Y6*(1+CAGR!$C$27)</f>
-        <v>6.3159722517728049E-4</v>
+        <v>7.0177469464142289E-4</v>
       </c>
       <c r="AA6" s="13">
         <f>Z6*(1+CAGR!$C$27)</f>
-        <v>6.3159722517728049E-4</v>
+        <v>7.0177469464142289E-4</v>
       </c>
       <c r="AB6" s="13">
         <f>AA6*(1+CAGR!$C$27)</f>
-        <v>6.3159722517728049E-4</v>
+        <v>7.0177469464142289E-4</v>
       </c>
       <c r="AC6" s="13">
         <f>AB6*(1+CAGR!$C$27)</f>
-        <v>6.3159722517728049E-4</v>
+        <v>7.0177469464142289E-4</v>
       </c>
       <c r="AD6" s="13">
         <f>AC6*(1+CAGR!$C$27)</f>
-        <v>6.3159722517728049E-4</v>
+        <v>7.0177469464142289E-4</v>
       </c>
       <c r="AE6" s="13">
         <f>AD6*(1+CAGR!$C$27)</f>
-        <v>6.3159722517728049E-4</v>
+        <v>7.0177469464142289E-4</v>
       </c>
       <c r="AF6" s="13">
         <f>AE6*(1+CAGR!$C$27)</f>
-        <v>6.3159722517728049E-4</v>
+        <v>7.0177469464142289E-4</v>
       </c>
       <c r="AG6" s="14"/>
     </row>
@@ -14486,127 +14486,127 @@
       </c>
       <c r="B7" s="14">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$3:$H$3,,MATCH($A7,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>2.6120121535980494E-4</v>
+        <v>2.9022357262200552E-4</v>
       </c>
       <c r="C7" s="14">
         <f>IFERROR(B7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>2.6361568474156881E-4</v>
+        <v>2.9290631637952095E-4</v>
       </c>
       <c r="D7" s="14">
         <f>IFERROR(C7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>2.660524727882265E-4</v>
+        <v>2.9561385865358505E-4</v>
       </c>
       <c r="E7" s="14">
         <f>IFERROR(D7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>2.6851178580713749E-4</v>
+        <v>2.9834642867459724E-4</v>
       </c>
       <c r="F7" s="14">
         <f>IFERROR(E7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>2.7099383201270751E-4</v>
+        <v>3.0110425779189721E-4</v>
       </c>
       <c r="G7" s="14">
         <f>IFERROR(F7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>2.7349882154401668E-4</v>
+        <v>3.0388757949335188E-4</v>
       </c>
       <c r="H7" s="14">
         <f>IFERROR(G7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>2.7602696648261086E-4</v>
+        <v>3.0669662942512315E-4</v>
       </c>
       <c r="I7" s="14">
         <f>IFERROR(H7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>2.7857848087045698E-4</v>
+        <v>3.0953164541161883E-4</v>
       </c>
       <c r="J7" s="14">
         <f>IFERROR(I7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>2.8115358072806478E-4</v>
+        <v>3.123928674756275E-4</v>
       </c>
       <c r="K7" s="14">
         <f>IFERROR(J7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>2.8375248407277586E-4</v>
+        <v>3.1528053785863982E-4</v>
       </c>
       <c r="L7" s="14">
         <f>IFERROR(K7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>2.8637541093722181E-4</v>
+        <v>3.1819490104135752E-4</v>
       </c>
       <c r="M7" s="14">
         <f>IFERROR(L7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>2.8902258338795296E-4</v>
+        <v>3.2113620376439216E-4</v>
       </c>
       <c r="N7" s="14">
         <f>IFERROR(M7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>2.9169422554423943E-4</v>
+        <v>3.2410469504915487E-4</v>
       </c>
       <c r="O7" s="14">
         <f>IFERROR(N7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>2.9439056359704572E-4</v>
+        <v>3.2710062621893964E-4</v>
       </c>
       <c r="P7" s="14">
         <f>IFERROR(O7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>2.9711182582818104E-4</v>
+        <v>3.3012425092020112E-4</v>
       </c>
       <c r="Q7" s="14">
         <f>IFERROR(P7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>2.9985824262962637E-4</v>
+        <v>3.3317582514402928E-4</v>
       </c>
       <c r="R7" s="14">
         <f>IFERROR(Q7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.0263004652304032E-4</v>
+        <v>3.3625560724782254E-4</v>
       </c>
       <c r="S7" s="14">
         <f>IFERROR(R7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.0542747217944522E-4</v>
+        <v>3.3936385797716135E-4</v>
       </c>
       <c r="T7" s="14">
         <f>IFERROR(S7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.0825075643909532E-4</v>
+        <v>3.4250084048788369E-4</v>
       </c>
       <c r="U7" s="14">
         <f>IFERROR(T7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.1110013833152844E-4</v>
+        <v>3.4566682036836494E-4</v>
       </c>
       <c r="V7" s="14">
         <f>IFERROR(U7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.1397585909580315E-4</v>
+        <v>3.4886206566200353E-4</v>
       </c>
       <c r="W7" s="14">
         <f>IFERROR(V7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.1687816220092298E-4</v>
+        <v>3.5208684688991441E-4</v>
       </c>
       <c r="X7" s="14">
         <f>IFERROR(W7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.1980729336644921E-4</v>
+        <v>3.5534143707383249E-4</v>
       </c>
       <c r="Y7" s="14">
         <f>IFERROR(X7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.2276350058330468E-4</v>
+        <v>3.5862611175922743E-4</v>
       </c>
       <c r="Z7" s="14">
         <f>IFERROR(Y7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.2574703413476932E-4</v>
+        <v>3.6194114903863257E-4</v>
       </c>
       <c r="AA7" s="14">
         <f>IFERROR(Z7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.2875814661767022E-4</v>
+        <v>3.6528682957518913E-4</v>
       </c>
       <c r="AB7" s="14">
         <f>IFERROR(AA7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.3179709296376732E-4</v>
+        <v>3.6866343662640818E-4</v>
       </c>
       <c r="AC7" s="14">
         <f>IFERROR(AB7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.3486413046133698E-4</v>
+        <v>3.7207125606815222E-4</v>
       </c>
       <c r="AD7" s="14">
         <f>IFERROR(AC7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.379595187769547E-4</v>
+        <v>3.7551057641883856E-4</v>
       </c>
       <c r="AE7" s="14">
         <f>IFERROR(AD7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.4108351997747969E-4</v>
+        <v>3.7898168886386631E-4</v>
       </c>
       <c r="AF7" s="14">
         <f>IFERROR(AE7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.4423639855224225E-4</v>
+        <v>3.8248488728026916E-4</v>
       </c>
       <c r="AG7" s="14"/>
     </row>
@@ -14863,127 +14863,127 @@
       </c>
       <c r="B2" s="13">
         <f>B5*Calibration!B32</f>
-        <v>5.2559933540910638E-4</v>
+        <v>1.3831561458134379E-3</v>
       </c>
       <c r="C2" s="13">
         <f>B2*(1+CAGR!$C$30)</f>
-        <v>5.312076378910423E-4</v>
+        <v>1.3979148365553746E-3</v>
       </c>
       <c r="D2" s="13">
         <f>C2*(1+CAGR!$C$30)</f>
-        <v>5.3687578264181293E-4</v>
+        <v>1.4128310069521394E-3</v>
       </c>
       <c r="E2" s="13">
         <f>D2*(1+CAGR!$C$30)</f>
-        <v>5.4260440819636725E-4</v>
+        <v>1.4279063373588614E-3</v>
       </c>
       <c r="F2" s="13">
         <f>E2*(1+CAGR!$C$30)</f>
-        <v>5.4839415990301369E-4</v>
+        <v>1.4431425260605624E-3</v>
       </c>
       <c r="G2" s="13">
         <f>F2*(1+CAGR!$C$30)</f>
-        <v>5.5424568999612033E-4</v>
+        <v>1.4585412894634747E-3</v>
       </c>
       <c r="H2" s="13">
         <f>G2*(1+CAGR!$C$30)</f>
-        <v>5.6015965766959182E-4</v>
+        <v>1.4741043622883998E-3</v>
       </c>
       <c r="I2" s="13">
         <f>H2*(1+CAGR!$C$30)</f>
-        <v>5.6613672915112919E-4</v>
+        <v>1.4898334977661296E-3</v>
       </c>
       <c r="J2" s="13">
         <f>I2*(1+CAGR!$C$30)</f>
-        <v>5.7217757777728283E-4</v>
+        <v>1.5057304678349551E-3</v>
       </c>
       <c r="K2" s="13">
         <f>J2*(1+CAGR!$C$30)</f>
-        <v>5.782828840693061E-4</v>
+        <v>1.5217970633402793E-3</v>
       </c>
       <c r="L2" s="13">
         <f>K2*(1+CAGR!$C$30)</f>
-        <v>5.8445333580981796E-4</v>
+        <v>1.538035094236363E-3</v>
       </c>
       <c r="M2" s="13">
         <f>L2*(1+CAGR!$C$30)</f>
-        <v>5.9068962812028412E-4</v>
+        <v>1.5544463897902213E-3</v>
       </c>
       <c r="N2" s="13">
         <f>M2*(1+CAGR!$C$30)</f>
-        <v>5.9699246353932495E-4</v>
+        <v>1.571032798787697E-3</v>
       </c>
       <c r="O2" s="13">
         <f>N2*(1+CAGR!$C$30)</f>
-        <v>6.0336255210185824E-4</v>
+        <v>1.5877961897417321E-3</v>
       </c>
       <c r="P2" s="13">
         <f>O2*(1+CAGR!$C$30)</f>
-        <v>6.0980061141908742E-4</v>
+        <v>1.6047384511028615E-3</v>
       </c>
       <c r="Q2" s="13">
         <f>P2*(1+CAGR!$C$30)</f>
-        <v>6.1630736675934248E-4</v>
+        <v>1.6218614914719539E-3</v>
       </c>
       <c r="R2" s="13">
         <f>Q2*(1+CAGR!$C$30)</f>
-        <v>6.2288355112978403E-4</v>
+        <v>1.6391672398152213E-3</v>
       </c>
       <c r="S2" s="13">
         <f>R2*(1+CAGR!$C$30)</f>
-        <v>6.2952990535897874E-4</v>
+        <v>1.6566576456815232E-3</v>
       </c>
       <c r="T2" s="13">
         <f>S2*(1+CAGR!$C$30)</f>
-        <v>6.3624717818035626E-4</v>
+        <v>1.6743346794219904E-3</v>
       </c>
       <c r="U2" s="13">
         <f>T2*(1+CAGR!$C$30)</f>
-        <v>6.4303612631655632E-4</v>
+        <v>1.6922003324119906E-3</v>
       </c>
       <c r="V2" s="13">
         <f>U2*(1+CAGR!$C$30)</f>
-        <v>6.4989751456467611E-4</v>
+        <v>1.7102566172754639E-3</v>
       </c>
       <c r="W2" s="13">
         <f>V2*(1+CAGR!$C$30)</f>
-        <v>6.5683211588242723E-4</v>
+        <v>1.728505568111651E-3</v>
       </c>
       <c r="X2" s="13">
         <f>W2*(1+CAGR!$C$30)</f>
-        <v>6.638407114752116E-4</v>
+        <v>1.7469492407242416E-3</v>
       </c>
       <c r="Y2" s="13">
         <f>X2*(1+CAGR!$C$30)</f>
-        <v>6.709240908841272E-4</v>
+        <v>1.7655897128529667E-3</v>
       </c>
       <c r="Z2" s="13">
         <f>Y2*(1+CAGR!$C$30)</f>
-        <v>6.7808305207491199E-4</v>
+        <v>1.7844290844076635E-3</v>
       </c>
       <c r="AA2" s="13">
         <f>Z2*(1+CAGR!$C$30)</f>
-        <v>6.8531840152783775E-4</v>
+        <v>1.8034694777048367E-3</v>
       </c>
       <c r="AB2" s="13">
         <f>AA2*(1+CAGR!$C$30)</f>
-        <v>6.9263095432856253E-4</v>
+        <v>1.8227130377067441E-3</v>
       </c>
       <c r="AC2" s="13">
         <f>AB2*(1+CAGR!$C$30)</f>
-        <v>7.0002153425995268E-4</v>
+        <v>1.8421619322630341E-3</v>
       </c>
       <c r="AD2" s="13">
         <f>AC2*(1+CAGR!$C$30)</f>
-        <v>7.0749097389488473E-4</v>
+        <v>1.8618183523549604E-3</v>
       </c>
       <c r="AE2" s="13">
         <f>AD2*(1+CAGR!$C$30)</f>
-        <v>7.1504011469003732E-4</v>
+        <v>1.881684512342204E-3</v>
       </c>
       <c r="AF2" s="13">
         <f>AE2*(1+CAGR!$C$30)</f>
-        <v>7.2266980708068419E-4</v>
+        <v>1.9017626502123273E-3</v>
       </c>
       <c r="AG2" s="14"/>
     </row>
@@ -15253,127 +15253,127 @@
       </c>
       <c r="B5" s="14">
         <f>'SYFAFE psgr'!E4*(1+CAGR!$C$33)</f>
-        <v>1.6356106527100811E-4</v>
+        <v>4.3042385597633716E-4</v>
       </c>
       <c r="C5" s="14">
         <f>B5*(1+CAGR!$C$33)</f>
-        <v>1.6530631087257168E-4</v>
+        <v>4.350166075593992E-4</v>
       </c>
       <c r="D5" s="14">
         <f>C5*(1+CAGR!$C$33)</f>
-        <v>1.6707017876792341E-4</v>
+        <v>4.3965836517874586E-4</v>
       </c>
       <c r="E5" s="14">
         <f>D5*(1+CAGR!$C$33)</f>
-        <v>1.6885286766252089E-4</v>
+        <v>4.4434965174347605E-4</v>
       </c>
       <c r="F5" s="14">
         <f>E5*(1+CAGR!$C$33)</f>
-        <v>1.7065457838206857E-4</v>
+        <v>4.4909099574228574E-4</v>
       </c>
       <c r="G5" s="14">
         <f>F5*(1+CAGR!$C$33)</f>
-        <v>1.7247551389514134E-4</v>
+        <v>4.5388293130300359E-4</v>
       </c>
       <c r="H5" s="14">
         <f>G5*(1+CAGR!$C$33)</f>
-        <v>1.7431587933604967E-4</v>
+        <v>4.5872599825276235E-4</v>
       </c>
       <c r="I5" s="14">
         <f>H5*(1+CAGR!$C$33)</f>
-        <v>1.7617588202794858E-4</v>
+        <v>4.636207421788121E-4</v>
       </c>
       <c r="J5" s="14">
         <f>I5*(1+CAGR!$C$33)</f>
-        <v>1.7805573150619334E-4</v>
+        <v>4.6856771448998251E-4</v>
       </c>
       <c r="K5" s="14">
         <f>J5*(1+CAGR!$C$33)</f>
-        <v>1.7995563954194426E-4</v>
+        <v>4.7356747247880075E-4</v>
       </c>
       <c r="L5" s="14">
         <f>K5*(1+CAGR!$C$33)</f>
-        <v>1.8187582016602344E-4</v>
+        <v>4.786205793842723E-4</v>
       </c>
       <c r="M5" s="14">
         <f>L5*(1+CAGR!$C$33)</f>
-        <v>1.8381648969302599E-4</v>
+        <v>4.8372760445533164E-4</v>
       </c>
       <c r="N5" s="14">
         <f>M5*(1+CAGR!$C$33)</f>
-        <v>1.8577786674568863E-4</v>
+        <v>4.8888912301497012E-4</v>
       </c>
       <c r="O5" s="14">
         <f>N5*(1+CAGR!$C$33)</f>
-        <v>1.8776017227951818E-4</v>
+        <v>4.9410571652504795E-4</v>
       </c>
       <c r="P5" s="14">
         <f>O5*(1+CAGR!$C$33)</f>
-        <v>1.8976362960768304E-4</v>
+        <v>4.993779726517975E-4</v>
       </c>
       <c r="Q5" s="14">
         <f>P5*(1+CAGR!$C$33)</f>
-        <v>1.9178846442616997E-4</v>
+        <v>5.0470648533202625E-4</v>
       </c>
       <c r="R5" s="14">
         <f>Q5*(1+CAGR!$C$33)</f>
-        <v>1.9383490483920962E-4</v>
+        <v>5.1009185484002532E-4</v>
       </c>
       <c r="S5" s="14">
         <f>R5*(1+CAGR!$C$33)</f>
-        <v>1.9590318138497316E-4</v>
+        <v>5.1553468785519251E-4</v>
       </c>
       <c r="T5" s="14">
         <f>S5*(1+CAGR!$C$33)</f>
-        <v>1.9799352706154316E-4</v>
+        <v>5.2103559753037673E-4</v>
       </c>
       <c r="U5" s="14">
         <f>T5*(1+CAGR!$C$33)</f>
-        <v>2.0010617735316161E-4</v>
+        <v>5.2659520356095155E-4</v>
       </c>
       <c r="V5" s="14">
         <f>U5*(1+CAGR!$C$33)</f>
-        <v>2.022413702567579E-4</v>
+        <v>5.3221413225462602E-4</v>
       </c>
       <c r="W5" s="14">
         <f>V5*(1+CAGR!$C$33)</f>
-        <v>2.0439934630876006E-4</v>
+        <v>5.3789301660200016E-4</v>
       </c>
       <c r="X5" s="14">
         <f>W5*(1+CAGR!$C$33)</f>
-        <v>2.0658034861219192E-4</v>
+        <v>5.4363249634787345E-4</v>
       </c>
       <c r="Y5" s="14">
         <f>X5*(1+CAGR!$C$33)</f>
-        <v>2.087846228640594E-4</v>
+        <v>5.4943321806331415E-4</v>
       </c>
       <c r="Z5" s="14">
         <f>Y5*(1+CAGR!$C$33)</f>
-        <v>2.1101241738302919E-4</v>
+        <v>5.552958352184978E-4</v>
       </c>
       <c r="AA5" s="14">
         <f>Z5*(1+CAGR!$C$33)</f>
-        <v>2.1326398313740256E-4</v>
+        <v>5.6122100825632248E-4</v>
       </c>
       <c r="AB5" s="14">
         <f>AA5*(1+CAGR!$C$33)</f>
-        <v>2.1553957377338785E-4</v>
+        <v>5.6720940466680999E-4</v>
       </c>
       <c r="AC5" s="14">
         <f>AB5*(1+CAGR!$C$33)</f>
-        <v>2.1783944564367441E-4</v>
+        <v>5.7326169906230092E-4</v>
       </c>
       <c r="AD5" s="14">
         <f>AC5*(1+CAGR!$C$33)</f>
-        <v>2.201638578363117E-4</v>
+        <v>5.7937857325345162E-4</v>
       </c>
       <c r="AE5" s="14">
         <f>AD5*(1+CAGR!$C$33)</f>
-        <v>2.2251307220389629E-4</v>
+        <v>5.8556071632604259E-4</v>
       </c>
       <c r="AF5" s="14">
         <f>AE5*(1+CAGR!$C$33)</f>
-        <v>2.2488735339307051E-4</v>
+        <v>5.9180882471860632E-4</v>
       </c>
       <c r="AG5" s="14"/>
     </row>
@@ -15643,127 +15643,127 @@
       </c>
       <c r="B8" s="13">
         <f>B5*Calibration!D32</f>
-        <v>4.9068319581302422E-4</v>
+        <v>1.2912715679290112E-3</v>
       </c>
       <c r="C8" s="13">
         <f>B8*(1+CAGR!$C$36)</f>
-        <v>4.9591893261771497E-4</v>
+        <v>1.3050498226781974E-3</v>
       </c>
       <c r="D8" s="13">
         <f>C8*(1+CAGR!$C$36)</f>
-        <v>5.0121053630377015E-4</v>
+        <v>1.3189750955362373E-3</v>
       </c>
       <c r="E8" s="13">
         <f>D8*(1+CAGR!$C$36)</f>
-        <v>5.065586029875626E-4</v>
+        <v>1.333048955230428E-3</v>
       </c>
       <c r="F8" s="13">
         <f>E8*(1+CAGR!$C$36)</f>
-        <v>5.1196373514620567E-4</v>
+        <v>1.3472729872268572E-3</v>
       </c>
       <c r="G8" s="13">
         <f>F8*(1+CAGR!$C$36)</f>
-        <v>5.1742654168542403E-4</v>
+        <v>1.3616487939090106E-3</v>
       </c>
       <c r="H8" s="13">
         <f>G8*(1+CAGR!$C$36)</f>
-        <v>5.2294763800814898E-4</v>
+        <v>1.3761779947582869E-3</v>
       </c>
       <c r="I8" s="13">
         <f>H8*(1+CAGR!$C$36)</f>
-        <v>5.285276460838457E-4</v>
+        <v>1.3908622265364362E-3</v>
       </c>
       <c r="J8" s="13">
         <f>I8*(1+CAGR!$C$36)</f>
-        <v>5.3416719451857995E-4</v>
+        <v>1.4057031434699474E-3</v>
       </c>
       <c r="K8" s="13">
         <f>J8*(1+CAGR!$C$36)</f>
-        <v>5.3986691862583269E-4</v>
+        <v>1.4207024174364021E-3</v>
       </c>
       <c r="L8" s="13">
         <f>K8*(1+CAGR!$C$36)</f>
-        <v>5.4562746049807026E-4</v>
+        <v>1.4358617381528167E-3</v>
       </c>
       <c r="M8" s="13">
         <f>L8*(1+CAGR!$C$36)</f>
-        <v>5.5144946907907796E-4</v>
+        <v>1.4511828133659949E-3</v>
       </c>
       <c r="N8" s="13">
         <f>M8*(1+CAGR!$C$36)</f>
-        <v>5.5733360023706591E-4</v>
+        <v>1.4666673690449104E-3</v>
       </c>
       <c r="O8" s="13">
         <f>N8*(1+CAGR!$C$36)</f>
-        <v>5.6328051683855458E-4</v>
+        <v>1.4823171495751439E-3</v>
       </c>
       <c r="P8" s="13">
         <f>O8*(1+CAGR!$C$36)</f>
-        <v>5.6929088882304909E-4</v>
+        <v>1.4981339179553927E-3</v>
       </c>
       <c r="Q8" s="13">
         <f>P8*(1+CAGR!$C$36)</f>
-        <v>5.753653932785099E-4</v>
+        <v>1.514119455996079E-3</v>
       </c>
       <c r="R8" s="13">
         <f>Q8*(1+CAGR!$C$36)</f>
-        <v>5.8150471451762881E-4</v>
+        <v>1.5302755645200763E-3</v>
       </c>
       <c r="S8" s="13">
         <f>R8*(1+CAGR!$C$36)</f>
-        <v>5.8770954415491943E-4</v>
+        <v>1.546604063565578E-3</v>
       </c>
       <c r="T8" s="13">
         <f>S8*(1+CAGR!$C$36)</f>
-        <v>5.9398058118462942E-4</v>
+        <v>1.5631067925911306E-3</v>
       </c>
       <c r="U8" s="13">
         <f>T8*(1+CAGR!$C$36)</f>
-        <v>6.0031853205948476E-4</v>
+        <v>1.5797856106828552E-3</v>
       </c>
       <c r="V8" s="13">
         <f>U8*(1+CAGR!$C$36)</f>
-        <v>6.067241107702737E-4</v>
+        <v>1.5966423967638786E-3</v>
       </c>
       <c r="W8" s="13">
         <f>V8*(1+CAGR!$C$36)</f>
-        <v>6.1319803892628019E-4</v>
+        <v>1.6136790498060009E-3</v>
       </c>
       <c r="X8" s="13">
         <f>W8*(1+CAGR!$C$36)</f>
-        <v>6.1974104583657568E-4</v>
+        <v>1.6308974890436208E-3</v>
       </c>
       <c r="Y8" s="13">
         <f>X8*(1+CAGR!$C$36)</f>
-        <v>6.2635386859217807E-4</v>
+        <v>1.6482996541899431E-3</v>
       </c>
       <c r="Z8" s="13">
         <f>Y8*(1+CAGR!$C$36)</f>
-        <v>6.3303725214908745E-4</v>
+        <v>1.665887505655494E-3</v>
       </c>
       <c r="AA8" s="13">
         <f>Z8*(1+CAGR!$C$36)</f>
-        <v>6.3979194941220761E-4</v>
+        <v>1.6836630247689681E-3</v>
       </c>
       <c r="AB8" s="13">
         <f>AA8*(1+CAGR!$C$36)</f>
-        <v>6.4661872132016338E-4</v>
+        <v>1.7016282140004308E-3</v>
       </c>
       <c r="AC8" s="13">
         <f>AB8*(1+CAGR!$C$36)</f>
-        <v>6.5351833693102308E-4</v>
+        <v>1.7197850971869036E-3</v>
       </c>
       <c r="AD8" s="13">
         <f>AC8*(1+CAGR!$C$36)</f>
-        <v>6.6049157350893492E-4</v>
+        <v>1.7381357197603557E-3</v>
       </c>
       <c r="AE8" s="13">
         <f>AD8*(1+CAGR!$C$36)</f>
-        <v>6.6753921661168874E-4</v>
+        <v>1.7566821489781287E-3</v>
       </c>
       <c r="AF8" s="13">
         <f>AE8*(1+CAGR!$C$36)</f>
-        <v>6.7466206017921136E-4</v>
+        <v>1.7754264741558199E-3</v>
       </c>
       <c r="AG8" s="14"/>
     </row>
@@ -15890,127 +15890,127 @@
       </c>
       <c r="B2" s="13">
         <f>B5*Calibration!$B$32</f>
-        <v>1.7413380181677545E-4</v>
+        <v>4.5824684688625117E-4</v>
       </c>
       <c r="C2" s="13">
         <f>B2*(1+CAGR!$C$37)</f>
-        <v>1.759918616869574E-4</v>
+        <v>4.631364781235721E-4</v>
       </c>
       <c r="D2" s="13">
         <f>C2*(1+CAGR!$C$37)</f>
-        <v>1.7786974761299504E-4</v>
+        <v>4.680782831920922E-4</v>
       </c>
       <c r="E2" s="13">
         <f>D2*(1+CAGR!$C$37)</f>
-        <v>1.7976767114484811E-4</v>
+        <v>4.7307281880223191E-4</v>
       </c>
       <c r="F2" s="13">
         <f>E2*(1+CAGR!$C$37)</f>
-        <v>1.8168584608977792E-4</v>
+        <v>4.7812064760467871E-4</v>
       </c>
       <c r="G2" s="13">
         <f>F2*(1+CAGR!$C$37)</f>
-        <v>1.8362448853643327E-4</v>
+        <v>4.8322233825377173E-4</v>
       </c>
       <c r="H2" s="13">
         <f>G2*(1+CAGR!$C$37)</f>
-        <v>1.855838168791937E-4</v>
+        <v>4.8837846547156226E-4</v>
       </c>
       <c r="I2" s="13">
         <f>H2*(1+CAGR!$C$37)</f>
-        <v>1.8756405184277219E-4</v>
+        <v>4.9358961011255825E-4</v>
       </c>
       <c r="J2" s="13">
         <f>I2*(1+CAGR!$C$37)</f>
-        <v>1.8956541650708063E-4</v>
+        <v>4.9885635922915944E-4</v>
       </c>
       <c r="K2" s="13">
         <f>J2*(1+CAGR!$C$37)</f>
-        <v>1.9158813633236044E-4</v>
+        <v>5.0417930613779046E-4</v>
       </c>
       <c r="L2" s="13">
         <f>K2*(1+CAGR!$C$37)</f>
-        <v>1.9363243918458137E-4</v>
+        <v>5.0955905048574029E-4</v>
       </c>
       <c r="M2" s="13">
         <f>L2*(1+CAGR!$C$37)</f>
-        <v>1.9569855536111144E-4</v>
+        <v>5.1499619831871409E-4</v>
       </c>
       <c r="N2" s="13">
         <f>M2*(1+CAGR!$C$37)</f>
-        <v>1.9778671761666057E-4</v>
+        <v>5.2049136214910659E-4</v>
       </c>
       <c r="O2" s="13">
         <f>N2*(1+CAGR!$C$37)</f>
-        <v>1.9989716118950127E-4</v>
+        <v>5.2604516102500317E-4</v>
       </c>
       <c r="P2" s="13">
         <f>O2*(1+CAGR!$C$37)</f>
-        <v>2.0203012382796889E-4</v>
+        <v>5.3165822059991796E-4</v>
       </c>
       <c r="Q2" s="13">
         <f>P2*(1+CAGR!$C$37)</f>
-        <v>2.0418584581724481E-4</v>
+        <v>5.3733117320327567E-4</v>
       </c>
       <c r="R2" s="13">
         <f>Q2*(1+CAGR!$C$37)</f>
-        <v>2.0636457000642537E-4</v>
+        <v>5.4306465791164552E-4</v>
       </c>
       <c r="S2" s="13">
         <f>R2*(1+CAGR!$C$37)</f>
-        <v>2.0856654183587953E-4</v>
+        <v>5.4885932062073543E-4</v>
       </c>
       <c r="T2" s="13">
         <f>S2*(1+CAGR!$C$37)</f>
-        <v>2.107920093648986E-4</v>
+        <v>5.5471581411815397E-4</v>
       </c>
       <c r="U2" s="13">
         <f>T2*(1+CAGR!$C$37)</f>
-        <v>2.1304122329964084E-4</v>
+        <v>5.6063479815694935E-4</v>
       </c>
       <c r="V2" s="13">
         <f>U2*(1+CAGR!$C$37)</f>
-        <v>2.1531443702137447E-4</v>
+        <v>5.6661693952993252E-4</v>
       </c>
       <c r="W2" s="13">
         <f>V2*(1+CAGR!$C$37)</f>
-        <v>2.176119066150217E-4</v>
+        <v>5.7266291214479366E-4</v>
       </c>
       <c r="X2" s="13">
         <f>W2*(1+CAGR!$C$37)</f>
-        <v>2.1993389089800772E-4</v>
+        <v>5.7877339710002006E-4</v>
       </c>
       <c r="Y2" s="13">
         <f>X2*(1+CAGR!$C$37)</f>
-        <v>2.2228065144941719E-4</v>
+        <v>5.8494908276162392E-4</v>
       </c>
       <c r="Z2" s="13">
         <f>Y2*(1+CAGR!$C$37)</f>
-        <v>2.2465245263946206E-4</v>
+        <v>5.9119066484068935E-4</v>
       </c>
       <c r="AA2" s="13">
         <f>Z2*(1+CAGR!$C$37)</f>
-        <v>2.2704956165926367E-4</v>
+        <v>5.9749884647174623E-4</v>
       </c>
       <c r="AB2" s="13">
         <f>AA2*(1+CAGR!$C$37)</f>
-        <v>2.2947224855095273E-4</v>
+        <v>6.038743382919806E-4</v>
       </c>
       <c r="AC2" s="13">
         <f>AB2*(1+CAGR!$C$37)</f>
-        <v>2.3192078623809044E-4</v>
+        <v>6.1031785852129039E-4</v>
       </c>
       <c r="AD2" s="13">
         <f>AC2*(1+CAGR!$C$37)</f>
-        <v>2.3439545055641423E-4</v>
+        <v>6.1683013304319513E-4</v>
       </c>
       <c r="AE2" s="13">
         <f>AD2*(1+CAGR!$C$37)</f>
-        <v>2.3689652028491157E-4</v>
+        <v>6.2341189548660917E-4</v>
       </c>
       <c r="AF2" s="13">
         <f>AE2*(1+CAGR!$C$37)</f>
-        <v>2.3942427717722525E-4</v>
+        <v>6.3006388730848725E-4</v>
       </c>
       <c r="AG2" s="14"/>
     </row>
@@ -16280,127 +16280,127 @@
       </c>
       <c r="B5" s="14">
         <f>'SYFAFE frgt'!E4*(1+CAGR!$C$40)</f>
-        <v>5.4188634204937654E-5</v>
+        <v>1.4260166896036224E-4</v>
       </c>
       <c r="C5" s="14">
         <f>B5*(1+CAGR!$C$40)</f>
-        <v>5.4766843177496042E-5</v>
+        <v>1.4412327151972642E-4</v>
       </c>
       <c r="D5" s="14">
         <f>C5*(1+CAGR!$C$40)</f>
-        <v>5.5351221813136962E-5</v>
+        <v>1.4566111003457095E-4</v>
       </c>
       <c r="E5" s="14">
         <f>D5*(1+CAGR!$C$40)</f>
-        <v>5.5941835944015153E-5</v>
+        <v>1.472153577474083E-4</v>
       </c>
       <c r="F5" s="14">
         <f>E5*(1+CAGR!$C$40)</f>
-        <v>5.6538752104734177E-5</v>
+        <v>1.4878618974930045E-4</v>
       </c>
       <c r="G5" s="14">
         <f>F5*(1+CAGR!$C$40)</f>
-        <v>5.7142037539841769E-5</v>
+        <v>1.5037378299958358E-4</v>
       </c>
       <c r="H5" s="14">
         <f>G5*(1+CAGR!$C$40)</f>
-        <v>5.7751760211405141E-5</v>
+        <v>1.5197831634580297E-4</v>
       </c>
       <c r="I5" s="14">
         <f>H5*(1+CAGR!$C$40)</f>
-        <v>5.836798880666714E-5</v>
+        <v>1.5359997054386086E-4</v>
       </c>
       <c r="J5" s="14">
         <f>I5*(1+CAGR!$C$40)</f>
-        <v>5.8990792745784086E-5</v>
+        <v>1.5523892827837914E-4</v>
       </c>
       <c r="K5" s="14">
         <f>J5*(1+CAGR!$C$40)</f>
-        <v>5.9620242189646188E-5</v>
+        <v>1.5689537418327941E-4</v>
       </c>
       <c r="L5" s="14">
         <f>K5*(1+CAGR!$C$40)</f>
-        <v>6.0256408047781369E-5</v>
+        <v>1.5856949486258253E-4</v>
       </c>
       <c r="M5" s="14">
         <f>L5*(1+CAGR!$C$40)</f>
-        <v>6.0899361986343489E-5</v>
+        <v>1.6026147891143021E-4</v>
       </c>
       <c r="N5" s="14">
         <f>M5*(1+CAGR!$C$40)</f>
-        <v>6.1549176436185747E-5</v>
+        <v>1.619715169373309E-4</v>
       </c>
       <c r="O5" s="14">
         <f>N5*(1+CAGR!$C$40)</f>
-        <v>6.2205924601020264E-5</v>
+        <v>1.6369980158163227E-4</v>
       </c>
       <c r="P5" s="14">
         <f>O5*(1+CAGR!$C$40)</f>
-        <v>6.2869680465664715E-5</v>
+        <v>1.6544652754122295E-4</v>
       </c>
       <c r="Q5" s="14">
         <f>P5*(1+CAGR!$C$40)</f>
-        <v>6.3540518804376973E-5</v>
+        <v>1.6721189159046572E-4</v>
       </c>
       <c r="R5" s="14">
         <f>Q5*(1+CAGR!$C$40)</f>
-        <v>6.4218515189278622E-5</v>
+        <v>1.6899609260336482E-4</v>
       </c>
       <c r="S5" s="14">
         <f>R5*(1+CAGR!$C$40)</f>
-        <v>6.4903745998868485E-5</v>
+        <v>1.7079933157596971E-4</v>
       </c>
       <c r="T5" s="14">
         <f>S5*(1+CAGR!$C$40)</f>
-        <v>6.5596288426626834E-5</v>
+        <v>1.7262181164901799E-4</v>
       </c>
       <c r="U5" s="14">
         <f>T5*(1+CAGR!$C$40)</f>
-        <v>6.6296220489711521E-5</v>
+        <v>1.7446373813081981E-4</v>
       </c>
       <c r="V5" s="14">
         <f>U5*(1+CAGR!$C$40)</f>
-        <v>6.7003621037746886E-5</v>
+        <v>1.7632531852038654E-4</v>
       </c>
       <c r="W5" s="14">
         <f>V5*(1+CAGR!$C$40)</f>
-        <v>6.7718569761706366E-5</v>
+        <v>1.7820676253080625E-4</v>
       </c>
       <c r="X5" s="14">
         <f>W5*(1+CAGR!$C$40)</f>
-        <v>6.8441147202890005E-5</v>
+        <v>1.8010828211286844E-4</v>
       </c>
       <c r="Y5" s="14">
         <f>X5*(1+CAGR!$C$40)</f>
-        <v>6.9171434761997649E-5</v>
+        <v>1.8203009147894117E-4</v>
       </c>
       <c r="Z5" s="14">
         <f>Y5*(1+CAGR!$C$40)</f>
-        <v>6.990951470829901E-5</v>
+        <v>1.8397240712710264E-4</v>
       </c>
       <c r="AA5" s="14">
         <f>Z5*(1+CAGR!$C$40)</f>
-        <v>7.0655470188901587E-5</v>
+        <v>1.8593544786553047E-4</v>
       </c>
       <c r="AB5" s="14">
         <f>AA5*(1+CAGR!$C$40)</f>
-        <v>7.1409385238117428E-5</v>
+        <v>1.8791943483715111E-4</v>
       </c>
       <c r="AC5" s="14">
         <f>AB5*(1+CAGR!$C$40)</f>
-        <v>7.2171344786929893E-5</v>
+        <v>1.8992459154455233E-4</v>
       </c>
       <c r="AD5" s="14">
         <f>AC5*(1+CAGR!$C$40)</f>
-        <v>7.2941434672561405E-5</v>
+        <v>1.9195114387516156E-4</v>
       </c>
       <c r="AE5" s="14">
         <f>AD5*(1+CAGR!$C$40)</f>
-        <v>7.3719741648143266E-5</v>
+        <v>1.9399932012669277E-4</v>
       </c>
       <c r="AF5" s="14">
         <f>AE5*(1+CAGR!$C$40)</f>
-        <v>7.4506353392488701E-5</v>
+        <v>1.9606935103286496E-4</v>
       </c>
       <c r="AG5" s="14"/>
     </row>
@@ -16670,127 +16670,127 @@
       </c>
       <c r="B8" s="13">
         <f>B5*Calibration!$D$32</f>
-        <v>1.6256590261481293E-4</v>
+        <v>4.2780500688108664E-4</v>
       </c>
       <c r="C8" s="13">
         <f>B8*(1+CAGR!$C$43)</f>
-        <v>1.643005295324881E-4</v>
+        <v>4.3236981455917922E-4</v>
       </c>
       <c r="D8" s="13">
         <f>C8*(1+CAGR!$C$43)</f>
-        <v>1.6605366543941087E-4</v>
+        <v>4.3698333010371281E-4</v>
       </c>
       <c r="E8" s="13">
         <f>D8*(1+CAGR!$C$43)</f>
-        <v>1.6782550783204543E-4</v>
+        <v>4.4164607324222486E-4</v>
       </c>
       <c r="F8" s="13">
         <f>E8*(1+CAGR!$C$43)</f>
-        <v>1.6961625631420251E-4</v>
+        <v>4.4635856924790136E-4</v>
       </c>
       <c r="G8" s="13">
         <f>F8*(1+CAGR!$C$43)</f>
-        <v>1.7142611261952527E-4</v>
+        <v>4.5112134899875076E-4</v>
       </c>
       <c r="H8" s="13">
         <f>G8*(1+CAGR!$C$43)</f>
-        <v>1.7325528063421539E-4</v>
+        <v>4.5593494903740895E-4</v>
       </c>
       <c r="I8" s="13">
         <f>H8*(1+CAGR!$C$43)</f>
-        <v>1.7510396642000139E-4</v>
+        <v>4.6079991163158263E-4</v>
       </c>
       <c r="J8" s="13">
         <f>I8*(1+CAGR!$C$43)</f>
-        <v>1.7697237823735223E-4</v>
+        <v>4.657167848351375E-4</v>
       </c>
       <c r="K8" s="13">
         <f>J8*(1+CAGR!$C$43)</f>
-        <v>1.7886072656893854E-4</v>
+        <v>4.7068612254983828E-4</v>
       </c>
       <c r="L8" s="13">
         <f>K8*(1+CAGR!$C$43)</f>
-        <v>1.8076922414334408E-4</v>
+        <v>4.7570848458774762E-4</v>
       </c>
       <c r="M8" s="13">
         <f>L8*(1+CAGR!$C$43)</f>
-        <v>1.8269808595903044E-4</v>
+        <v>4.8078443673429071E-4</v>
       </c>
       <c r="N8" s="13">
         <f>M8*(1+CAGR!$C$43)</f>
-        <v>1.8464752930855721E-4</v>
+        <v>4.859145508119928E-4</v>
       </c>
       <c r="O8" s="13">
         <f>N8*(1+CAGR!$C$43)</f>
-        <v>1.8661777380306078E-4</v>
+        <v>4.9109940474489694E-4</v>
       </c>
       <c r="P8" s="13">
         <f>O8*(1+CAGR!$C$43)</f>
-        <v>1.8860904139699416E-4</v>
+        <v>4.9633958262366897E-4</v>
       </c>
       <c r="Q8" s="13">
         <f>P8*(1+CAGR!$C$43)</f>
-        <v>1.9062155641313091E-4</v>
+        <v>5.0163567477139724E-4</v>
       </c>
       <c r="R8" s="13">
         <f>Q8*(1+CAGR!$C$43)</f>
-        <v>1.9265554556783588E-4</v>
+        <v>5.0698827781009447E-4</v>
       </c>
       <c r="S8" s="13">
         <f>R8*(1+CAGR!$C$43)</f>
-        <v>1.9471123799660547E-4</v>
+        <v>5.1239799472790914E-4</v>
       </c>
       <c r="T8" s="13">
         <f>S8*(1+CAGR!$C$43)</f>
-        <v>1.967888652798805E-4</v>
+        <v>5.1786543494705402E-4</v>
       </c>
       <c r="U8" s="13">
         <f>T8*(1+CAGR!$C$43)</f>
-        <v>1.9888866146913458E-4</v>
+        <v>5.2339121439245952E-4</v>
       </c>
       <c r="V8" s="13">
         <f>U8*(1+CAGR!$C$43)</f>
-        <v>2.0101086311324066E-4</v>
+        <v>5.2897595556115971E-4</v>
       </c>
       <c r="W8" s="13">
         <f>V8*(1+CAGR!$C$43)</f>
-        <v>2.0315570928511911E-4</v>
+        <v>5.3462028759241882E-4</v>
       </c>
       <c r="X8" s="13">
         <f>W8*(1+CAGR!$C$43)</f>
-        <v>2.0532344160867003E-4</v>
+        <v>5.4032484633860544E-4</v>
       </c>
       <c r="Y8" s="13">
         <f>X8*(1+CAGR!$C$43)</f>
-        <v>2.0751430428599295E-4</v>
+        <v>5.4609027443682358E-4</v>
       </c>
       <c r="Z8" s="13">
         <f>Y8*(1+CAGR!$C$43)</f>
-        <v>2.0972854412489703E-4</v>
+        <v>5.51917221381308E-4</v>
       </c>
       <c r="AA8" s="13">
         <f>Z8*(1+CAGR!$C$43)</f>
-        <v>2.1196641056670475E-4</v>
+        <v>5.5780634359659149E-4</v>
       </c>
       <c r="AB8" s="13">
         <f>AA8*(1+CAGR!$C$43)</f>
-        <v>2.1422815571435226E-4</v>
+        <v>5.6375830451145341E-4</v>
       </c>
       <c r="AC8" s="13">
         <f>AB8*(1+CAGR!$C$43)</f>
-        <v>2.1651403436078967E-4</v>
+        <v>5.6977377463365711E-4</v>
       </c>
       <c r="AD8" s="13">
         <f>AC8*(1+CAGR!$C$43)</f>
-        <v>2.1882430401768419E-4</v>
+        <v>5.7585343162548479E-4</v>
       </c>
       <c r="AE8" s="13">
         <f>AD8*(1+CAGR!$C$43)</f>
-        <v>2.2115922494442977E-4</v>
+        <v>5.8199796038007842E-4</v>
       </c>
       <c r="AF8" s="13">
         <f>AE8*(1+CAGR!$C$43)</f>
-        <v>2.2351906017746608E-4</v>
+        <v>5.8820805309859508E-4</v>
       </c>
       <c r="AG8" s="14"/>
     </row>
@@ -18962,127 +18962,127 @@
       </c>
       <c r="B2" s="13">
         <f>B5*Calibration!$B$43</f>
-        <v>2.8337186195252851E-3</v>
+        <v>4.1217725374913241E-3</v>
       </c>
       <c r="C2" s="13">
         <f>B2*(1+CAGR!$C$58)</f>
-        <v>2.8337186195252851E-3</v>
+        <v>4.1217725374913241E-3</v>
       </c>
       <c r="D2" s="13">
         <f>C2*(1+CAGR!$C$58)</f>
-        <v>2.8337186195252851E-3</v>
+        <v>4.1217725374913241E-3</v>
       </c>
       <c r="E2" s="13">
         <f>D2*(1+CAGR!$C$58)</f>
-        <v>2.8337186195252851E-3</v>
+        <v>4.1217725374913241E-3</v>
       </c>
       <c r="F2" s="13">
         <f>E2*(1+CAGR!$C$58)</f>
-        <v>2.8337186195252851E-3</v>
+        <v>4.1217725374913241E-3</v>
       </c>
       <c r="G2" s="13">
         <f>F2*(1+CAGR!$C$58)</f>
-        <v>2.8337186195252851E-3</v>
+        <v>4.1217725374913241E-3</v>
       </c>
       <c r="H2" s="13">
         <f>G2*(1+CAGR!$C$58)</f>
-        <v>2.8337186195252851E-3</v>
+        <v>4.1217725374913241E-3</v>
       </c>
       <c r="I2" s="13">
         <f>H2*(1+CAGR!$C$58)</f>
-        <v>2.8337186195252851E-3</v>
+        <v>4.1217725374913241E-3</v>
       </c>
       <c r="J2" s="13">
         <f>I2*(1+CAGR!$C$58)</f>
-        <v>2.8337186195252851E-3</v>
+        <v>4.1217725374913241E-3</v>
       </c>
       <c r="K2" s="13">
         <f>J2*(1+CAGR!$C$58)</f>
-        <v>2.8337186195252851E-3</v>
+        <v>4.1217725374913241E-3</v>
       </c>
       <c r="L2" s="13">
         <f>K2*(1+CAGR!$C$58)</f>
-        <v>2.8337186195252851E-3</v>
+        <v>4.1217725374913241E-3</v>
       </c>
       <c r="M2" s="13">
         <f>L2*(1+CAGR!$C$58)</f>
-        <v>2.8337186195252851E-3</v>
+        <v>4.1217725374913241E-3</v>
       </c>
       <c r="N2" s="13">
         <f>M2*(1+CAGR!$C$58)</f>
-        <v>2.8337186195252851E-3</v>
+        <v>4.1217725374913241E-3</v>
       </c>
       <c r="O2" s="13">
         <f>N2*(1+CAGR!$C$58)</f>
-        <v>2.8337186195252851E-3</v>
+        <v>4.1217725374913241E-3</v>
       </c>
       <c r="P2" s="13">
         <f>O2*(1+CAGR!$C$58)</f>
-        <v>2.8337186195252851E-3</v>
+        <v>4.1217725374913241E-3</v>
       </c>
       <c r="Q2" s="13">
         <f>P2*(1+CAGR!$C$58)</f>
-        <v>2.8337186195252851E-3</v>
+        <v>4.1217725374913241E-3</v>
       </c>
       <c r="R2" s="13">
         <f>Q2*(1+CAGR!$C$58)</f>
-        <v>2.8337186195252851E-3</v>
+        <v>4.1217725374913241E-3</v>
       </c>
       <c r="S2" s="13">
         <f>R2*(1+CAGR!$C$58)</f>
-        <v>2.8337186195252851E-3</v>
+        <v>4.1217725374913241E-3</v>
       </c>
       <c r="T2" s="13">
         <f>S2*(1+CAGR!$C$58)</f>
-        <v>2.8337186195252851E-3</v>
+        <v>4.1217725374913241E-3</v>
       </c>
       <c r="U2" s="13">
         <f>T2*(1+CAGR!$C$58)</f>
-        <v>2.8337186195252851E-3</v>
+        <v>4.1217725374913241E-3</v>
       </c>
       <c r="V2" s="13">
         <f>U2*(1+CAGR!$C$58)</f>
-        <v>2.8337186195252851E-3</v>
+        <v>4.1217725374913241E-3</v>
       </c>
       <c r="W2" s="13">
         <f>V2*(1+CAGR!$C$58)</f>
-        <v>2.8337186195252851E-3</v>
+        <v>4.1217725374913241E-3</v>
       </c>
       <c r="X2" s="13">
         <f>W2*(1+CAGR!$C$58)</f>
-        <v>2.8337186195252851E-3</v>
+        <v>4.1217725374913241E-3</v>
       </c>
       <c r="Y2" s="13">
         <f>X2*(1+CAGR!$C$58)</f>
-        <v>2.8337186195252851E-3</v>
+        <v>4.1217725374913241E-3</v>
       </c>
       <c r="Z2" s="13">
         <f>Y2*(1+CAGR!$C$58)</f>
-        <v>2.8337186195252851E-3</v>
+        <v>4.1217725374913241E-3</v>
       </c>
       <c r="AA2" s="13">
         <f>Z2*(1+CAGR!$C$58)</f>
-        <v>2.8337186195252851E-3</v>
+        <v>4.1217725374913241E-3</v>
       </c>
       <c r="AB2" s="13">
         <f>AA2*(1+CAGR!$C$58)</f>
-        <v>2.8337186195252851E-3</v>
+        <v>4.1217725374913241E-3</v>
       </c>
       <c r="AC2" s="13">
         <f>AB2*(1+CAGR!$C$58)</f>
-        <v>2.8337186195252851E-3</v>
+        <v>4.1217725374913241E-3</v>
       </c>
       <c r="AD2" s="13">
         <f>AC2*(1+CAGR!$C$58)</f>
-        <v>2.8337186195252851E-3</v>
+        <v>4.1217725374913241E-3</v>
       </c>
       <c r="AE2" s="13">
         <f>AD2*(1+CAGR!$C$58)</f>
-        <v>2.8337186195252851E-3</v>
+        <v>4.1217725374913241E-3</v>
       </c>
       <c r="AF2" s="13">
         <f>AE2*(1+CAGR!$C$58)</f>
-        <v>2.8337186195252851E-3</v>
+        <v>4.1217725374913241E-3</v>
       </c>
     </row>
     <row r="3" spans="1:32">
@@ -19220,127 +19220,127 @@
       </c>
       <c r="B4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182399449386899E-4</v>
+        <v>1.2826530829001732E-3</v>
       </c>
       <c r="C4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182399449386899E-4</v>
+        <v>1.2826530829001732E-3</v>
       </c>
       <c r="D4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182399449386899E-4</v>
+        <v>1.2826530829001732E-3</v>
       </c>
       <c r="E4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182399449386899E-4</v>
+        <v>1.2826530829001732E-3</v>
       </c>
       <c r="F4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182399449386899E-4</v>
+        <v>1.2826530829001732E-3</v>
       </c>
       <c r="G4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182399449386899E-4</v>
+        <v>1.2826530829001732E-3</v>
       </c>
       <c r="H4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182399449386899E-4</v>
+        <v>1.2826530829001732E-3</v>
       </c>
       <c r="I4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182399449386899E-4</v>
+        <v>1.2826530829001732E-3</v>
       </c>
       <c r="J4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182399449386899E-4</v>
+        <v>1.2826530829001732E-3</v>
       </c>
       <c r="K4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182399449386899E-4</v>
+        <v>1.2826530829001732E-3</v>
       </c>
       <c r="L4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182399449386899E-4</v>
+        <v>1.2826530829001732E-3</v>
       </c>
       <c r="M4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182399449386899E-4</v>
+        <v>1.2826530829001732E-3</v>
       </c>
       <c r="N4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182399449386899E-4</v>
+        <v>1.2826530829001732E-3</v>
       </c>
       <c r="O4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182399449386899E-4</v>
+        <v>1.2826530829001732E-3</v>
       </c>
       <c r="P4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182399449386899E-4</v>
+        <v>1.2826530829001732E-3</v>
       </c>
       <c r="Q4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182399449386899E-4</v>
+        <v>1.2826530829001732E-3</v>
       </c>
       <c r="R4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182399449386899E-4</v>
+        <v>1.2826530829001732E-3</v>
       </c>
       <c r="S4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182399449386899E-4</v>
+        <v>1.2826530829001732E-3</v>
       </c>
       <c r="T4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182399449386899E-4</v>
+        <v>1.2826530829001732E-3</v>
       </c>
       <c r="U4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182399449386899E-4</v>
+        <v>1.2826530829001732E-3</v>
       </c>
       <c r="V4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182399449386899E-4</v>
+        <v>1.2826530829001732E-3</v>
       </c>
       <c r="W4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182399449386899E-4</v>
+        <v>1.2826530829001732E-3</v>
       </c>
       <c r="X4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182399449386899E-4</v>
+        <v>1.2826530829001732E-3</v>
       </c>
       <c r="Y4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182399449386899E-4</v>
+        <v>1.2826530829001732E-3</v>
       </c>
       <c r="Z4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182399449386899E-4</v>
+        <v>1.2826530829001732E-3</v>
       </c>
       <c r="AA4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182399449386899E-4</v>
+        <v>1.2826530829001732E-3</v>
       </c>
       <c r="AB4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182399449386899E-4</v>
+        <v>1.2826530829001732E-3</v>
       </c>
       <c r="AC4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182399449386899E-4</v>
+        <v>1.2826530829001732E-3</v>
       </c>
       <c r="AD4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182399449386899E-4</v>
+        <v>1.2826530829001732E-3</v>
       </c>
       <c r="AE4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182399449386899E-4</v>
+        <v>1.2826530829001732E-3</v>
       </c>
       <c r="AF4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182399449386899E-4</v>
+        <v>1.2826530829001732E-3</v>
       </c>
     </row>
     <row r="5" spans="1:32">
@@ -19349,127 +19349,127 @@
       </c>
       <c r="B5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182386251894039E-4</v>
+        <v>1.2826528909366407E-3</v>
       </c>
       <c r="C5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182386251894039E-4</v>
+        <v>1.2826528909366407E-3</v>
       </c>
       <c r="D5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182386251894039E-4</v>
+        <v>1.2826528909366407E-3</v>
       </c>
       <c r="E5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182386251894039E-4</v>
+        <v>1.2826528909366407E-3</v>
       </c>
       <c r="F5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182386251894039E-4</v>
+        <v>1.2826528909366407E-3</v>
       </c>
       <c r="G5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182386251894039E-4</v>
+        <v>1.2826528909366407E-3</v>
       </c>
       <c r="H5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182386251894039E-4</v>
+        <v>1.2826528909366407E-3</v>
       </c>
       <c r="I5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182386251894039E-4</v>
+        <v>1.2826528909366407E-3</v>
       </c>
       <c r="J5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182386251894039E-4</v>
+        <v>1.2826528909366407E-3</v>
       </c>
       <c r="K5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182386251894039E-4</v>
+        <v>1.2826528909366407E-3</v>
       </c>
       <c r="L5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182386251894039E-4</v>
+        <v>1.2826528909366407E-3</v>
       </c>
       <c r="M5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182386251894039E-4</v>
+        <v>1.2826528909366407E-3</v>
       </c>
       <c r="N5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182386251894039E-4</v>
+        <v>1.2826528909366407E-3</v>
       </c>
       <c r="O5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182386251894039E-4</v>
+        <v>1.2826528909366407E-3</v>
       </c>
       <c r="P5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182386251894039E-4</v>
+        <v>1.2826528909366407E-3</v>
       </c>
       <c r="Q5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182386251894039E-4</v>
+        <v>1.2826528909366407E-3</v>
       </c>
       <c r="R5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182386251894039E-4</v>
+        <v>1.2826528909366407E-3</v>
       </c>
       <c r="S5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182386251894039E-4</v>
+        <v>1.2826528909366407E-3</v>
       </c>
       <c r="T5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182386251894039E-4</v>
+        <v>1.2826528909366407E-3</v>
       </c>
       <c r="U5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182386251894039E-4</v>
+        <v>1.2826528909366407E-3</v>
       </c>
       <c r="V5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182386251894039E-4</v>
+        <v>1.2826528909366407E-3</v>
       </c>
       <c r="W5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182386251894039E-4</v>
+        <v>1.2826528909366407E-3</v>
       </c>
       <c r="X5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182386251894039E-4</v>
+        <v>1.2826528909366407E-3</v>
       </c>
       <c r="Y5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182386251894039E-4</v>
+        <v>1.2826528909366407E-3</v>
       </c>
       <c r="Z5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182386251894039E-4</v>
+        <v>1.2826528909366407E-3</v>
       </c>
       <c r="AA5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182386251894039E-4</v>
+        <v>1.2826528909366407E-3</v>
       </c>
       <c r="AB5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182386251894039E-4</v>
+        <v>1.2826528909366407E-3</v>
       </c>
       <c r="AC5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182386251894039E-4</v>
+        <v>1.2826528909366407E-3</v>
       </c>
       <c r="AD5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182386251894039E-4</v>
+        <v>1.2826528909366407E-3</v>
       </c>
       <c r="AE5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182386251894039E-4</v>
+        <v>1.2826528909366407E-3</v>
       </c>
       <c r="AF5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.8182386251894039E-4</v>
+        <v>1.2826528909366407E-3</v>
       </c>
     </row>
     <row r="6" spans="1:32">
@@ -19736,127 +19736,127 @@
       </c>
       <c r="B8" s="13">
         <f>B5*Calibration!D43</f>
-        <v>2.6454715875568208E-3</v>
+        <v>3.8479586728099213E-3</v>
       </c>
       <c r="C8" s="13">
         <f>B8*(1+CAGR!$C$64)</f>
-        <v>2.6454715875568208E-3</v>
+        <v>3.8479586728099213E-3</v>
       </c>
       <c r="D8" s="13">
         <f>C8*(1+CAGR!$C$64)</f>
-        <v>2.6454715875568208E-3</v>
+        <v>3.8479586728099213E-3</v>
       </c>
       <c r="E8" s="13">
         <f>D8*(1+CAGR!$C$64)</f>
-        <v>2.6454715875568208E-3</v>
+        <v>3.8479586728099213E-3</v>
       </c>
       <c r="F8" s="13">
         <f>E8*(1+CAGR!$C$64)</f>
-        <v>2.6454715875568208E-3</v>
+        <v>3.8479586728099213E-3</v>
       </c>
       <c r="G8" s="13">
         <f>F8*(1+CAGR!$C$64)</f>
-        <v>2.6454715875568208E-3</v>
+        <v>3.8479586728099213E-3</v>
       </c>
       <c r="H8" s="13">
         <f>G8*(1+CAGR!$C$64)</f>
-        <v>2.6454715875568208E-3</v>
+        <v>3.8479586728099213E-3</v>
       </c>
       <c r="I8" s="13">
         <f>H8*(1+CAGR!$C$64)</f>
-        <v>2.6454715875568208E-3</v>
+        <v>3.8479586728099213E-3</v>
       </c>
       <c r="J8" s="13">
         <f>I8*(1+CAGR!$C$64)</f>
-        <v>2.6454715875568208E-3</v>
+        <v>3.8479586728099213E-3</v>
       </c>
       <c r="K8" s="13">
         <f>J8*(1+CAGR!$C$64)</f>
-        <v>2.6454715875568208E-3</v>
+        <v>3.8479586728099213E-3</v>
       </c>
       <c r="L8" s="13">
         <f>K8*(1+CAGR!$C$64)</f>
-        <v>2.6454715875568208E-3</v>
+        <v>3.8479586728099213E-3</v>
       </c>
       <c r="M8" s="13">
         <f>L8*(1+CAGR!$C$64)</f>
-        <v>2.6454715875568208E-3</v>
+        <v>3.8479586728099213E-3</v>
       </c>
       <c r="N8" s="13">
         <f>M8*(1+CAGR!$C$64)</f>
-        <v>2.6454715875568208E-3</v>
+        <v>3.8479586728099213E-3</v>
       </c>
       <c r="O8" s="13">
         <f>N8*(1+CAGR!$C$64)</f>
-        <v>2.6454715875568208E-3</v>
+        <v>3.8479586728099213E-3</v>
       </c>
       <c r="P8" s="13">
         <f>O8*(1+CAGR!$C$64)</f>
-        <v>2.6454715875568208E-3</v>
+        <v>3.8479586728099213E-3</v>
       </c>
       <c r="Q8" s="13">
         <f>P8*(1+CAGR!$C$64)</f>
-        <v>2.6454715875568208E-3</v>
+        <v>3.8479586728099213E-3</v>
       </c>
       <c r="R8" s="13">
         <f>Q8*(1+CAGR!$C$64)</f>
-        <v>2.6454715875568208E-3</v>
+        <v>3.8479586728099213E-3</v>
       </c>
       <c r="S8" s="13">
         <f>R8*(1+CAGR!$C$64)</f>
-        <v>2.6454715875568208E-3</v>
+        <v>3.8479586728099213E-3</v>
       </c>
       <c r="T8" s="13">
         <f>S8*(1+CAGR!$C$64)</f>
-        <v>2.6454715875568208E-3</v>
+        <v>3.8479586728099213E-3</v>
       </c>
       <c r="U8" s="13">
         <f>T8*(1+CAGR!$C$64)</f>
-        <v>2.6454715875568208E-3</v>
+        <v>3.8479586728099213E-3</v>
       </c>
       <c r="V8" s="13">
         <f>U8*(1+CAGR!$C$64)</f>
-        <v>2.6454715875568208E-3</v>
+        <v>3.8479586728099213E-3</v>
       </c>
       <c r="W8" s="13">
         <f>V8*(1+CAGR!$C$64)</f>
-        <v>2.6454715875568208E-3</v>
+        <v>3.8479586728099213E-3</v>
       </c>
       <c r="X8" s="13">
         <f>W8*(1+CAGR!$C$64)</f>
-        <v>2.6454715875568208E-3</v>
+        <v>3.8479586728099213E-3</v>
       </c>
       <c r="Y8" s="13">
         <f>X8*(1+CAGR!$C$64)</f>
-        <v>2.6454715875568208E-3</v>
+        <v>3.8479586728099213E-3</v>
       </c>
       <c r="Z8" s="13">
         <f>Y8*(1+CAGR!$C$64)</f>
-        <v>2.6454715875568208E-3</v>
+        <v>3.8479586728099213E-3</v>
       </c>
       <c r="AA8" s="13">
         <f>Z8*(1+CAGR!$C$64)</f>
-        <v>2.6454715875568208E-3</v>
+        <v>3.8479586728099213E-3</v>
       </c>
       <c r="AB8" s="13">
         <f>AA8*(1+CAGR!$C$64)</f>
-        <v>2.6454715875568208E-3</v>
+        <v>3.8479586728099213E-3</v>
       </c>
       <c r="AC8" s="13">
         <f>AB8*(1+CAGR!$C$64)</f>
-        <v>2.6454715875568208E-3</v>
+        <v>3.8479586728099213E-3</v>
       </c>
       <c r="AD8" s="13">
         <f>AC8*(1+CAGR!$C$64)</f>
-        <v>2.6454715875568208E-3</v>
+        <v>3.8479586728099213E-3</v>
       </c>
       <c r="AE8" s="13">
         <f>AD8*(1+CAGR!$C$64)</f>
-        <v>2.6454715875568208E-3</v>
+        <v>3.8479586728099213E-3</v>
       </c>
       <c r="AF8" s="13">
         <f>AE8*(1+CAGR!$C$64)</f>
-        <v>2.6454715875568208E-3</v>
+        <v>3.8479586728099213E-3</v>
       </c>
     </row>
   </sheetData>
@@ -19980,127 +19980,127 @@
       </c>
       <c r="B2" s="13">
         <f>B5*Calibration!$B$44</f>
-        <v>3.447500066695273E-3</v>
+        <v>5.0145455515567608E-3</v>
       </c>
       <c r="C2" s="13">
         <f>B2*(1+CAGR!$C$65)</f>
-        <v>3.4599439494026039E-3</v>
+        <v>5.0326457445856055E-3</v>
       </c>
       <c r="D2" s="13">
         <f>C2*(1+CAGR!$C$65)</f>
-        <v>3.4724327487781984E-3</v>
+        <v>5.0508112709501066E-3</v>
       </c>
       <c r="E2" s="13">
         <f>D2*(1+CAGR!$C$65)</f>
-        <v>3.4849666269504797E-3</v>
+        <v>5.0690423664734247E-3</v>
       </c>
       <c r="F2" s="13">
         <f>E2*(1+CAGR!$C$65)</f>
-        <v>3.4975457466330808E-3</v>
+        <v>5.0873392678299351E-3</v>
       </c>
       <c r="G2" s="13">
         <f>F2*(1+CAGR!$C$65)</f>
-        <v>3.5101702711269546E-3</v>
+        <v>5.1057022125482968E-3</v>
       </c>
       <c r="H2" s="13">
         <f>G2*(1+CAGR!$C$65)</f>
-        <v>3.522840364322496E-3</v>
+        <v>5.1241314390145388E-3</v>
       </c>
       <c r="I2" s="13">
         <f>H2*(1+CAGR!$C$65)</f>
-        <v>3.5355561907016676E-3</v>
+        <v>5.1426271864751525E-3</v>
       </c>
       <c r="J2" s="13">
         <f>I2*(1+CAGR!$C$65)</f>
-        <v>3.5483179153401366E-3</v>
+        <v>5.1611896950401982E-3</v>
       </c>
       <c r="K2" s="13">
         <f>J2*(1+CAGR!$C$65)</f>
-        <v>3.5611257039094174E-3</v>
+        <v>5.1798192056864241E-3</v>
       </c>
       <c r="L2" s="13">
         <f>K2*(1+CAGR!$C$65)</f>
-        <v>3.5739797226790209E-3</v>
+        <v>5.1985159602603928E-3</v>
       </c>
       <c r="M2" s="13">
         <f>L2*(1+CAGR!$C$65)</f>
-        <v>3.5868801385186147E-3</v>
+        <v>5.2172802014816199E-3</v>
       </c>
       <c r="N2" s="13">
         <f>M2*(1+CAGR!$C$65)</f>
-        <v>3.5998271189001891E-3</v>
+        <v>5.2361121729457283E-3</v>
       </c>
       <c r="O2" s="13">
         <f>N2*(1+CAGR!$C$65)</f>
-        <v>3.6128208319002307E-3</v>
+        <v>5.255012119127607E-3</v>
       </c>
       <c r="P2" s="13">
         <f>O2*(1+CAGR!$C$65)</f>
-        <v>3.6258614462019046E-3</v>
+        <v>5.2739802853845868E-3</v>
       </c>
       <c r="Q2" s="13">
         <f>P2*(1+CAGR!$C$65)</f>
-        <v>3.638949131097244E-3</v>
+        <v>5.2930169179596261E-3</v>
       </c>
       <c r="R2" s="13">
         <f>Q2*(1+CAGR!$C$65)</f>
-        <v>3.6520840564893487E-3</v>
+        <v>5.3121222639845051E-3</v>
       </c>
       <c r="S2" s="13">
         <f>R2*(1+CAGR!$C$65)</f>
-        <v>3.6652663928945892E-3</v>
+        <v>5.3312965714830372E-3</v>
       </c>
       <c r="T2" s="13">
         <f>S2*(1+CAGR!$C$65)</f>
-        <v>3.6784963114448225E-3</v>
+        <v>5.3505400893742857E-3</v>
       </c>
       <c r="U2" s="13">
         <f>T2*(1+CAGR!$C$65)</f>
-        <v>3.6917739838896115E-3</v>
+        <v>5.3698530674757975E-3</v>
       </c>
       <c r="V2" s="13">
         <f>U2*(1+CAGR!$C$65)</f>
-        <v>3.7050995825984568E-3</v>
+        <v>5.389235756506845E-3</v>
       </c>
       <c r="W2" s="13">
         <f>V2*(1+CAGR!$C$65)</f>
-        <v>3.7184732805630319E-3</v>
+        <v>5.408688408091682E-3</v>
       </c>
       <c r="X2" s="13">
         <f>W2*(1+CAGR!$C$65)</f>
-        <v>3.7318952513994319E-3</v>
+        <v>5.4282112747628094E-3</v>
       </c>
       <c r="Y2" s="13">
         <f>X2*(1+CAGR!$C$65)</f>
-        <v>3.7453656693504245E-3</v>
+        <v>5.4478046099642533E-3</v>
       </c>
       <c r="Z2" s="13">
         <f>Y2*(1+CAGR!$C$65)</f>
-        <v>3.7588847092877137E-3</v>
+        <v>5.4674686680548559E-3</v>
       </c>
       <c r="AA2" s="13">
         <f>Z2*(1+CAGR!$C$65)</f>
-        <v>3.7724525467142099E-3</v>
+        <v>5.4872037043115773E-3</v>
       </c>
       <c r="AB2" s="13">
         <f>AA2*(1+CAGR!$C$65)</f>
-        <v>3.7860693577663074E-3</v>
+        <v>5.50700997493281E-3</v>
       </c>
       <c r="AC2" s="13">
         <f>AB2*(1+CAGR!$C$65)</f>
-        <v>3.799735319216172E-3</v>
+        <v>5.526887737041704E-3</v>
       </c>
       <c r="AD2" s="13">
         <f>AC2*(1+CAGR!$C$65)</f>
-        <v>3.8134506084740354E-3</v>
+        <v>5.5468372486895054E-3</v>
       </c>
       <c r="AE2" s="13">
         <f>AD2*(1+CAGR!$C$65)</f>
-        <v>3.8272154035904975E-3</v>
+        <v>5.5668587688589054E-3</v>
       </c>
       <c r="AF2" s="13">
         <f>AE2*(1+CAGR!$C$65)</f>
-        <v>3.8410298832588399E-3</v>
+        <v>5.586952557467403E-3</v>
       </c>
     </row>
     <row r="3" spans="1:32">
@@ -20109,127 +20109,127 @@
       </c>
       <c r="B3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$65:$C$71,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="C3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="D3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="E3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="F3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="G3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="H3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="I3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="J3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="K3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="L3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="M3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="N3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="O3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="P3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="Q3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="R3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="S3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="T3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="U3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="V3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="W3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="X3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="Y3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="Z3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="AA3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="AB3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="AC3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="AD3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="AE3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="AF3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
     </row>
     <row r="4" spans="1:32">
@@ -20238,127 +20238,127 @@
       </c>
       <c r="B4" s="14">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A4,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$65:$C$71,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="C4" s="14">
         <f>IFERROR(B4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="D4" s="14">
         <f>IFERROR(C4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="E4" s="14">
         <f>IFERROR(D4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="F4" s="14">
         <f>IFERROR(E4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="G4" s="14">
         <f>IFERROR(F4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="H4" s="14">
         <f>IFERROR(G4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="I4" s="14">
         <f>IFERROR(H4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="J4" s="14">
         <f>IFERROR(I4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="K4" s="14">
         <f>IFERROR(J4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="L4" s="14">
         <f>IFERROR(K4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="M4" s="14">
         <f>IFERROR(L4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="N4" s="14">
         <f>IFERROR(M4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="O4" s="14">
         <f>IFERROR(N4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="P4" s="14">
         <f>IFERROR(O4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="Q4" s="14">
         <f>IFERROR(P4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="R4" s="14">
         <f>IFERROR(Q4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="S4" s="14">
         <f>IFERROR(R4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="T4" s="14">
         <f>IFERROR(S4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="U4" s="14">
         <f>IFERROR(T4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="V4" s="14">
         <f>IFERROR(U4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="W4" s="14">
         <f>IFERROR(V4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="X4" s="14">
         <f>IFERROR(W4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="Y4" s="14">
         <f>IFERROR(X4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="Z4" s="14">
         <f>IFERROR(Y4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="AA4" s="14">
         <f>IFERROR(Z4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="AB4" s="14">
         <f>IFERROR(AA4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="AC4" s="14">
         <f>IFERROR(AB4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="AD4" s="14">
         <f>IFERROR(AC4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="AE4" s="14">
         <f>IFERROR(AD4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="AF4" s="14">
         <f>IFERROR(AE4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
     </row>
     <row r="5" spans="1:32">
@@ -20367,127 +20367,127 @@
       </c>
       <c r="B5" s="14">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A5,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$65:$C$71,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0728262869504018E-3</v>
+        <v>1.5604745992005844E-3</v>
       </c>
       <c r="C5" s="14">
         <f>IFERROR(B5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0739180674663646E-3</v>
+        <v>1.5620626435874393E-3</v>
       </c>
       <c r="D5" s="14">
         <f>IFERROR(C5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0750109590519474E-3</v>
+        <v>1.5636523040755599E-3</v>
       </c>
       <c r="E5" s="14">
         <f>IFERROR(D5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0761049628378499E-3</v>
+        <v>1.5652435823095999E-3</v>
       </c>
       <c r="F5" s="14">
         <f>IFERROR(E5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.077200079955922E-3</v>
+        <v>1.5668364799358867E-3</v>
       </c>
       <c r="G5" s="14">
         <f>IFERROR(F5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0782963115391661E-3</v>
+        <v>1.5684309986024234E-3</v>
       </c>
       <c r="H5" s="14">
         <f>IFERROR(G5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.079393658721737E-3</v>
+        <v>1.5700271399588901E-3</v>
       </c>
       <c r="I5" s="14">
         <f>IFERROR(H5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0804921226389441E-3</v>
+        <v>1.5716249056566458E-3</v>
       </c>
       <c r="J5" s="14">
         <f>IFERROR(I5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0815917044272518E-3</v>
+        <v>1.5732242973487299E-3</v>
       </c>
       <c r="K5" s="14">
         <f>IFERROR(J5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0826924052242815E-3</v>
+        <v>1.574825316689864E-3</v>
       </c>
       <c r="L5" s="14">
         <f>IFERROR(K5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0837942261688119E-3</v>
+        <v>1.5764279653364536E-3</v>
       </c>
       <c r="M5" s="14">
         <f>IFERROR(L5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.084897168400781E-3</v>
+        <v>1.5780322449465904E-3</v>
       </c>
       <c r="N5" s="14">
         <f>IFERROR(M5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0860012330612865E-3</v>
+        <v>1.5796381571800528E-3</v>
       </c>
       <c r="O5" s="14">
         <f>IFERROR(N5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0871064212925874E-3</v>
+        <v>1.5812457036983088E-3</v>
       </c>
       <c r="P5" s="14">
         <f>IFERROR(O5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0882127342381055E-3</v>
+        <v>1.5828548861645168E-3</v>
       </c>
       <c r="Q5" s="14">
         <f>IFERROR(P5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0893201730424258E-3</v>
+        <v>1.5844657062435282E-3</v>
       </c>
       <c r="R5" s="14">
         <f>IFERROR(Q5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0904287388512983E-3</v>
+        <v>1.5860781656018884E-3</v>
       </c>
       <c r="S5" s="14">
         <f>IFERROR(R5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0915384328116391E-3</v>
+        <v>1.5876922659078386E-3</v>
       </c>
       <c r="T5" s="14">
         <f>IFERROR(S5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0926492560715314E-3</v>
+        <v>1.5893080088313183E-3</v>
       </c>
       <c r="U5" s="14">
         <f>IFERROR(T5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0937612097802266E-3</v>
+        <v>1.5909253960439658E-3</v>
       </c>
       <c r="V5" s="14">
         <f>IFERROR(U5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0948742950881458E-3</v>
+        <v>1.592544429219121E-3</v>
       </c>
       <c r="W5" s="14">
         <f>IFERROR(V5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0959885131468807E-3</v>
+        <v>1.5941651100318264E-3</v>
       </c>
       <c r="X5" s="14">
         <f>IFERROR(W5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0971038651091953E-3</v>
+        <v>1.5957874401588293E-3</v>
       </c>
       <c r="Y5" s="14">
         <f>IFERROR(X5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0982203521290265E-3</v>
+        <v>1.5974114212785836E-3</v>
       </c>
       <c r="Z5" s="14">
         <f>IFERROR(Y5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0993379753614853E-3</v>
+        <v>1.5990370550712509E-3</v>
       </c>
       <c r="AA5" s="14">
         <f>IFERROR(Z5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.1004567359628585E-3</v>
+        <v>1.6006643432187029E-3</v>
       </c>
       <c r="AB5" s="14">
         <f>IFERROR(AA5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.1015766350906096E-3</v>
+        <v>1.6022932874045228E-3</v>
       </c>
       <c r="AC5" s="14">
         <f>IFERROR(AB5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.1026976739033801E-3</v>
+        <v>1.6039238893140071E-3</v>
       </c>
       <c r="AD5" s="14">
         <f>IFERROR(AC5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.1038198535609904E-3</v>
+        <v>1.6055561506341674E-3</v>
       </c>
       <c r="AE5" s="14">
         <f>IFERROR(AD5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.104943175224441E-3</v>
+        <v>1.6071900730537322E-3</v>
       </c>
       <c r="AF5" s="14">
         <f>IFERROR(AE5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.1060676400559146E-3</v>
+        <v>1.6088256582631483E-3</v>
       </c>
     </row>
     <row r="6" spans="1:32">
@@ -20754,127 +20754,127 @@
       </c>
       <c r="B8" s="13">
         <f>B5*Calibration!$D$44</f>
-        <v>3.2184788608512049E-3</v>
+        <v>4.6814237976017525E-3</v>
       </c>
       <c r="C8" s="13">
         <f>B8*(1+CAGR!$C$71)</f>
-        <v>3.2300960827991794E-3</v>
+        <v>4.6983215749806248E-3</v>
       </c>
       <c r="D8" s="13">
         <f>C8*(1+CAGR!$C$71)</f>
-        <v>3.2417552375519428E-3</v>
+        <v>4.715280345530099E-3</v>
       </c>
       <c r="E8" s="13">
         <f>D8*(1+CAGR!$C$71)</f>
-        <v>3.2534564764675495E-3</v>
+        <v>4.7323003294073452E-3</v>
       </c>
       <c r="F8" s="13">
         <f>E8*(1+CAGR!$C$71)</f>
-        <v>3.2651999514503875E-3</v>
+        <v>4.7493817475642002E-3</v>
       </c>
       <c r="G8" s="13">
         <f>F8*(1+CAGR!$C$71)</f>
-        <v>3.2769858149531489E-3</v>
+        <v>4.7665248217500346E-3</v>
       </c>
       <c r="H8" s="13">
         <f>G8*(1+CAGR!$C$71)</f>
-        <v>3.2888142199788096E-3</v>
+        <v>4.7837297745146317E-3</v>
       </c>
       <c r="I8" s="13">
         <f>H8*(1+CAGR!$C$71)</f>
-        <v>3.300685320082616E-3</v>
+        <v>4.8009968292110775E-3</v>
       </c>
       <c r="J8" s="13">
         <f>I8*(1+CAGR!$C$71)</f>
-        <v>3.3125992693740776E-3</v>
+        <v>4.8183262099986577E-3</v>
       </c>
       <c r="K8" s="13">
         <f>J8*(1+CAGR!$C$71)</f>
-        <v>3.3245562225189679E-3</v>
+        <v>4.8357181418457705E-3</v>
       </c>
       <c r="L8" s="13">
         <f>K8*(1+CAGR!$C$71)</f>
-        <v>3.3365563347413328E-3</v>
+        <v>4.8531728505328466E-3</v>
       </c>
       <c r="M8" s="13">
         <f>L8*(1+CAGR!$C$71)</f>
-        <v>3.3485997618255049E-3</v>
+        <v>4.8706905626552787E-3</v>
       </c>
       <c r="N8" s="13">
         <f>M8*(1+CAGR!$C$71)</f>
-        <v>3.3606866601181267E-3</v>
+        <v>4.888271505626365E-3</v>
       </c>
       <c r="O8" s="13">
         <f>N8*(1+CAGR!$C$71)</f>
-        <v>3.3728171865301799E-3</v>
+        <v>4.9059159076802602E-3</v>
       </c>
       <c r="P8" s="13">
         <f>O8*(1+CAGR!$C$71)</f>
-        <v>3.3849914985390217E-3</v>
+        <v>4.9236239978749392E-3</v>
       </c>
       <c r="Q8" s="13">
         <f>P8*(1+CAGR!$C$71)</f>
-        <v>3.3972097541904306E-3</v>
+        <v>4.9413960060951702E-3</v>
       </c>
       <c r="R8" s="13">
         <f>Q8*(1+CAGR!$C$71)</f>
-        <v>3.4094721121006566E-3</v>
+        <v>4.9592321630554988E-3</v>
       </c>
       <c r="S8" s="13">
         <f>R8*(1+CAGR!$C$71)</f>
-        <v>3.4217787314584822E-3</v>
+        <v>4.9771327003032446E-3</v>
       </c>
       <c r="T8" s="13">
         <f>S8*(1+CAGR!$C$71)</f>
-        <v>3.4341297720272865E-3</v>
+        <v>4.9950978502215056E-3</v>
       </c>
       <c r="U8" s="13">
         <f>T8*(1+CAGR!$C$71)</f>
-        <v>3.4465253941471214E-3</v>
+        <v>5.0131278460321749E-3</v>
       </c>
       <c r="V8" s="13">
         <f>U8*(1+CAGR!$C$71)</f>
-        <v>3.4589657587367922E-3</v>
+        <v>5.0312229217989689E-3</v>
       </c>
       <c r="W8" s="13">
         <f>V8*(1+CAGR!$C$71)</f>
-        <v>3.4714510272959472E-3</v>
+        <v>5.0493833124304671E-3</v>
       </c>
       <c r="X8" s="13">
         <f>W8*(1+CAGR!$C$71)</f>
-        <v>3.4839813619071728E-3</v>
+        <v>5.0676092536831585E-3</v>
       </c>
       <c r="Y8" s="13">
         <f>X8*(1+CAGR!$C$71)</f>
-        <v>3.4965569252380993E-3</v>
+        <v>5.0859009821645059E-3</v>
       </c>
       <c r="Z8" s="13">
         <f>Y8*(1+CAGR!$C$71)</f>
-        <v>3.5091778805435118E-3</v>
+        <v>5.1042587353360156E-3</v>
       </c>
       <c r="AA8" s="13">
         <f>Z8*(1+CAGR!$C$71)</f>
-        <v>3.5218443916674703E-3</v>
+        <v>5.1226827515163187E-3</v>
       </c>
       <c r="AB8" s="13">
         <f>AA8*(1+CAGR!$C$71)</f>
-        <v>3.5345566230454355E-3</v>
+        <v>5.1411732698842683E-3</v>
       </c>
       <c r="AC8" s="13">
         <f>AB8*(1+CAGR!$C$71)</f>
-        <v>3.5473147397064044E-3</v>
+        <v>5.1597305304820415E-3</v>
       </c>
       <c r="AD8" s="13">
         <f>AC8*(1+CAGR!$C$71)</f>
-        <v>3.5601189072750525E-3</v>
+        <v>5.1783547742182577E-3</v>
       </c>
       <c r="AE8" s="13">
         <f>AD8*(1+CAGR!$C$71)</f>
-        <v>3.5729692919738839E-3</v>
+        <v>5.1970462428711037E-3</v>
       </c>
       <c r="AF8" s="13">
         <f>AE8*(1+CAGR!$C$71)</f>
-        <v>3.5858660606253893E-3</v>
+        <v>5.2158051790914747E-3</v>
       </c>
     </row>
   </sheetData>
@@ -20934,25 +20934,25 @@
         <v>16</v>
       </c>
       <c r="B2" s="34">
-        <v>1.5235737752907245E-4</v>
+        <v>1.6928597503230273E-4</v>
       </c>
       <c r="C2" s="34">
-        <v>3.5473239004613325E-5</v>
+        <v>3.9414710005125919E-5</v>
       </c>
       <c r="D2" s="34">
-        <v>4.7148258210860994E-5</v>
+        <v>5.2386953567623324E-5</v>
       </c>
       <c r="E2" s="34">
-        <v>4.5262767450633711E-5</v>
+        <v>5.0291963834037454E-5</v>
       </c>
       <c r="F2" s="34">
-        <v>7.7515170564549307E-5</v>
+        <v>8.6127967293943671E-5</v>
       </c>
       <c r="G2" s="34">
-        <v>5.8349457765161877E-5</v>
+        <v>6.483273085017986E-5</v>
       </c>
       <c r="H2" s="34">
-        <v>4.2336866703967495E-5</v>
+        <v>4.704096300440833E-5</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -20962,22 +20962,22 @@
         <v>17</v>
       </c>
       <c r="B3" s="34">
-        <v>6.1294250672918476E-4</v>
+        <v>6.8104722969909411E-4</v>
       </c>
       <c r="C3" s="34">
-        <v>2.9083656797108536E-4</v>
+        <v>3.2315174219009485E-4</v>
       </c>
       <c r="D3" s="34">
-        <v>2.5298072785642648E-4</v>
+        <v>2.8108969761825162E-4</v>
       </c>
       <c r="E3" s="34">
-        <v>2.8253964452549401E-4</v>
+        <v>3.1393293836166002E-4</v>
       </c>
       <c r="F3" s="34">
         <v>0</v>
       </c>
       <c r="G3" s="34">
-        <v>2.5880886022515496E-4</v>
+        <v>2.8756540025017219E-4</v>
       </c>
       <c r="H3" s="34">
         <v>0</v>
@@ -20990,16 +20990,16 @@
         <v>18</v>
       </c>
       <c r="B4" s="34">
-        <v>1.7229535868595907E-4</v>
+        <v>4.5340883864726072E-4</v>
       </c>
       <c r="C4" s="34">
-        <v>5.3616529758339677E-5</v>
+        <v>1.4109613094299915E-4</v>
       </c>
       <c r="D4" s="34">
-        <v>5.3616529758339677E-5</v>
+        <v>1.4109613094299915E-4</v>
       </c>
       <c r="E4" s="34">
-        <v>5.3616529758339677E-5</v>
+        <v>1.4109613094299915E-4</v>
       </c>
       <c r="F4" s="34">
         <v>0</v>
@@ -21008,7 +21008,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="34">
-        <v>1.6084958927501902E-4</v>
+        <v>4.2328839282899743E-4</v>
       </c>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -21046,16 +21046,16 @@
         <v>20</v>
       </c>
       <c r="B6" s="34">
-        <v>3.4351009391108858E-3</v>
+        <v>4.9965104568885609E-3</v>
       </c>
       <c r="C6" s="34">
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="D6" s="34">
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="E6" s="34">
-        <v>1.0689678069647774E-3</v>
+        <v>1.5548622646760399E-3</v>
       </c>
       <c r="F6" s="34">
         <v>0</v>
@@ -21064,7 +21064,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="34">
-        <v>3.2069034208943321E-3</v>
+        <v>4.6645867940281194E-3</v>
       </c>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
@@ -27577,6 +27577,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
     <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
@@ -27720,22 +27735,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7954CBA-CC49-4137-B897-2F07557F3495}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="40f4d404-d193-41dc-bb72-733c1e774208"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33097742-8605-4D00-9519-07E7CAC067CD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81E16404-9CDB-444B-B1EF-816DE1AF2890}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -27751,28 +27775,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7954CBA-CC49-4137-B897-2F07557F3495}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="40f4d404-d193-41dc-bb72-733c1e774208"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33097742-8605-4D00-9519-07E7CAC067CD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>